--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20 19:59:55</t>
+          <t>2026-06-21 12:22:39</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,10 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,6 +171,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
+  <autoFilter ref="A1:P8"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Hora inicio"/>
+    <tableColumn id="4" name="Hora fin"/>
+    <tableColumn id="5" name="Distrito"/>
+    <tableColumn id="6" name="Zona afectada"/>
+    <tableColumn id="7" name="Motivo"/>
+    <tableColumn id="8" name="Ubicación"/>
+    <tableColumn id="9" name="Título"/>
+    <tableColumn id="10" name="Subestaciones / SED"/>
+    <tableColumn id="11" name="Descripción completa"/>
+    <tableColumn id="12" name="Categoría"/>
+    <tableColumn id="13" name="Creado"/>
+    <tableColumn id="14" name="Modificado"/>
+    <tableColumn id="15" name="URL"/>
+    <tableColumn id="16" name="Hash"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -562,9 +590,585 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5877</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Av. Italia de Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Conexión de nuevo suministro de gran industria.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 2574.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 23 DE JUNIO DE 2026.
+Circuito : SED 2574.
+Hora : 09:00 a 11:00 Hrs.
+Motivo : Conexión de nuevo suministro de gran industria.
+Zonas afectadas: Av. Italia de Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:29 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:29</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5877&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>e62c6a962cd487ed90ae2938eec8e76aceb8020d8d27734ab5422eedc0385461</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Bolognesi San Martin de Porras, Calle San Martin, Calle Fray Martin, Av. Unión, Av. Amazonas, Av. Arequipa, Av. Ramon Castilla, Av. Francisco Bolognesi, Av. Chachani, Av. Aviación (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de tablero de distribución.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1132.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 24 DE JUNIO DE 2026.
+Circuito : SED 1132.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de tablero de distribución.
+Zonas afectadas: Bolognesi San Martin de Porras, Calle San Martin, Calle Fray Martin, Av. Unión, Av. Amazonas, Av. Arequipa, Av. Ramon Castilla, Av. Francisco Bolognesi, Av. Chachani, Av. Aviación (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:30 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:30</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5878&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>0dc12218615c348b4e85834ea464419715cb3b5c35300e1b3bc331fef6d28e46</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Alto Libertad: Av. Alfonso Ugarte, Av. Nicolas de Piérola con Av. Tumbes, Calle Abancay (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 100KVA</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3186.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 24 DE JUNIO DE 2026.
+Circuito : SED 3186.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de transformador a 100KVA
+Zonas afectadas: Alto Libertad: Av. Alfonso Ugarte, Av. Nicolas de Piérola con Av. Tumbes, Calle Abancay (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:30 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:30</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5879&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>34f77fb443a1065cb507a21f06bdebd2ffe92033c01c998bdffb004a2cca7551</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5874</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Vitor, de Vitor</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Vitor: Cuarta Pampa, La Caleta, Primera Pampa, Segunda Pampa, Tercera Pampa, Virgen de Chapi.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Vitor desde REC - 200139.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 25 DE JUNIO DE 2026:
+Circuito : Vitor desde REC - 200139.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Vitor: Cuarta Pampa, La Caleta, Primera Pampa, Segunda Pampa, Tercera Pampa, Virgen de Chapi.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:27 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:27</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5874&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>ca506cf2cb74dc51ec9e04add95b2868a2b2c634d5f786099c1ec86dcea53d5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Yura, de Yura</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Upis Los Milagros, Av. A Yura, CA Vía Yura – Arequipa, Asoc. Granjeros Industria Santusa (Distrito de Yura).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ciudad Municipal desde EMT 37380.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10015, 4287, 4147, 4778, 4777, 4148.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 25 DE JUNIO DE 2026.
+Circuito : Ciudad Municipal desde EMT 37380.
+Hora : 08:00 a 15:00 Hrs.
+Motivo : Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.
+Zonas afectadas: Upis Los Milagros, Av. A Yura, CA Vía Yura – Arequipa, Asoc. Granjeros Industria Santusa (Distrito de Yura).
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10015, 4287, 4147, 4778, 4777, 4148.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:31 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:31</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5880&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>6b1c3c616f6eefe93e256bcc524ff5ebe5be0ead698f3194b52f862c0a3a7300</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>La Joya, de La Joya</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Panamericana desde REC - 200137.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 26 DE JUNIO DE 2026:
+Circuito : Panamericana desde REC - 200137.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:29 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:29</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5876&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>c1e87dd416faefd531af72cbde75c07a7541bbd2c287c2702fa0951ad12048e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5875</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Villa Continental zona 3 y 4, Cesar Vallejo, José Carlos Mariátegui, Urbanización Casimiro Cuadros, Av. Héroes del Cenepa, (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Zamacola desde EMT 15481.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5194, 1765, 1722, 2842, 1875.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 26 DE JUNIO DE 2026.
+Circuito : Zamacola desde EMT 15481.
+Hora : 07:30 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión.
+Zonas afectadas: Villa Continental zona 3 y 4, Cesar Vallejo, José Carlos Mariátegui, Urbanización Casimiro Cuadros, Av. Héroes del Cenepa, (Distrito de Cayma).
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5194, 1765, 1722, 2842, 1875.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:28 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:28</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5875&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9c07490ae1b813717ac2cf735ca6c9c2e68dfa68b528a7e2fffe221c149b7929</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -582,173 +1186,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-21 19:31:29</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:33:45</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>REQUESTS_STATIC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
+      <c r="B16" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1205,7 +1205,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 15:33:45</t>
+          <t>2026-06-23 12:48:59</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1205,7 +1205,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 12:48:59</t>
+          <t>2026-06-24 12:30:28</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Av. Italia de Rio Seco (Distrito de Cerro Colorado).</t>
+          <t>Bolognesi San Martin de Porras, Calle San Martin, Calle Fray Martin, Av. Unión, Av. Amazonas, Av. Arequipa, Av. Ramon Castilla, Av. Francisco Bolognesi, Av. Chachani, Av. Aviación (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Conexión de nuevo suministro de gran industria.</t>
+          <t>Cambio de tablero de distribución.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 2574.</t>
+          <t>Circuito : SED 1132.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,85 +638,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 23 DE JUNIO DE 2026.
-Circuito : SED 2574.
-Hora : 09:00 a 11:00 Hrs.
-Motivo : Conexión de nuevo suministro de gran industria.
-Zonas afectadas: Av. Italia de Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 22/06/2026 9:29 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026 9:29</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5877&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>e62c6a962cd487ed90ae2938eec8e76aceb8020d8d27734ab5422eedc0385461</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5878</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Bolognesi San Martin de Porras, Calle San Martin, Calle Fray Martin, Av. Unión, Av. Amazonas, Av. Arequipa, Av. Ramon Castilla, Av. Francisco Bolognesi, Av. Chachani, Av. Aviación (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de tablero de distribución.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1132.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 24 DE JUNIO DE 2026.
@@ -726,76 +647,76 @@
 Zonas afectadas: Bolognesi San Martin de Porras, Calle San Martin, Calle Fray Martin, Av. Unión, Av. Amazonas, Av. Arequipa, Av. Ramon Castilla, Av. Francisco Bolognesi, Av. Chachani, Av. Aviación (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:30 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:30</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5878&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>0dc12218615c348b4e85834ea464419715cb3b5c35300e1b3bc331fef6d28e46</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5879</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Alto Libertad: Av. Alfonso Ugarte, Av. Nicolas de Piérola con Av. Tumbes, Calle Abancay (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 100KVA</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3186.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 24 DE JUNIO DE 2026.
@@ -805,80 +726,80 @@
 Zonas afectadas: Alto Libertad: Av. Alfonso Ugarte, Av. Nicolas de Piérola con Av. Tumbes, Calle Abancay (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:30 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:30</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5879&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>34f77fb443a1065cb507a21f06bdebd2ffe92033c01c998bdffb004a2cca7551</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5874</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Vitor, de Vitor</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Vitor: Cuarta Pampa, La Caleta, Primera Pampa, Segunda Pampa, Tercera Pampa, Virgen de Chapi.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Vitor desde REC - 200139.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 25 DE JUNIO DE 2026:
@@ -889,80 +810,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:27 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:27</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5874&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>ca506cf2cb74dc51ec9e04add95b2868a2b2c634d5f786099c1ec86dcea53d5f</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5880</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Upis Los Milagros, Av. A Yura, CA Vía Yura – Arequipa, Asoc. Granjeros Industria Santusa (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde EMT 37380.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>10015, 4287, 4147, 4778, 4777, 4148.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 25 DE JUNIO DE 2026.
@@ -973,80 +894,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10015, 4287, 4147, 4778, 4777, 4148.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:31 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:31</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5880&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>6b1c3c616f6eefe93e256bcc524ff5ebe5be0ead698f3194b52f862c0a3a7300</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5876</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Panamericana desde REC - 200137.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 26 DE JUNIO DE 2026:
@@ -1057,80 +978,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:29</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5876&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>c1e87dd416faefd531af72cbde75c07a7541bbd2c287c2702fa0951ad12048e9</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5875</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Villa Continental zona 3 y 4, Cesar Vallejo, José Carlos Mariátegui, Urbanización Casimiro Cuadros, Av. Héroes del Cenepa, (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : Zamacola desde EMT 15481.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5194, 1765, 1722, 2842, 1875.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 26 DE JUNIO DE 2026.
@@ -1141,25 +1062,105 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5194, 1765, 1722, 2842, 1875.</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 22/06/2026 9:28 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>22/06/2026 9:28</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5875&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9c07490ae1b813717ac2cf735ca6c9c2e68dfa68b528a7e2fffe221c149b7929</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5881</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [307] ALTO CAYMA.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 28 DE JUNIO DE 2026:
+Circuito : [307] ALTO CAYMA.
+Hora : 06:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).
+Zonas afectadas: Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3937, 3961, 2073, 1637, 2974, 3579, 3760, 1021, 1443, 1807, 2901, 2900, 2899, 1833, 1037, 2658, 2249, 3311, 4307, 3471, 2798, 3831, 1934, 3472, 3576, 1828, 1499, 1519, 1645, 3578, 3518, 1350, 1307, 3173, 1844, 2637, 1235, 1446, 2426, 2973, 1274, 2427, 3129, 2629, 3139, 1663, 1810, 3793, 3792, 3799, 3800, 3870, 2424, 4099, 4101, 4170, 3962, 4209, 4242, 4248, 4365, 4374, 4371, 4411, 4458, 4502, 4586, 4584, 4632, 4629, 4675, 4681, 4691, 4709, 4739, 4856, 4914, 4636, 4582, 5024, 4999, 5016, 4913, 5252, 5018, 5279, 5297, 5249, 5290, 5413, 5617, 5676, 5759, 5621, 5417, 5830, 5823, 5800, 5882, 3238, 4942, 10239, 10132, 5959, 10190, 5967.</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>el 22/06/2026 9:28 por Cuenta del sistema</t>
+          <t>el 24/06/2026 10:40 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 9:28</t>
+          <t>24/06/2026 10:40</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5875&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5881&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9c07490ae1b813717ac2cf735ca6c9c2e68dfa68b528a7e2fffe221c149b7929</t>
+          <t>a28cb6db084253a523c96f43bf6d211cedd3064c8951eae6a972c0977343754d</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1206,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24 12:30:28</t>
+          <t>2026-06-25 12:34:13</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1230,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1242,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1254,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1302,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1314,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
-  <autoFilter ref="A1:P8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
+  <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, de Cayma</t>
+          <t>Vitor, de Vitor</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bolognesi San Martin de Porras, Calle San Martin, Calle Fray Martin, Av. Unión, Av. Amazonas, Av. Arequipa, Av. Ramon Castilla, Av. Francisco Bolognesi, Av. Chachani, Av. Aviación (Distrito de Cayma).</t>
+          <t>Urbanizaciones del distrito de Vitor: Cuarta Pampa, La Caleta, Primera Pampa, Segunda Pampa, Tercera Pampa, Virgen de Chapi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de tablero de distribución.</t>
+          <t>Mantenimiento de redes en media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 1132.</t>
+          <t>Circuito : Vitor desde REC - 200139.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,170 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 24 DE JUNIO DE 2026.
-Circuito : SED 1132.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de tablero de distribución.
-Zonas afectadas: Bolognesi San Martin de Porras, Calle San Martin, Calle Fray Martin, Av. Unión, Av. Amazonas, Av. Arequipa, Av. Ramon Castilla, Av. Francisco Bolognesi, Av. Chachani, Av. Aviación (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 22/06/2026 9:30 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026 9:30</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5878&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>0dc12218615c348b4e85834ea464419715cb3b5c35300e1b3bc331fef6d28e46</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Alto Libertad: Av. Alfonso Ugarte, Av. Nicolas de Piérola con Av. Tumbes, Calle Abancay (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 100KVA</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3186.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 24 DE JUNIO DE 2026.
-Circuito : SED 3186.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de transformador a 100KVA
-Zonas afectadas: Alto Libertad: Av. Alfonso Ugarte, Av. Nicolas de Piérola con Av. Tumbes, Calle Abancay (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 22/06/2026 9:30 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026 9:30</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5879&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>34f77fb443a1065cb507a21f06bdebd2ffe92033c01c998bdffb004a2cca7551</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5874</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Vitor, de Vitor</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Vitor: Cuarta Pampa, La Caleta, Primera Pampa, Segunda Pampa, Tercera Pampa, Virgen de Chapi.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Vitor desde REC - 200139.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 25 DE JUNIO DE 2026:
@@ -810,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:27 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:27</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5874&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>ca506cf2cb74dc51ec9e04add95b2868a2b2c634d5f786099c1ec86dcea53d5f</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5880</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Upis Los Milagros, Av. A Yura, CA Vía Yura – Arequipa, Asoc. Granjeros Industria Santusa (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde EMT 37380.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>10015, 4287, 4147, 4778, 4777, 4148.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 25 DE JUNIO DE 2026.
@@ -894,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10015, 4287, 4147, 4778, 4777, 4148.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:31 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:31</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5880&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>6b1c3c616f6eefe93e256bcc524ff5ebe5be0ead698f3194b52f862c0a3a7300</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5876</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>La Joya, de La Joya</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Panamericana desde REC - 200137.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 26 DE JUNIO DE 2026:
@@ -978,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:29</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5876&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>c1e87dd416faefd531af72cbde75c07a7541bbd2c287c2702fa0951ad12048e9</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5875</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Villa Continental zona 3 y 4, Cesar Vallejo, José Carlos Mariátegui, Urbanización Casimiro Cuadros, Av. Héroes del Cenepa, (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Zamacola desde EMT 15481.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>5194, 1765, 1722, 2842, 1875.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 26 DE JUNIO DE 2026.
@@ -1062,76 +904,160 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5194, 1765, 1722, 2842, 1875.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:28 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:28</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5875&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>9c07490ae1b813717ac2cf735ca6c9c2e68dfa68b528a7e2fffe221c149b7929</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Andaray, Yanaquihua, de Andaray, de Yanaquihua</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Andaray: Alto Peru, Andaray, Callalli, Casillo, Chilachila, Huaranguil, Huecche. Urbanizaciones del distrito de Yanaquihua: 4 de Agosto, Alpacay, Charco, Charco Quiroz, Huaquillo, Ispacas, La Barrera, Lucmani, Pachaiza, Vallecito, Yanaquihua.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Reubicación de línea de media tensión.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ispacas desde REC - 600209.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+SÁBADO, 27 DE JUNIO DE 2026:
+Circuito : Ispacas desde REC - 600209.
+Hora : 10:00 a 14:00 Hrs.
+Motivo : Reubicación de línea de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Andaray: Alto Peru, Andaray, Callalli, Casillo, Chilachila, Huaranguil, Huecche. Urbanizaciones del distrito de Yanaquihua: 4 de Agosto, Alpacay, Charco, Charco Quiroz, Huaquillo, Ispacas, La Barrera, Lucmani, Pachaiza, Vallecito, Yanaquihua.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 25/06/2026 10:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>25/06/2026 10:10</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5882&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>cb5a17132842506b45e67e692a4d56baea28705277768cf3d65ce69de3c41c24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5881</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : [307] ALTO CAYMA.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 28 DE JUNIO DE 2026:
@@ -1142,30 +1068,30 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3937, 3961, 2073, 1637, 2974, 3579, 3760, 1021, 1443, 1807, 2901, 2900, 2899, 1833, 1037, 2658, 2249, 3311, 4307, 3471, 2798, 3831, 1934, 3472, 3576, 1828, 1499, 1519, 1645, 3578, 3518, 1350, 1307, 3173, 1844, 2637, 1235, 1446, 2426, 2973, 1274, 2427, 3129, 2629, 3139, 1663, 1810, 3793, 3792, 3799, 3800, 3870, 2424, 4099, 4101, 4170, 3962, 4209, 4242, 4248, 4365, 4374, 4371, 4411, 4458, 4502, 4586, 4584, 4632, 4629, 4675, 4681, 4691, 4709, 4739, 4856, 4914, 4636, 4582, 5024, 4999, 5016, 4913, 5252, 5018, 5279, 5297, 5249, 5290, 5413, 5617, 5676, 5759, 5621, 5417, 5830, 5823, 5800, 5882, 3238, 4942, 10239, 10132, 5959, 10190, 5967.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 24/06/2026 10:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>24/06/2026 10:40</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5881&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>a28cb6db084253a523c96f43bf6d211cedd3064c8951eae6a972c0977343754d</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
+  <autoFilter ref="A1:P7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1206,7 +1132,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25 12:34:13</t>
+          <t>2026-06-26 12:27:54</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1156,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1168,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1180,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1228,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1240,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1252,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1279,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
-  <autoFilter ref="A1:P7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
+  <autoFilter ref="A1:P5"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,223 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Vitor, de Vitor</t>
+          <t>La Joya, de La Joya</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Vitor: Cuarta Pampa, La Caleta, Primera Pampa, Segunda Pampa, Tercera Pampa, Virgen de Chapi.</t>
+          <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión.</t>
+          <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Vitor desde REC - 200139.</t>
+          <t>Circuito : Panamericana desde REC - 200137.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
+          <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
+          <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 25 DE JUNIO DE 2026:
-Circuito : Vitor desde REC - 200139.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Vitor: Cuarta Pampa, La Caleta, Primera Pampa, Segunda Pampa, Tercera Pampa, Virgen de Chapi.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4790, 6576, 6577, 6578, 6579, 6586, 6594, 6831, 6832, 6833, 6834, 6835, 6836, 6838, 6883, 6884, 6886, 6889, 6953, 6954, 7619, 7845, 7846, 7847, 7848, 7849, 7850, 7851, 7852, 7853, 7854, 7855, 7856, 7857, 7858, 7859, 7860, 7861, 7862, 7863, 7864, 7865, 7866, 7922, 7930, 8615, 8616, 8645, 8663, 8681, 8854, 8861, 8877, 8903, 8907, 9519, 10049, 10116, 10230, 10202.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 22/06/2026 9:27 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026 9:27</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5874&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>ca506cf2cb74dc51ec9e04add95b2868a2b2c634d5f786099c1ec86dcea53d5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Yura, de Yura</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Upis Los Milagros, Av. A Yura, CA Vía Yura – Arequipa, Asoc. Granjeros Industria Santusa (Distrito de Yura).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Ciudad Municipal desde EMT 37380.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>10015, 4287, 4147, 4778, 4777, 4148.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 25 DE JUNIO DE 2026.
-Circuito : Ciudad Municipal desde EMT 37380.
-Hora : 08:00 a 15:00 Hrs.
-Motivo : Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.
-Zonas afectadas: Upis Los Milagros, Av. A Yura, CA Vía Yura – Arequipa, Asoc. Granjeros Industria Santusa (Distrito de Yura).
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10015, 4287, 4147, 4778, 4777, 4148.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 22/06/2026 9:31 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026 9:31</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5880&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>6b1c3c616f6eefe93e256bcc524ff5ebe5be0ead698f3194b52f862c0a3a7300</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>La Joya, de La Joya</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Panamericana desde REC - 200137.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 26 DE JUNIO DE 2026:
@@ -820,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:29</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5876&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>c1e87dd416faefd531af72cbde75c07a7541bbd2c287c2702fa0951ad12048e9</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5875</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Villa Continental zona 3 y 4, Cesar Vallejo, José Carlos Mariátegui, Urbanización Casimiro Cuadros, Av. Héroes del Cenepa, (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Zamacola desde EMT 15481.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>5194, 1765, 1722, 2842, 1875.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 26 DE JUNIO DE 2026.
@@ -904,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5194, 1765, 1722, 2842, 1875.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 22/06/2026 9:28 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>22/06/2026 9:28</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5875&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>9c07490ae1b813717ac2cf735ca6c9c2e68dfa68b528a7e2fffe221c149b7929</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5882</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Andaray, Yanaquihua, de Andaray, de Yanaquihua</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Andaray: Alto Peru, Andaray, Callalli, Casillo, Chilachila, Huaranguil, Huecche. Urbanizaciones del distrito de Yanaquihua: 4 de Agosto, Alpacay, Charco, Charco Quiroz, Huaquillo, Ispacas, La Barrera, Lucmani, Pachaiza, Vallecito, Yanaquihua.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Reubicación de línea de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ispacas desde REC - 600209.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SÁBADO, 27 DE JUNIO DE 2026:
@@ -988,76 +820,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 25/06/2026 10:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25/06/2026 10:10</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5882&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>cb5a17132842506b45e67e692a4d56baea28705277768cf3d65ce69de3c41c24</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5881</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : [307] ALTO CAYMA.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 28 DE JUNIO DE 2026:
@@ -1068,30 +900,30 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3937, 3961, 2073, 1637, 2974, 3579, 3760, 1021, 1443, 1807, 2901, 2900, 2899, 1833, 1037, 2658, 2249, 3311, 4307, 3471, 2798, 3831, 1934, 3472, 3576, 1828, 1499, 1519, 1645, 3578, 3518, 1350, 1307, 3173, 1844, 2637, 1235, 1446, 2426, 2973, 1274, 2427, 3129, 2629, 3139, 1663, 1810, 3793, 3792, 3799, 3800, 3870, 2424, 4099, 4101, 4170, 3962, 4209, 4242, 4248, 4365, 4374, 4371, 4411, 4458, 4502, 4586, 4584, 4632, 4629, 4675, 4681, 4691, 4709, 4739, 4856, 4914, 4636, 4582, 5024, 4999, 5016, 4913, 5252, 5018, 5279, 5297, 5249, 5290, 5413, 5617, 5676, 5759, 5621, 5417, 5830, 5823, 5800, 5882, 3238, 4942, 10239, 10132, 5959, 10190, 5967.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 24/06/2026 10:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24/06/2026 10:40</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5881&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>a28cb6db084253a523c96f43bf6d211cedd3064c8951eae6a972c0977343754d</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P7"/>
+  <autoFilter ref="A1:P5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1132,7 +964,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26 12:27:54</t>
+          <t>2026-06-27 11:48:05</t>
         </is>
       </c>
     </row>
@@ -1156,7 +988,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1000,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1012,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1084,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1111,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
-  <autoFilter ref="A1:P5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La Joya, de La Joya</t>
+          <t>Andaray, Yanaquihua, de Andaray, de Yanaquihua</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.</t>
+          <t>Urbanizaciones del distrito de Andaray: Alto Peru, Andaray, Callalli, Casillo, Chilachila, Huaranguil, Huecche. Urbanizaciones del distrito de Yanaquihua: 4 de Agosto, Alpacay, Charco, Charco Quiroz, Huaquillo, Ispacas, La Barrera, Lucmani, Pachaiza, Vallecito, Yanaquihua.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión.</t>
+          <t>Reubicación de línea de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Panamericana desde REC - 200137.</t>
+          <t>Circuito : Ispacas desde REC - 600209.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,178 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
+          <t>6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 26 DE JUNIO DE 2026:
-Circuito : Panamericana desde REC - 200137.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de La Joya: El Ramal, Las Casuarinas.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6965, 6719, 6718, 6791, 6973, 6721, 7670, 6942, 6728, 6999, 6726, 6725, 6717, 6715, 7615, 6724, 6723, 6722, 7632, 6720, 6568, 7947, 7933, 8900, 8569, 8675, 8676, 8677, 8742, 6716.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 22/06/2026 9:29 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026 9:29</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5876&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>c1e87dd416faefd531af72cbde75c07a7541bbd2c287c2702fa0951ad12048e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5875</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Villa Continental zona 3 y 4, Cesar Vallejo, José Carlos Mariátegui, Urbanización Casimiro Cuadros, Av. Héroes del Cenepa, (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Zamacola desde EMT 15481.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>5194, 1765, 1722, 2842, 1875.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 26 DE JUNIO DE 2026.
-Circuito : Zamacola desde EMT 15481.
-Hora : 07:30 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión.
-Zonas afectadas: Villa Continental zona 3 y 4, Cesar Vallejo, José Carlos Mariátegui, Urbanización Casimiro Cuadros, Av. Héroes del Cenepa, (Distrito de Cayma).
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5194, 1765, 1722, 2842, 1875.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 22/06/2026 9:28 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026 9:28</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5875&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>9c07490ae1b813717ac2cf735ca6c9c2e68dfa68b528a7e2fffe221c149b7929</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5882</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>27/06/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Andaray, Yanaquihua, de Andaray, de Yanaquihua</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Andaray: Alto Peru, Andaray, Callalli, Casillo, Chilachila, Huaranguil, Huecche. Urbanizaciones del distrito de Yanaquihua: 4 de Agosto, Alpacay, Charco, Charco Quiroz, Huaquillo, Ispacas, La Barrera, Lucmani, Pachaiza, Vallecito, Yanaquihua.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Reubicación de línea de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Ispacas desde REC - 600209.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SÁBADO, 27 DE JUNIO DE 2026:
@@ -820,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 25/06/2026 10:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>25/06/2026 10:10</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5882&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>cb5a17132842506b45e67e692a4d56baea28705277768cf3d65ce69de3c41c24</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5881</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [307] ALTO CAYMA.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 28 DE JUNIO DE 2026:
@@ -900,30 +732,30 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3937, 3961, 2073, 1637, 2974, 3579, 3760, 1021, 1443, 1807, 2901, 2900, 2899, 1833, 1037, 2658, 2249, 3311, 4307, 3471, 2798, 3831, 1934, 3472, 3576, 1828, 1499, 1519, 1645, 3578, 3518, 1350, 1307, 3173, 1844, 2637, 1235, 1446, 2426, 2973, 1274, 2427, 3129, 2629, 3139, 1663, 1810, 3793, 3792, 3799, 3800, 3870, 2424, 4099, 4101, 4170, 3962, 4209, 4242, 4248, 4365, 4374, 4371, 4411, 4458, 4502, 4586, 4584, 4632, 4629, 4675, 4681, 4691, 4709, 4739, 4856, 4914, 4636, 4582, 5024, 4999, 5016, 4913, 5252, 5018, 5279, 5297, 5249, 5290, 5413, 5617, 5676, 5759, 5621, 5417, 5830, 5823, 5800, 5882, 3238, 4942, 10239, 10132, 5959, 10190, 5967.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 24/06/2026 10:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>24/06/2026 10:40</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5881&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>a28cb6db084253a523c96f43bf6d211cedd3064c8951eae6a972c0977343754d</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P5"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -964,7 +796,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27 11:48:05</t>
+          <t>2026-06-28 11:59:29</t>
         </is>
       </c>
     </row>
@@ -988,7 +820,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -1000,7 +832,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -1012,7 +844,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +916,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1111,7 +943,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,17 +593,17 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -613,115 +613,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Andaray, Yanaquihua, de Andaray, de Yanaquihua</t>
+          <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Andaray: Alto Peru, Andaray, Callalli, Casillo, Chilachila, Huaranguil, Huecche. Urbanizaciones del distrito de Yanaquihua: 4 de Agosto, Alpacay, Charco, Charco Quiroz, Huaquillo, Ispacas, La Barrera, Lucmani, Pachaiza, Vallecito, Yanaquihua.</t>
+          <t>Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reubicación de línea de media tensión.</t>
+          <t>Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Ispacas desde REC - 600209.</t>
+          <t>Circuito : [307] ALTO CAYMA.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
-        </is>
-      </c>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-SÁBADO, 27 DE JUNIO DE 2026:
-Circuito : Ispacas desde REC - 600209.
-Hora : 10:00 a 14:00 Hrs.
-Motivo : Reubicación de línea de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Andaray: Alto Peru, Andaray, Callalli, Casillo, Chilachila, Huaranguil, Huecche. Urbanizaciones del distrito de Yanaquihua: 4 de Agosto, Alpacay, Charco, Charco Quiroz, Huaquillo, Ispacas, La Barrera, Lucmani, Pachaiza, Vallecito, Yanaquihua.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6317, 6318, 6319, 7263, 7264, 7265, 7266, 7267, 7268, 7269, 7270, 7272, 7275, 7276, 7277, 7278, 7435, 7436, 7439, 7781, 7782, 7783, 7784, 7785, 7786, 7980, 7982, 7983, 7986, 7987, 8620, 10197, 10242.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 25/06/2026 10:10 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>25/06/2026 10:10</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5882&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>cb5a17132842506b45e67e692a4d56baea28705277768cf3d65ce69de3c41c24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5881</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [307] ALTO CAYMA.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 28 DE JUNIO DE 2026:
@@ -732,30 +648,598 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3937, 3961, 2073, 1637, 2974, 3579, 3760, 1021, 1443, 1807, 2901, 2900, 2899, 1833, 1037, 2658, 2249, 3311, 4307, 3471, 2798, 3831, 1934, 3472, 3576, 1828, 1499, 1519, 1645, 3578, 3518, 1350, 1307, 3173, 1844, 2637, 1235, 1446, 2426, 2973, 1274, 2427, 3129, 2629, 3139, 1663, 1810, 3793, 3792, 3799, 3800, 3870, 2424, 4099, 4101, 4170, 3962, 4209, 4242, 4248, 4365, 4374, 4371, 4411, 4458, 4502, 4586, 4584, 4632, 4629, 4675, 4681, 4691, 4709, 4739, 4856, 4914, 4636, 4582, 5024, 4999, 5016, 4913, 5252, 5018, 5279, 5297, 5249, 5290, 5413, 5617, 5676, 5759, 5621, 5417, 5830, 5823, 5800, 5882, 3238, 4942, 10239, 10132, 5959, 10190, 5967.</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 24/06/2026 10:40 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026 10:40</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5881&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>a28cb6db084253a523c96f43bf6d211cedd3064c8951eae6a972c0977343754d</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>5885</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Calle Señor de Huanca, Av. Cesar Vallejo, Av. Señor Milagroso, Av. Alto Cayma, Jr. Corpac, Calle La Lomada, Calle Chachani, Calle Sol de Oro, Sol de Oro zona A (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Zamacola desde EMT 38976.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>4511, 2330.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 01 DE JULIO DE 2026.
+Circuito : Zamacola desde EMT 38976.
+Hora : 07:30 a 15:00 Hrs.
+Motivo : Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.
+Zonas afectadas: Calle Señor de Huanca, Av. Cesar Vallejo, Av. Señor Milagroso, Av. Alto Cayma, Jr. Corpac, Calle La Lomada, Calle Chachani, Calle Sol de Oro, Sol de Oro zona A (Distrito de Cayma).
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4511, 2330.</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>el 24/06/2026 10:40 por Cuenta del sistema</t>
+          <t>el 29/06/2026 6:03 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 10:40</t>
+          <t>29/06/2026 6:03</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5881&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5885&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>a28cb6db084253a523c96f43bf6d211cedd3064c8951eae6a972c0977343754d</t>
+          <t>87b8e810eba19562e47d7e678c41aeb16f8847c4969f6164da51b98b68266038</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5886</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 100 KVA</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 2846</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 02 DE JULIO DE 2026.
+Circuito : SED 2846.
+Hora : 07:30 a 12:30 Hrs.
+Motivo : Cambio de transformador a 100 KVA
+Zonas afectadas: Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 29/06/2026 6:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>29/06/2026 6:04</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5886&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7b3229bb6939a8a92208bfc0f84717a9064571dd4dcefbf0ce35716f0ff847a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 100 KVA</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3183</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 02 DE JULIO DE 2026.
+Circuito : SED 3183.
+Hora : 07:30 a 12:30 Hrs.
+Motivo : Cambio de transformador a 100 KVA
+Zonas afectadas: Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 29/06/2026 6:05 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>29/06/2026 6:05</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5887&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>23c408d2a1c979d8f1b70c1a84c1dce5b2732adebe5d57a93985d37a7f00ad15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5888</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Uraca, de Uraca</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Uraca: Cantas, El Pedregal, La Mezana, Pitis, Villa Hermosa.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Torán desde CC - 810123.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 02 DE JULIO DE 2026:
+Circuito : Torán desde CC - 810123.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Uraca: Cantas, El Pedregal, La Mezana, Pitis, Villa Hermosa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 29/06/2026 6:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>29/06/2026 6:06</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5888&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0d16357bc8d9fc30ac2585399135fb3bcac675a58e1552cafc7f2afe2dd855fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pionero I desde REC - 200538.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 03 DE JULIO DE 2026:
+Circuito : Pionero I desde REC - 200538.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)
+Zonas afectadas: Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 29/06/2026 6:07 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>29/06/2026 6:07</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5889&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>f29d31980be7bad7c23f7fc40e3d0e70bf7e169c87cccf86ac91e1483a692e81</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5883</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a mayor potencia</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4056</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 03 DE JULIO DE 2026.
+Circuito : SED 4056.
+Hora : 07:30 a 12:30 Hrs.
+Motivo : Cambio de transformador a mayor potencia
+Zonas afectadas: Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>29/06/2026 6:02</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5883&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>394f2bbfc705e1b7511bba674d43991218532fba90fd211fa494cee19c25fc6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5884</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Yura, de Yura</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Dios (Distrito de Yura).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a mayor potencia.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 10292.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 03 DE JULIO DE 2026.
+Circuito : SED 10292.
+Hora : 07:30 a 12:30 Hrs.
+Motivo : Cambio de transformador a mayor potencia.
+Zonas afectadas: Ciudad de Dios (Distrito de Yura).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>29/06/2026 6:02</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5884&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>47ee2bf0880ab307ae27eee3a30d1f2ca6a54be11002ab2871f2defb3da5fa9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -796,7 +1280,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28 11:59:29</t>
+          <t>2026-06-29 14:30:28</t>
         </is>
       </c>
     </row>
@@ -820,7 +1304,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -832,7 +1316,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -844,7 +1328,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -892,7 +1376,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -904,7 +1388,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -916,7 +1400,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -943,7 +1427,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
+  <autoFilter ref="A1:P8"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
+          <t>Calle Señor de Huanca, Av. Cesar Vallejo, Av. Señor Milagroso, Av. Alto Cayma, Jr. Corpac, Calle La Lomada, Calle Chachani, Calle Sol de Oro, Sol de Oro zona A (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).</t>
+          <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [307] ALTO CAYMA.</t>
+          <t>Circuito : Zamacola desde EMT 38976.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,92 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4511, 2330.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 28 DE JUNIO DE 2026:
-Circuito : [307] ALTO CAYMA.
-Hora : 06:00 a 14:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de poste, cambio de conductor a 120 mm2).
-Zonas afectadas: Urbanizaciones del distrito de Cayma: Advidge, Bello Amanecer, Bello Horizonte, Bello Monte, Boulevard Los Arces, Cerrito San Jacinto, Colegio de Ingenieros, Conjunto Multifamiliar Edifica Inversiones del Sur S.A.C, El Arroyo de Cayma, El Mirador, Emperatriz, Entel II, Jorge Basadre, La Campiña, La Puerta del Sol, La Romero, La Tomilla Zona A, Las Condes, Las Efigies, Las Terrazas de Cayma, Los Andenes, Los Ángeles de Cayma, Los Girasoles, Los Portales, Los Ruiseñores, Macondo, Mirasol de Cayma, Quinta Los Andenes de Cayma, Quinta Residencial Mediterráneo, Quinta Samay, Residencial Los Arces, Residencial Los Delfines, Residencial Monte Rosa, Residencial Santa Elisa, San Antonio, San Doria de Cayma, Santa Elisa, Un Rincón en la Chacrita, Valle Escondido, Villa Cayma. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, Cerro Colorado (Pueblo Viejo), El Rosario II, La Alborada, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3937, 3961, 2073, 1637, 2974, 3579, 3760, 1021, 1443, 1807, 2901, 2900, 2899, 1833, 1037, 2658, 2249, 3311, 4307, 3471, 2798, 3831, 1934, 3472, 3576, 1828, 1499, 1519, 1645, 3578, 3518, 1350, 1307, 3173, 1844, 2637, 1235, 1446, 2426, 2973, 1274, 2427, 3129, 2629, 3139, 1663, 1810, 3793, 3792, 3799, 3800, 3870, 2424, 4099, 4101, 4170, 3962, 4209, 4242, 4248, 4365, 4374, 4371, 4411, 4458, 4502, 4586, 4584, 4632, 4629, 4675, 4681, 4691, 4709, 4739, 4856, 4914, 4636, 4582, 5024, 4999, 5016, 4913, 5252, 5018, 5279, 5297, 5249, 5290, 5413, 5617, 5676, 5759, 5621, 5417, 5830, 5823, 5800, 5882, 3238, 4942, 10239, 10132, 5959, 10190, 5967.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 24/06/2026 10:40 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026 10:40</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5881&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>a28cb6db084253a523c96f43bf6d211cedd3064c8951eae6a972c0977343754d</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5885</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Calle Señor de Huanca, Av. Cesar Vallejo, Av. Señor Milagroso, Av. Alto Cayma, Jr. Corpac, Calle La Lomada, Calle Chachani, Calle Sol de Oro, Sol de Oro zona A (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Zamacola desde EMT 38976.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4511, 2330.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 01 DE JULIO DE 2026.
@@ -732,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4511, 2330.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:03 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:03</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5885&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>87b8e810eba19562e47d7e678c41aeb16f8847c4969f6164da51b98b68266038</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5886</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 100 KVA</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2846</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 02 DE JULIO DE 2026.
@@ -811,76 +731,76 @@
 Zonas afectadas: Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:04</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5886&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>7b3229bb6939a8a92208bfc0f84717a9064571dd4dcefbf0ce35716f0ff847a2</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5887</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 100 KVA</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3183</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 02 DE JULIO DE 2026.
@@ -890,80 +810,80 @@
 Zonas afectadas: Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:05</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5887&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>23c408d2a1c979d8f1b70c1a84c1dce5b2732adebe5d57a93985d37a7f00ad15</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5888</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Uraca, de Uraca</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Uraca: Cantas, El Pedregal, La Mezana, Pitis, Villa Hermosa.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Torán desde CC - 810123.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 02 DE JULIO DE 2026:
@@ -974,80 +894,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:06</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5888&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>0d16357bc8d9fc30ac2585399135fb3bcac675a58e1552cafc7f2afe2dd855fc</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5889</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pionero I desde REC - 200538.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026:
@@ -1058,76 +978,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:07</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5889&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>f29d31980be7bad7c23f7fc40e3d0e70bf7e169c87cccf86ac91e1483a692e81</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5883</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a mayor potencia</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4056</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026.
@@ -1137,76 +1057,76 @@
 Zonas afectadas: Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:02</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5883&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>394f2bbfc705e1b7511bba674d43991218532fba90fd211fa494cee19c25fc6a</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5884</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a mayor potencia.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10292.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026.
@@ -1216,30 +1136,30 @@
 Zonas afectadas: Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:02</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5884&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>47ee2bf0880ab307ae27eee3a30d1f2ca6a54be11002ab2871f2defb3da5fa9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1280,7 +1200,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29 14:30:28</t>
+          <t>2026-06-30 12:25:56</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1224,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1236,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1248,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1320,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1347,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30 12:25:56</t>
+          <t>2026-07-01 12:49:31</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 12:49:31</t>
+          <t>2026-07-02 12:22:28</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>7</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
-  <autoFilter ref="A1:P8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Calle Señor de Huanca, Av. Cesar Vallejo, Av. Señor Milagroso, Av. Alto Cayma, Jr. Corpac, Calle La Lomada, Calle Chachani, Calle Sol de Oro, Sol de Oro zona A (Distrito de Cayma).</t>
+          <t>Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.</t>
+          <t>Cambio de transformador a 100 KVA</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Zamacola desde EMT 38976.</t>
+          <t>Circuito : SED 2846</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,92 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>4511, 2330.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 01 DE JULIO DE 2026.
-Circuito : Zamacola desde EMT 38976.
-Hora : 07:30 a 15:00 Hrs.
-Motivo : Subsanación de deficiencias en atención a la Resolución Osinergmin 228-2009-OS/CD y otros mantenimientos de redes de media tensión.
-Zonas afectadas: Calle Señor de Huanca, Av. Cesar Vallejo, Av. Señor Milagroso, Av. Alto Cayma, Jr. Corpac, Calle La Lomada, Calle Chachani, Calle Sol de Oro, Sol de Oro zona A (Distrito de Cayma).
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4511, 2330.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 29/06/2026 6:03 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>29/06/2026 6:03</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5885&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>87b8e810eba19562e47d7e678c41aeb16f8847c4969f6164da51b98b68266038</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5886</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 100 KVA</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 2846</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 02 DE JULIO DE 2026.
@@ -731,76 +647,76 @@
 Zonas afectadas: Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:04</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5886&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>7b3229bb6939a8a92208bfc0f84717a9064571dd4dcefbf0ce35716f0ff847a2</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5887</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 100 KVA</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3183</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 02 DE JULIO DE 2026.
@@ -810,80 +726,80 @@
 Zonas afectadas: Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:05</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5887&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>23c408d2a1c979d8f1b70c1a84c1dce5b2732adebe5d57a93985d37a7f00ad15</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5888</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Uraca, de Uraca</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Uraca: Cantas, El Pedregal, La Mezana, Pitis, Villa Hermosa.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Torán desde CC - 810123.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 02 DE JULIO DE 2026:
@@ -894,80 +810,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:06</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5888&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>0d16357bc8d9fc30ac2585399135fb3bcac675a58e1552cafc7f2afe2dd855fc</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5889</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pionero I desde REC - 200538.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026:
@@ -978,76 +894,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:07</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5889&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>f29d31980be7bad7c23f7fc40e3d0e70bf7e169c87cccf86ac91e1483a692e81</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5883</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a mayor potencia</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4056</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026.
@@ -1057,76 +973,76 @@
 Zonas afectadas: Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:02</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5883&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>394f2bbfc705e1b7511bba674d43991218532fba90fd211fa494cee19c25fc6a</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5884</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a mayor potencia.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10292.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026.
@@ -1136,30 +1052,444 @@
 Zonas afectadas: Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>29/06/2026 6:02</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5884&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>47ee2bf0880ab307ae27eee3a30d1f2ca6a54be11002ab2871f2defb3da5fa9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5893</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>SET : [93] SAN ANTONIO.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 05 DE JULIO DE 2026:
+SET : [93] SAN ANTONIO.
+Hora : 06:00 a 16:00 Hrs.
+Motivo : Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.
+Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
+          <t>el 02/07/2026 8:12 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 6:02</t>
+          <t>02/07/2026 8:12</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5884&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5893&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47ee2bf0880ab307ae27eee3a30d1f2ca6a54be11002ab2871f2defb3da5fa9c</t>
+          <t>2821a5d7f82070a776fac2ffaa4ae59d5c2ef4384eff42c234d3fe30083516e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5894</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Caylloma, de Caylloma</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 05 DE JULIO DE 2026:
+Hora : 06:00 a 16:00 Hrs.
+Motivo : Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.
+Zonas afectadas: Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 02/07/2026 17:56 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2026 17:56</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5894&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>05cdeb3c6b982940030097696f280ba2f9c1c2ce8c493ae4dfc0327ec7d0bc72</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>SET : [87] ORCOPAMPA.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 05 DE JULIO DE 2026:
+SET : [87] ORCOPAMPA.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.
+Zonas afectadas: Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2026 8:10</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5890&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>634257f31dc0b27c766e664d97d0e7ef2483703973471ac9a2bf0ab182b4cd62</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5891</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>SET : [70] COTAHUASI.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 05 DE JULIO DE 2026:
+SET : [70] COTAHUASI.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.
+Zonas afectadas: Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2026 8:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5891&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>133fd2c0b75f4878a4f9bcdb40aad25277f4ff7b74f746df1c8fa281bbfba61a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5892</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Pruebas eléctricas a transformador de potencia.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SET : [91] CALLALLI.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 05 DE JULIO DE 2026:
+SET : [91] CALLALLI.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Pruebas eléctricas a transformador de potencia.
+Zonas afectadas : Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 02/07/2026 8:11 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2026 8:11</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5892&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1c652983661656f190bc434e501bf6800a6de04b54af1e1d326910d0d9361b4f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1200,7 +1530,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02 12:22:28</t>
+          <t>2026-07-03 12:21:08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1554,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1566,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1578,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1626,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1638,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1650,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1677,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,297 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, de Cayma</t>
+          <t>Majes, de Majes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
+          <t>Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de transformador a 100 KVA</t>
+          <t>Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 2846</t>
+          <t>Circuito : Pionero I desde REC - 200538.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 02 DE JULIO DE 2026.
-Circuito : SED 2846.
-Hora : 07:30 a 12:30 Hrs.
-Motivo : Cambio de transformador a 100 KVA
-Zonas afectadas: Jr. Chorrillos, Av. Pumacahua, Calle América, Calle Ilo, Calle General Ollantay, Av. José Carlos Mariátegui (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 29/06/2026 6:04 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>29/06/2026 6:04</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5886&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>7b3229bb6939a8a92208bfc0f84717a9064571dd4dcefbf0ce35716f0ff847a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5887</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 100 KVA</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3183</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 02 DE JULIO DE 2026.
-Circuito : SED 3183.
-Hora : 07:30 a 12:30 Hrs.
-Motivo : Cambio de transformador a 100 KVA
-Zonas afectadas: Av. Puno, Calle Loreto, Calle Carabaya, Calle Lambayeque (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 29/06/2026 6:05 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>29/06/2026 6:05</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5887&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>23c408d2a1c979d8f1b70c1a84c1dce5b2732adebe5d57a93985d37a7f00ad15</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5888</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Uraca, de Uraca</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Uraca: Cantas, El Pedregal, La Mezana, Pitis, Villa Hermosa.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Torán desde CC - 810123.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 02 DE JULIO DE 2026:
-Circuito : Torán desde CC - 810123.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Uraca: Cantas, El Pedregal, La Mezana, Pitis, Villa Hermosa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7156, 7129, 7128, 7127, 7126, 7151, 7124, 7131, 7946, 7130, 7471, 7125, 7176, 7486, 7132, 7994, 8538.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 29/06/2026 6:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29/06/2026 6:06</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5888&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0d16357bc8d9fc30ac2585399135fb3bcac675a58e1552cafc7f2afe2dd855fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Pionero I desde REC - 200538.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026:
@@ -894,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:07</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5889&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>f29d31980be7bad7c23f7fc40e3d0e70bf7e169c87cccf86ac91e1483a692e81</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5883</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a mayor potencia</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4056</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026.
@@ -973,76 +731,76 @@
 Zonas afectadas: Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:02</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5883&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>394f2bbfc705e1b7511bba674d43991218532fba90fd211fa494cee19c25fc6a</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5884</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>03/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a mayor potencia.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10292.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 03 DE JULIO DE 2026.
@@ -1052,80 +810,80 @@
 Zonas afectadas: Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29/06/2026 6:02</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5884&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>47ee2bf0880ab307ae27eee3a30d1f2ca6a54be11002ab2871f2defb3da5fa9c</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5893</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SET : [93] SAN ANTONIO.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1136,76 +894,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:12 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:12</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5893&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>2821a5d7f82070a776fac2ffaa4ae59d5c2ef4384eff42c234d3fe30083516e0</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5894</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Caylloma, de Caylloma</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1214,80 +972,80 @@
 Zonas afectadas: Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 17:56 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 17:56</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5894&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>05cdeb3c6b982940030097696f280ba2f9c1c2ce8c493ae4dfc0327ec7d0bc72</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5890</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>SET : [87] ORCOPAMPA.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1298,80 +1056,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5890&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>634257f31dc0b27c766e664d97d0e7ef2483703973471ac9a2bf0ab182b4cd62</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5891</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1382,80 +1140,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5891&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>133fd2c0b75f4878a4f9bcdb40aad25277f4ff7b74f746df1c8fa281bbfba61a</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5892</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Pruebas eléctricas a transformador de potencia.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>SET : [91] CALLALLI.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1466,30 +1224,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:11 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:11</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5892&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>1c652983661656f190bc434e501bf6800a6de04b54af1e1d326910d0d9361b4f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1530,7 +1288,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03 12:21:08</t>
+          <t>2026-07-04 11:48:02</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1312,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1324,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1336,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1408,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1435,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,297 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.</t>
+          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)</t>
+          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Pionero I desde REC - 200538.</t>
+          <t>SET : [93] SAN ANTONIO.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES</t>
+          <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
+          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 03 DE JULIO DE 2026:
-Circuito : Pionero I desde REC - 200538.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de poste, limpieza de aisladores y podado de árboles cercanos a la línea de media tensión)
-Zonas afectadas: Urbanizaciones del distrito de Majes: Avg Aspein, Avg Los Olivos, Futuros Forjadores de Majes - Aspein Sector 1Y6, La Nueva Arequipa de Majes Zona A, La Nueva Arequipa de Majes Zona B, La Nueva Arequipa de Majes Zona C, Rafael Hoyos Rubio.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6154, 6963, 6412, 6413, 6438, 7867, 7660, 8912, 8988, 8986, 8987, 8715, 8716, 8973, 8992, 8993, 8994, 8995, 8996, 8997, 8999, 8998, 8965, 8959, 6411, 8718, 8719, 8717, 8721, 8720.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 29/06/2026 6:07 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>29/06/2026 6:07</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5889&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>f29d31980be7bad7c23f7fc40e3d0e70bf7e169c87cccf86ac91e1483a692e81</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5883</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a mayor potencia</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4056</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 03 DE JULIO DE 2026.
-Circuito : SED 4056.
-Hora : 07:30 a 12:30 Hrs.
-Motivo : Cambio de transformador a mayor potencia
-Zonas afectadas: Urbanización Teresa de Jesús (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>29/06/2026 6:02</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5883&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>394f2bbfc705e1b7511bba674d43991218532fba90fd211fa494cee19c25fc6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5884</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Yura, de Yura</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Ciudad de Dios (Distrito de Yura).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a mayor potencia.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 10292.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 03 DE JULIO DE 2026.
-Circuito : SED 10292.
-Hora : 07:30 a 12:30 Hrs.
-Motivo : Cambio de transformador a mayor potencia.
-Zonas afectadas: Ciudad de Dios (Distrito de Yura).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 29/06/2026 6:02 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29/06/2026 6:02</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5884&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>47ee2bf0880ab307ae27eee3a30d1f2ca6a54be11002ab2871f2defb3da5fa9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5893</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>SET : [93] SAN ANTONIO.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -894,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:12 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:12</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5893&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>2821a5d7f82070a776fac2ffaa4ae59d5c2ef4384eff42c234d3fe30083516e0</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5894</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Caylloma, de Caylloma</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -972,80 +730,80 @@
 Zonas afectadas: Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 17:56 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 17:56</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5894&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>05cdeb3c6b982940030097696f280ba2f9c1c2ce8c493ae4dfc0327ec7d0bc72</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5890</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SET : [87] ORCOPAMPA.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1056,80 +814,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5890&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>634257f31dc0b27c766e664d97d0e7ef2483703973471ac9a2bf0ab182b4cd62</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5891</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1140,80 +898,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5891&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>133fd2c0b75f4878a4f9bcdb40aad25277f4ff7b74f746df1c8fa281bbfba61a</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5892</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Pruebas eléctricas a transformador de potencia.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SET : [91] CALLALLI.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 05 DE JULIO DE 2026:
@@ -1224,30 +982,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 02/07/2026 8:11 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>02/07/2026 8:11</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5892&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>1c652983661656f190bc434e501bf6800a6de04b54af1e1d326910d0d9361b4f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1288,7 +1046,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04 11:48:02</t>
+          <t>2026-07-05 11:49:06</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1070,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1082,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1094,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1166,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1193,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P20" headerRowCount="1">
+  <autoFilter ref="A1:P20"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1004,8 +1004,1152 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización Heresi, Calle Los Manzanos (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 200 KVA</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4916.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 06 DE JULIO DE 2026.
+Circuito : SED 4916.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de transformador a 200 KVA
+Zonas afectadas: Urbanización Heresi, Calle Los Manzanos (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:08 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:08</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5905&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>e75fce447214779e1a768be17ed363c4a108ba1db4f36ad3dfafcf8607198ea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Acari, Bella Unión, de Acari, de Bella Unión</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización del Distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliacion Huaroto, Anexo de Chocavento, Anexo El Molino, Anexo Huaroto, Anexo La Joya, Cruz Pata, Humarote, Machaynioc, Mallco, Otapara, Pueblo Nuevo de Acari, Pueblo Viejo de Acari, Santa Teresa, Sector Alto Chocavento, Sector Portachuelos, Upis Miraflores. Urbanización del Distrito de Bella Unión: Bella Unión, Fundo Incahuasi.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [5601] ACARI.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 07 DE JULIO DE 2026:
+Circuito : [5601] ACARI.
+Hora : 07:30 a 10:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas Afectadas: Urbanización del Distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliacion Huaroto, Anexo de Chocavento, Anexo El Molino, Anexo Huaroto, Anexo La Joya, Cruz Pata, Humarote, Machaynioc, Mallco, Otapara, Pueblo Nuevo de Acari, Pueblo Viejo de Acari, Santa Teresa, Sector Alto Chocavento, Sector Portachuelos, Upis Miraflores. Urbanización del Distrito de Bella Unión: Bella Unión, Fundo Incahuasi.
+Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9666, 9667, 9673, 9671, 9672, 9610, 9620, 9660, 9662, 9611, 9613, 9615, 9618, 9617, 9616, 9814, 9815, 9693, 9696, 9612, 9614, 9661, 9669, 9807, 9810, 9811, 9816, 9817, 9813, 9812, 9852, 9857, 9842, 9843, 9844, 9839, 9840, 9841, 9860, 9872, 9878, 9879, 7989, 9883, 9884, 9885, 9952, 9966, 9959, 9973, 9970, 9971, 9794, 9997, 9571, 9587, 9364, 9363, 9372, 9391, 9397, 9393, 10250, 9969, 9413, 9416, 9445, 10201, 9670, 9619, 9967.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:09</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5907&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>16a74ce1f73ff45a8af4f122621da9816b3579672378031bb4ead11edc66608b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5908</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Cerro Colorado: Semi-Rural Pachacutec Grupo 15, Semi-Rural Pachacutec Grupo 25.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (podado de ramas de árboles cercanos a línea de media tensión).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [707] COMERCIO.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 07 DE JULIO DE 2026:
+Circuito : [707] COMERCIO.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (podado de ramas de árboles cercanos a línea de media tensión).
+Zonas afectadas: Urbanizaciones del Distrito de Cerro Colorado: Semi-Rural Pachacutec Grupo 15, Semi-Rural Pachacutec Grupo 25.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:10</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5908&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>bb54f1edf0d109046bd1a2c93b94fafd63a09ad8243dd17d36cb6c2202800b26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5906</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Bella Unión, de Bella Unión</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Bella Unión: Fundo Santa Julia, Sector Coquito, Fundo Los Olivos, Fundo Santa Sofía, Empresa Minera Los Molles.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Platinos desde REC - 560307.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 07 DE JULIO DE 2026:
+Circuito : Platinos desde REC - 560307.
+Hora : 13:30 a 17:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Bella Unión: Fundo Santa Julia, Sector Coquito, Fundo Los Olivos, Fundo Santa Sofía, Empresa Minera Los Molles.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9555, 9556, 9557, 9558, 9559, 9560, 9561, 7988.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:09</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5906&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>a3a738e58eef8f6e67fbd7b68be2fd65e8a02004db699995990bd0255808a52b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5899</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: D1, D3, D4, D-4 Juan Velazco Alvarado, El Alto.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio e intermediación de postes, limpieza de aisladores y podado de ramas de árboles cercanos a la línea de media tensión).</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pedregal desde BC - 950215.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 08 DE JULIO DE 2026:
+Circuito : Pedregal desde BC - 950215.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio e intermediación de postes, limpieza de aisladores y podado de ramas de árboles cercanos a la línea de media tensión).
+Zonas afectadas: Urbanizaciones del distrito de Majes: D1, D3, D4, D-4 Juan Velazco Alvarado, El Alto.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:04</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5899&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>cb54dcedab8c72292e80ba56ef9603e30dc30b94f047f351167592ed3e63c90d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5895</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de subestación tipo caseta.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1548.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 08 DE JULIO DE 2026.
+Circuito : SED 1548.
+Hora : 07:30 a 11:30 Hrs.
+Motivo : Mantenimiento de subestación tipo caseta.
+Zonas afectadas: Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5895&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1466c54750ce7fabcb21e4338b5debcaf43df6ea9d81d73803b77a0ec14f8397</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de subestación tipo caseta.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4488</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 08 DE JULIO DE 2026.
+Circuito : SED 4488.
+Hora : 07:30 a 11:30 Hrs.
+Motivo : Mantenimiento de subestación tipo caseta.
+Zonas afectadas: Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5896&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0bd20768ba0d1b39101a6475ba8aa13c183555b28e651cf179155a8bcc99cb41</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5897</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Acari, de Acari</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliación Huaroto, Anexo Huaroto, Anexo La Joya, Humarote, Otapara, Upis Miraflores, Machaynioc, Sector Mallco.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Acarí desde REC - 560105.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 08 DE JULIO DE 2026:
+Circuito : Acarí desde REC - 560105.
+Hora : 07:30 a 12:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas Afectadas: Urbanizaciones del distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliación Huaroto, Anexo Huaroto, Anexo La Joya, Humarote, Otapara, Upis Miraflores, Machaynioc, Sector Mallco.
+Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9587, 9814, 9445, 9815, 9693, 9966, 9816, 9817, 9812, 9813, 9883, 9970, 9794, 9997, 9391, 9416, 9884, 9885.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5897&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>61263ad9c945dd5e1f8be618a210112bcd5b76ca4a43be292f51a44e4075afae</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>5898</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Caraveli, Bella Unión, de Caraveli, de Bella Unión</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Caraveli: Fundo Marceliano. Urbanizaciones del distrito de Bella Unión: Fundo San Isidro.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Chala desde SL - 560264.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9832, 9678.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 08 DE JULIO DE 2026:
+Circuito : Chala desde SL - 560264.
+Hora : 14:30 a 16:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Caraveli: Fundo Marceliano. Urbanizaciones del distrito de Bella Unión: Fundo San Isidro.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9832, 9678.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:03 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:03</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5898&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>07ae7144f41a36a6fc0994eb5d8c014c010c2c1a979d5c26c1b3ac151816a1c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Valle Blanco desde BC - 200577.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 09 DE JULIO DE 2026:
+Circuito : Valle Blanco desde BC - 200577.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:05 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:05</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5901&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>eec06c9e26677b0d6945206bf673da94dc85413acbd5c05c83a93e08fd578b53</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>5902</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Lomas, de Lomas</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Chala desde REC - 200157.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 09 DE JULIO DE 2026:
+Circuito : Chala desde REC - 200157.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:06</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5902&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>3a3feafd29901401df7aed9c45921fcc59d37fb98ad972591efa5d166db4dfac</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Cocachacra</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito Cocachacra: El Fiscal.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de transformador y limpieza de aisladores).</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Fiscal desde CC - 200243.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>8222 8223 8512 8224 8513.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 09 DE JULIO DE 2026:
+Circuito : Fiscal desde CC - 200243.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de transformador y limpieza de aisladores).
+Zonas afectadas: Urbanizaciones del distrito Cocachacra: El Fiscal.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8222 8223 8512 8224 8513.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:04</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5900&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>74a48a1e37cadf8f292836fb6f4ea66db71a266cf5d7511741e0d825f76963f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>5903</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>José Luis Bustamante, Rivero, de José Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 160 KVA</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3245.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 10 DE JULIO DE 2026.
+Circuito : SED 3245.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de transformador a 160 KVA
+Zonas afectadas: Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:06</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5903&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4113bd84b32737addd1cd18cfbb0c5599a9ce1250d3715761149a382910f9c51</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Bella Unión, Jaqui, Yauca, de Bella Unión, de Jaqui, de Yauca</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [5603] PLATINOS.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 10 DE JULIO DE 2026:
+Circuito : [5603] PLATINOS.
+Hora : 07:30 a 13:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:07 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:07</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5904&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>946b20909abaf56343358a2b8246ca27cc6f417123c11a409dccb58477cf575a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1046,7 +2190,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 11:49:06</t>
+          <t>2026-07-06 14:03:50</t>
         </is>
       </c>
     </row>
@@ -1070,7 +2214,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -1082,7 +2226,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -1094,7 +2238,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -1142,7 +2286,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1154,7 +2298,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1166,7 +2310,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1193,7 +2337,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P20" headerRowCount="1">
-  <autoFilter ref="A1:P20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P15" headerRowCount="1">
+  <autoFilter ref="A1:P15"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
+          <t>Urbanización Heresi, Calle Los Manzanos (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
+          <t>Cambio de transformador a 200 KVA</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SET : [93] SAN ANTONIO.</t>
+          <t>Circuito : SED 4916.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,422 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 05 DE JULIO DE 2026:
-SET : [93] SAN ANTONIO.
-Hora : 06:00 a 16:00 Hrs.
-Motivo : Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.
-Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 02/07/2026 8:12 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026 8:12</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5893&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>2821a5d7f82070a776fac2ffaa4ae59d5c2ef4384eff42c234d3fe30083516e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5894</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Caylloma, de Caylloma</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de la línea L-6015 por ET-AYMARAES SAC</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 05 DE JULIO DE 2026:
-Hora : 06:00 a 16:00 Hrs.
-Motivo : Mantenimiento de la línea L-6015 por ET-AYMARAES SAC.
-Zonas afectadas: Urbanizaciones del distrito de Caylloma: Municipalidad distrital de Caylloma (Suministro en bloque).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 02/07/2026 17:56 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026 17:56</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5894&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>05cdeb3c6b982940030097696f280ba2f9c1c2ce8c493ae4dfc0327ec7d0bc72</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SET : [87] ORCOPAMPA.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 05 DE JULIO DE 2026:
-SET : [87] ORCOPAMPA.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.
-Zonas afectadas: Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026 8:10</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5890&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>634257f31dc0b27c766e664d97d0e7ef2483703973471ac9a2bf0ab182b4cd62</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5891</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>SET : [70] COTAHUASI.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 05 DE JULIO DE 2026:
-SET : [70] COTAHUASI.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : AFECTADO POR DESCONEXIÓN DE LA LÍNEA L-1040 y L-1047.
-Zonas afectadas: Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 02/07/2026 8:10 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026 8:10</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5891&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>133fd2c0b75f4878a4f9bcdb40aad25277f4ff7b74f746df1c8fa281bbfba61a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5892</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Pruebas eléctricas a transformador de potencia.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SET : [91] CALLALLI.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 05 DE JULIO DE 2026:
-SET : [91] CALLALLI.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Pruebas eléctricas a transformador de potencia.
-Zonas afectadas : Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 02/07/2026 8:11 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>02/07/2026 8:11</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5892&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1c652983661656f190bc434e501bf6800a6de04b54af1e1d326910d0d9361b4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5905</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Urbanización Heresi, Calle Los Manzanos (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 200 KVA</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4916.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 LUNES, 06 DE JULIO DE 2026.
@@ -1061,76 +647,76 @@
 Zonas afectadas: Urbanización Heresi, Calle Los Manzanos (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:08</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5905&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>e75fce447214779e1a768be17ed363c4a108ba1db4f36ad3dfafcf8607198ea5</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5907</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Acari, Bella Unión, de Acari, de Bella Unión</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanización del Distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliacion Huaroto, Anexo de Chocavento, Anexo El Molino, Anexo Huaroto, Anexo La Joya, Cruz Pata, Humarote, Machaynioc, Mallco, Otapara, Pueblo Nuevo de Acari, Pueblo Viejo de Acari, Santa Teresa, Sector Alto Chocavento, Sector Portachuelos, Upis Miraflores. Urbanización del Distrito de Bella Unión: Bella Unión, Fundo Incahuasi.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5601] ACARI.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 07 DE JULIO DE 2026:
@@ -1141,80 +727,80 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9666, 9667, 9673, 9671, 9672, 9610, 9620, 9660, 9662, 9611, 9613, 9615, 9618, 9617, 9616, 9814, 9815, 9693, 9696, 9612, 9614, 9661, 9669, 9807, 9810, 9811, 9816, 9817, 9813, 9812, 9852, 9857, 9842, 9843, 9844, 9839, 9840, 9841, 9860, 9872, 9878, 9879, 7989, 9883, 9884, 9885, 9952, 9966, 9959, 9973, 9970, 9971, 9794, 9997, 9571, 9587, 9364, 9363, 9372, 9391, 9397, 9393, 10250, 9969, 9413, 9416, 9445, 10201, 9670, 9619, 9967.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5907&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>16a74ce1f73ff45a8af4f122621da9816b3579672378031bb4ead11edc66608b</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5908</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cerro Colorado: Semi-Rural Pachacutec Grupo 15, Semi-Rural Pachacutec Grupo 25.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (podado de ramas de árboles cercanos a línea de media tensión).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : [707] COMERCIO.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 07 DE JULIO DE 2026:
@@ -1225,76 +811,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5908&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>bb54f1edf0d109046bd1a2c93b94fafd63a09ad8243dd17d36cb6c2202800b26</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5906</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Bella Unión, de Bella Unión</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Bella Unión: Fundo Santa Julia, Sector Coquito, Fundo Los Olivos, Fundo Santa Sofía, Empresa Minera Los Molles.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Platinos desde REC - 560307.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 07 DE JULIO DE 2026:
@@ -1305,80 +891,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9555, 9556, 9557, 9558, 9559, 9560, 9561, 7988.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5906&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>a3a738e58eef8f6e67fbd7b68be2fd65e8a02004db699995990bd0255808a52b</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5899</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: D1, D3, D4, D-4 Juan Velazco Alvarado, El Alto.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio e intermediación de postes, limpieza de aisladores y podado de ramas de árboles cercanos a la línea de media tensión).</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pedregal desde BC - 950215.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026:
@@ -1389,76 +975,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:04</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5899&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>cb54dcedab8c72292e80ba56ef9603e30dc30b94f047f351167592ed3e63c90d</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5895</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación tipo caseta.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1548.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026.
@@ -1468,76 +1054,76 @@
 Zonas afectadas: Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:01</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5895&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>1466c54750ce7fabcb21e4338b5debcaf43df6ea9d81d73803b77a0ec14f8397</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5896</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación tipo caseta.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4488</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026.
@@ -1547,76 +1133,76 @@
 Zonas afectadas: Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:01</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5896&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>0bd20768ba0d1b39101a6475ba8aa13c183555b28e651cf179155a8bcc99cb41</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5897</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Acari, de Acari</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliación Huaroto, Anexo Huaroto, Anexo La Joya, Humarote, Otapara, Upis Miraflores, Machaynioc, Sector Mallco.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Acarí desde REC - 560105.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026:
@@ -1627,80 +1213,80 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9587, 9814, 9445, 9815, 9693, 9966, 9816, 9817, 9812, 9813, 9883, 9970, 9794, 9997, 9391, 9416, 9884, 9885.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:02</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5897&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>61263ad9c945dd5e1f8be618a210112bcd5b76ca4a43be292f51a44e4075afae</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>5898</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Caraveli, Bella Unión, de Caraveli, de Bella Unión</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caraveli: Fundo Marceliano. Urbanizaciones del distrito de Bella Unión: Fundo San Isidro.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : Chala desde SL - 560264.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9832, 9678.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 08 DE JULIO DE 2026:
@@ -1711,80 +1297,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9832, 9678.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:03 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:03</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5898&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>07ae7144f41a36a6fc0994eb5d8c014c010c2c1a979d5c26c1b3ac151816a1c8</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>5901</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : Valle Blanco desde BC - 200577.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1795,80 +1381,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:05</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5901&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>eec06c9e26677b0d6945206bf673da94dc85413acbd5c05c83a93e08fd578b53</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>5902</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Lomas, de Lomas</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : Chala desde REC - 200157.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1879,80 +1465,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:06</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5902&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>3a3feafd29901401df7aed9c45921fcc59d37fb98ad972591efa5d166db4dfac</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>5900</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Cocachacra</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Cocachacra: El Fiscal.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de transformador y limpieza de aisladores).</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : Fiscal desde CC - 200243.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8222 8223 8512 8224 8513.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1963,76 +1549,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8222 8223 8512 8224 8513.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:04</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5900&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>74a48a1e37cadf8f292836fb6f4ea66db71a266cf5d7511741e0d825f76963f3</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>5903</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>José Luis Bustamante, Rivero, de José Luis Bustamante</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 160 KVA</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3245.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026.
@@ -2042,80 +1628,80 @@
 Zonas afectadas: Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:06</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5903&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>4113bd84b32737addd1cd18cfbb0c5599a9ce1250d3715761149a382910f9c51</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>5904</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Bella Unión, Jaqui, Yauca, de Bella Unión, de Jaqui, de Yauca</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5603] PLATINOS.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026:
@@ -2126,30 +1712,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:07</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5904&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>946b20909abaf56343358a2b8246ca27cc6f417123c11a409dccb58477cf575a</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P20"/>
+  <autoFilter ref="A1:P15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2190,7 +1776,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06 14:03:50</t>
+          <t>2026-07-07 12:40:06</t>
         </is>
       </c>
     </row>
@@ -2214,7 +1800,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -2226,7 +1812,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -2238,7 +1824,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2310,7 +1896,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -2337,7 +1923,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P15" headerRowCount="1">
-  <autoFilter ref="A1:P15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P14" headerRowCount="1">
+  <autoFilter ref="A1:P14"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, de Cayma</t>
+          <t>Acari, Bella Unión, de Acari, de Bella Unión</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanización Heresi, Calle Los Manzanos (Distrito de Cayma).</t>
+          <t>Urbanización del Distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliacion Huaroto, Anexo de Chocavento, Anexo El Molino, Anexo Huaroto, Anexo La Joya, Cruz Pata, Humarote, Machaynioc, Mallco, Otapara, Pueblo Nuevo de Acari, Pueblo Viejo de Acari, Santa Teresa, Sector Alto Chocavento, Sector Portachuelos, Upis Miraflores. Urbanización del Distrito de Bella Unión: Bella Unión, Fundo Incahuasi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de transformador a 200 KVA</t>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 4916.</t>
+          <t>Circuito : [5601] ACARI.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,85 +638,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 06 DE JULIO DE 2026.
-Circuito : SED 4916.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Cambio de transformador a 200 KVA
-Zonas afectadas: Urbanización Heresi, Calle Los Manzanos (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:08 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:08</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5905&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>e75fce447214779e1a768be17ed363c4a108ba1db4f36ad3dfafcf8607198ea5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5907</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Acari, Bella Unión, de Acari, de Bella Unión</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanización del Distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliacion Huaroto, Anexo de Chocavento, Anexo El Molino, Anexo Huaroto, Anexo La Joya, Cruz Pata, Humarote, Machaynioc, Mallco, Otapara, Pueblo Nuevo de Acari, Pueblo Viejo de Acari, Santa Teresa, Sector Alto Chocavento, Sector Portachuelos, Upis Miraflores. Urbanización del Distrito de Bella Unión: Bella Unión, Fundo Incahuasi.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [5601] ACARI.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 07 DE JULIO DE 2026:
@@ -727,80 +648,80 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9666, 9667, 9673, 9671, 9672, 9610, 9620, 9660, 9662, 9611, 9613, 9615, 9618, 9617, 9616, 9814, 9815, 9693, 9696, 9612, 9614, 9661, 9669, 9807, 9810, 9811, 9816, 9817, 9813, 9812, 9852, 9857, 9842, 9843, 9844, 9839, 9840, 9841, 9860, 9872, 9878, 9879, 7989, 9883, 9884, 9885, 9952, 9966, 9959, 9973, 9970, 9971, 9794, 9997, 9571, 9587, 9364, 9363, 9372, 9391, 9397, 9393, 10250, 9969, 9413, 9416, 9445, 10201, 9670, 9619, 9967.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5907&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>16a74ce1f73ff45a8af4f122621da9816b3579672378031bb4ead11edc66608b</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5908</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Cerro Colorado: Semi-Rural Pachacutec Grupo 15, Semi-Rural Pachacutec Grupo 25.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (podado de ramas de árboles cercanos a línea de media tensión).</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [707] COMERCIO.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 07 DE JULIO DE 2026:
@@ -811,76 +732,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5908&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>bb54f1edf0d109046bd1a2c93b94fafd63a09ad8243dd17d36cb6c2202800b26</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5906</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Bella Unión, de Bella Unión</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Bella Unión: Fundo Santa Julia, Sector Coquito, Fundo Los Olivos, Fundo Santa Sofía, Empresa Minera Los Molles.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Platinos desde REC - 560307.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 07 DE JULIO DE 2026:
@@ -891,80 +812,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9555, 9556, 9557, 9558, 9559, 9560, 9561, 7988.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5906&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>a3a738e58eef8f6e67fbd7b68be2fd65e8a02004db699995990bd0255808a52b</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5899</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: D1, D3, D4, D-4 Juan Velazco Alvarado, El Alto.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio e intermediación de postes, limpieza de aisladores y podado de ramas de árboles cercanos a la línea de media tensión).</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pedregal desde BC - 950215.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026:
@@ -975,76 +896,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:04</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5899&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>cb54dcedab8c72292e80ba56ef9603e30dc30b94f047f351167592ed3e63c90d</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5895</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación tipo caseta.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1548.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026.
@@ -1054,76 +975,76 @@
 Zonas afectadas: Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:01</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5895&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>1466c54750ce7fabcb21e4338b5debcaf43df6ea9d81d73803b77a0ec14f8397</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5896</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación tipo caseta.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4488</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026.
@@ -1133,76 +1054,76 @@
 Zonas afectadas: Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:01</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5896&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>0bd20768ba0d1b39101a6475ba8aa13c183555b28e651cf179155a8bcc99cb41</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5897</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Acari, de Acari</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliación Huaroto, Anexo Huaroto, Anexo La Joya, Humarote, Otapara, Upis Miraflores, Machaynioc, Sector Mallco.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Acarí desde REC - 560105.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 08 DE JULIO DE 2026:
@@ -1213,80 +1134,80 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9587, 9814, 9445, 9815, 9693, 9966, 9816, 9817, 9812, 9813, 9883, 9970, 9794, 9997, 9391, 9416, 9884, 9885.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:02</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5897&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>61263ad9c945dd5e1f8be618a210112bcd5b76ca4a43be292f51a44e4075afae</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5898</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Caraveli, Bella Unión, de Caraveli, de Bella Unión</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caraveli: Fundo Marceliano. Urbanizaciones del distrito de Bella Unión: Fundo San Isidro.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Chala desde SL - 560264.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>9832, 9678.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 08 DE JULIO DE 2026:
@@ -1297,80 +1218,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9832, 9678.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:03 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:03</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5898&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>07ae7144f41a36a6fc0994eb5d8c014c010c2c1a979d5c26c1b3ac151816a1c8</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>5901</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : Valle Blanco desde BC - 200577.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1381,80 +1302,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:05</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5901&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>eec06c9e26677b0d6945206bf673da94dc85413acbd5c05c83a93e08fd578b53</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>5902</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Lomas, de Lomas</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : Chala desde REC - 200157.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1465,80 +1386,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:06</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5902&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>3a3feafd29901401df7aed9c45921fcc59d37fb98ad972591efa5d166db4dfac</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>5900</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Cocachacra</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Cocachacra: El Fiscal.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de transformador y limpieza de aisladores).</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : Fiscal desde CC - 200243.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>8222 8223 8512 8224 8513.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1549,76 +1470,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8222 8223 8512 8224 8513.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:04</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5900&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>74a48a1e37cadf8f292836fb6f4ea66db71a266cf5d7511741e0d825f76963f3</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>5903</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>José Luis Bustamante, Rivero, de José Luis Bustamante</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 160 KVA</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3245.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026.
@@ -1628,80 +1549,80 @@
 Zonas afectadas: Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:06</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5903&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>4113bd84b32737addd1cd18cfbb0c5599a9ce1250d3715761149a382910f9c51</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>5904</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Bella Unión, Jaqui, Yauca, de Bella Unión, de Jaqui, de Yauca</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5603] PLATINOS.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026:
@@ -1712,30 +1633,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:07</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5904&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>946b20909abaf56343358a2b8246ca27cc6f417123c11a409dccb58477cf575a</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P15"/>
+  <autoFilter ref="A1:P14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1776,7 +1697,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07 12:40:06</t>
+          <t>2026-07-08 11:59:11</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1721,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1733,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1745,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1817,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1844,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Acari, Bella Unión, de Acari, de Bella Unión</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanización del Distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliacion Huaroto, Anexo de Chocavento, Anexo El Molino, Anexo Huaroto, Anexo La Joya, Cruz Pata, Humarote, Machaynioc, Mallco, Otapara, Pueblo Nuevo de Acari, Pueblo Viejo de Acari, Santa Teresa, Sector Alto Chocavento, Sector Portachuelos, Upis Miraflores. Urbanización del Distrito de Bella Unión: Bella Unión, Fundo Incahuasi.</t>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+          <t>Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [5601] ACARI.</t>
+          <t>Circuito : Valle Blanco desde BC - 200577.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,662 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 07 DE JULIO DE 2026:
-Circuito : [5601] ACARI.
-Hora : 07:30 a 10:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas Afectadas: Urbanización del Distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliacion Huaroto, Anexo de Chocavento, Anexo El Molino, Anexo Huaroto, Anexo La Joya, Cruz Pata, Humarote, Machaynioc, Mallco, Otapara, Pueblo Nuevo de Acari, Pueblo Viejo de Acari, Santa Teresa, Sector Alto Chocavento, Sector Portachuelos, Upis Miraflores. Urbanización del Distrito de Bella Unión: Bella Unión, Fundo Incahuasi.
-Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9666, 9667, 9673, 9671, 9672, 9610, 9620, 9660, 9662, 9611, 9613, 9615, 9618, 9617, 9616, 9814, 9815, 9693, 9696, 9612, 9614, 9661, 9669, 9807, 9810, 9811, 9816, 9817, 9813, 9812, 9852, 9857, 9842, 9843, 9844, 9839, 9840, 9841, 9860, 9872, 9878, 9879, 7989, 9883, 9884, 9885, 9952, 9966, 9959, 9973, 9970, 9971, 9794, 9997, 9571, 9587, 9364, 9363, 9372, 9391, 9397, 9393, 10250, 9969, 9413, 9416, 9445, 10201, 9670, 9619, 9967.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:09</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5907&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>16a74ce1f73ff45a8af4f122621da9816b3579672378031bb4ead11edc66608b</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5908</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Cerro Colorado: Semi-Rural Pachacutec Grupo 15, Semi-Rural Pachacutec Grupo 25.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (podado de ramas de árboles cercanos a línea de media tensión).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [707] COMERCIO.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 07 DE JULIO DE 2026:
-Circuito : [707] COMERCIO.
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (podado de ramas de árboles cercanos a línea de media tensión).
-Zonas afectadas: Urbanizaciones del Distrito de Cerro Colorado: Semi-Rural Pachacutec Grupo 15, Semi-Rural Pachacutec Grupo 25.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3972, 2806, 3381, 4009, 4035, 4198, 4204, 4232, 4317, 4945, 5045, 5010, 5511, 5694, 5695, 5795, 5808.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:10 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:10</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5908&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>bb54f1edf0d109046bd1a2c93b94fafd63a09ad8243dd17d36cb6c2202800b26</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5906</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Bella Unión, de Bella Unión</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Bella Unión: Fundo Santa Julia, Sector Coquito, Fundo Los Olivos, Fundo Santa Sofía, Empresa Minera Los Molles.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Platinos desde REC - 560307.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 07 DE JULIO DE 2026:
-Circuito : Platinos desde REC - 560307.
-Hora : 13:30 a 17:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Bella Unión: Fundo Santa Julia, Sector Coquito, Fundo Los Olivos, Fundo Santa Sofía, Empresa Minera Los Molles.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9555, 9556, 9557, 9558, 9559, 9560, 9561, 7988.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:09 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:09</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5906&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>a3a738e58eef8f6e67fbd7b68be2fd65e8a02004db699995990bd0255808a52b</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5899</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Majes: D1, D3, D4, D-4 Juan Velazco Alvarado, El Alto.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio e intermediación de postes, limpieza de aisladores y podado de ramas de árboles cercanos a la línea de media tensión).</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Pedregal desde BC - 950215.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 08 DE JULIO DE 2026:
-Circuito : Pedregal desde BC - 950215.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio e intermediación de postes, limpieza de aisladores y podado de ramas de árboles cercanos a la línea de media tensión).
-Zonas afectadas: Urbanizaciones del distrito de Majes: D1, D3, D4, D-4 Juan Velazco Alvarado, El Alto.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6095, 6227, 6094, 6247, 6097, 6096, 6291, 6292, 6118, 6117, 6958, 6116, 6115, 7825, 6108, 6107, 6106, 6086, 6099, 8812, 6098, 6103, 6113, 6092, 6091, 6089, 6090, 6105, 6104, 6102, 8673, 6101, 6112, 6628, 6111, 6110, 6109, 10231, 7677, 6093, 8655, 6406, 7681, 7682, 7683, 7684, 7918, 8905, 8672, 8666, 6119, 6100, 6114.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:04</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5899&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>cb54dcedab8c72292e80ba56ef9603e30dc30b94f047f351167592ed3e63c90d</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5895</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de subestación tipo caseta.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1548.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 08 DE JULIO DE 2026.
-Circuito : SED 1548.
-Hora : 07:30 a 11:30 Hrs.
-Motivo : Mantenimiento de subestación tipo caseta.
-Zonas afectadas: Parque industrial Rio Seco, Manzana C (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:01</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5895&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1466c54750ce7fabcb21e4338b5debcaf43df6ea9d81d73803b77a0ec14f8397</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de subestación tipo caseta.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4488</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 08 DE JULIO DE 2026.
-Circuito : SED 4488.
-Hora : 07:30 a 11:30 Hrs.
-Motivo : Mantenimiento de subestación tipo caseta.
-Zonas afectadas: Parque industrial Rio Seco APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:01 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:01</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5896&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0bd20768ba0d1b39101a6475ba8aa13c183555b28e651cf179155a8bcc99cb41</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5897</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Acari, de Acari</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliación Huaroto, Anexo Huaroto, Anexo La Joya, Humarote, Otapara, Upis Miraflores, Machaynioc, Sector Mallco.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Acarí desde REC - 560105.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 08 DE JULIO DE 2026:
-Circuito : Acarí desde REC - 560105.
-Hora : 07:30 a 12:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas Afectadas: Urbanizaciones del distrito de Acari: Amato, Ampliación El Molino, Anexo Ampliación Huaroto, Anexo Huaroto, Anexo La Joya, Humarote, Otapara, Upis Miraflores, Machaynioc, Sector Mallco.
-Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 9587, 9814, 9445, 9815, 9693, 9966, 9816, 9817, 9812, 9813, 9883, 9970, 9794, 9997, 9391, 9416, 9884, 9885.</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:02 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:02</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5897&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>61263ad9c945dd5e1f8be618a210112bcd5b76ca4a43be292f51a44e4075afae</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>5898</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Caraveli, Bella Unión, de Caraveli, de Bella Unión</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Caraveli: Fundo Marceliano. Urbanizaciones del distrito de Bella Unión: Fundo San Isidro.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Chala desde SL - 560264.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9832, 9678.</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 08 DE JULIO DE 2026:
-Circuito : Chala desde SL - 560264.
-Hora : 14:30 a 16:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Caraveli: Fundo Marceliano. Urbanizaciones del distrito de Bella Unión: Fundo San Isidro.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9832, 9678.</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:03 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:03</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5898&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>07ae7144f41a36a6fc0994eb5d8c014c010c2c1a979d5c26c1b3ac151816a1c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>5901</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Valle Blanco desde BC - 200577.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1302,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:05</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5901&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>eec06c9e26677b0d6945206bf673da94dc85413acbd5c05c83a93e08fd578b53</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5902</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Lomas, de Lomas</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Chala desde REC - 200157.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1386,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:06</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5902&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>3a3feafd29901401df7aed9c45921fcc59d37fb98ad972591efa5d166db4dfac</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5900</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cocachacra</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Cocachacra: El Fiscal.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de transformador y limpieza de aisladores).</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Fiscal desde CC - 200243.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8222 8223 8512 8224 8513.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 09 DE JULIO DE 2026:
@@ -1470,76 +820,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8222 8223 8512 8224 8513.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:04</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5900&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>74a48a1e37cadf8f292836fb6f4ea66db71a266cf5d7511741e0d825f76963f3</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5903</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>José Luis Bustamante, Rivero, de José Luis Bustamante</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 160 KVA</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3245.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026.
@@ -1549,80 +899,80 @@
 Zonas afectadas: Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:06</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5903&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>4113bd84b32737addd1cd18cfbb0c5599a9ce1250d3715761149a382910f9c51</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5904</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Bella Unión, Jaqui, Yauca, de Bella Unión, de Jaqui, de Yauca</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5603] PLATINOS.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026:
@@ -1633,25 +983,689 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 06/07/2026 8:07 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026 8:07</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5904&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>946b20909abaf56343358a2b8246ca27cc6f417123c11a409dccb58477cf575a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5909</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SET : [87] ORCOPAMPA.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+SET : [87] ORCOPAMPA.
+Hora : 06:00 a 11:00 Hrs.
+Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
+Zonas afectadas: Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 09/07/2026 8:37 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 8:37</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5909&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7d58f363bf64144821431759edcbb8f866d296a817760c894a06a4dfb2b6750c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>SET : [70] COTAHUASI.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+SET : [70] COTAHUASI.
+Hora : 06:00 a 11:00 Hrs.
+Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
+Zonas afectadas: Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 09/07/2026 8:38 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 8:38</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5910&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>758906cc21e11fc8945b62a938e206dbffbe255ed8f0b32a66a3fc7ca960a89c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>SET : [91] CALLALLI.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+SET : [91] CALLALLI.
+Hora : 06:00 a 11:00 Hrs.
+Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
+Zonas afectadas : Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 8:39</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5911&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>b801cd78fbaf1af4c2ba4ec99483767d7ba33ef79791d5c4af306df7f1432c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>SET : [93] SAN ANTONIO.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+SET : [93] SAN ANTONIO.
+Hora : 06:00 a 11:00 Hrs.
+Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
+Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 8:39</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5912&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>df96400307be0b6b48b6e1ea0f19096408e7898428c64d68f70190b7ba5c21f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Caylloma, de Caylloma</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+Hora : 06:00 a 11:00 Hrs.
+Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
+Zonas afectadas: Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 09/07/2026 8:40 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 8:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5913&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>952a86417f2929701403cebfbf01c802cef8bf172ef6f7dea7eef0d3906986cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5915</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>La Joya, Mollendo, Vitor, de La Joya, de Mollendo, de Vitor</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de La Joya: A.H. Santa Rosa, Asentamiento 6, Avpi Señales de Esperanza, Cristo Rey Zona 1, Cristo Rey Zona 2, Irrigación San Isidro, Progreso Km48, San José, Sector Gloria Irrigación La Joya, Sor Ana de Los Ángeles Monteagudo, Villa Esperanza San Jose II, Villa Hermosa, Cerrito Buena Vista, Cesar Garrido Lecca Soto, El Ramal, El Triunfo II, El Triunfo Zona "A", El Triunfo Zona "B", El Triunfo Zona "C", Héroes Anónimos, La Curva, La Florida, La Joya Antigua Sector 1, La Joya Antigua Sector 3, La Pradera del Lago, La Victoria, Las Casuarinas, Las Dunas, Leche Gloria, Los Girasoles de La Joya, Los Laureles, Los Médanos Zona A, Los Médanos Zona B, Los Milagros, Los Patriotas, Los Rosales, Marko Jara Schenone, Mirador La Victoria, Mirador La Victoria II, P.J. El Paraíso, Palca, primavera, San Francisco, Villa San Juan. Urbanizaciones del distrito de Mollendo: A.H. Villa Panamericana, Asentamiento 5, Asentamiento 7, Centro de Servicios Estrellita de Oro, Colonización La Joya - Asentamiento 5, La Cruz del Cerrito San Camilo, Nuevo Amanecer Irrigación San Camilo, Urbanizaciones del distrito de Vitor: Alto La Cano, Asoc de Viv Centro de Servicios San Isidro Valle Encantado, Casa Huerta - San Isidro, Esmeralda, Irrigación La Cano, Irrigación San Isidro, Joia Morena, La Cano II, Las Fincas, San Luis La Cano, 9 de febrero, Barrio Nuevo Zona "A", Cuarta Pampa, El Pacay, Irrigación Benito Lazo Sector L71-1A-3, La Caleta, Primera Pampa, San Luis, Segunda Pampa, Sotillo, Tercera Pampa, Valencia Chico, Valencia Grande, Virgen de Chapi.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Subestación y Pruebas a transformador de Potencia.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [26] REPARTICION, [27] EL CRUCE.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+Circuito : [26] REPARTICION, [27] EL CRUCE.
+Hora : 06:00 a 14:00 Hrs.
+Motivo : Mantenimiento de Subestación y Pruebas a transformador de Potencia.
+Zonas afectadas: Urbanizaciones del distrito de La Joya: A.H. Santa Rosa, Asentamiento 6, Avpi Señales de Esperanza, Cristo Rey Zona 1, Cristo Rey Zona 2, Irrigación San Isidro, Progreso Km48, San José, Sector Gloria Irrigación La Joya, Sor Ana de Los Ángeles Monteagudo, Villa Esperanza San Jose II, Villa Hermosa, Cerrito Buena Vista, Cesar Garrido Lecca Soto, El Ramal, El Triunfo II, El Triunfo Zona "A", El Triunfo Zona "B", El Triunfo Zona "C", Héroes Anónimos, La Curva, La Florida, La Joya Antigua Sector 1, La Joya Antigua Sector 3, La Pradera del Lago, La Victoria, Las Casuarinas, Las Dunas, Leche Gloria, Los Girasoles de La Joya, Los Laureles, Los Médanos Zona A, Los Médanos Zona B, Los Milagros, Los Patriotas, Los Rosales, Marko Jara Schenone, Mirador La Victoria, Mirador La Victoria II, P.J. El Paraíso, Palca, primavera, San Francisco, Villa San Juan.
+Urbanizaciones del distrito de Mollendo: A.H. Villa Panamericana, Asentamiento 5, Asentamiento 7, Centro de Servicios Estrellita de Oro, Colonización La Joya - Asentamiento 5, La Cruz del Cerrito San Camilo, Nuevo Amanecer Irrigación San Camilo,
+Urbanizaciones del distrito de Vitor: Alto La Cano, Asoc de Viv Centro de Servicios San Isidro Valle Encantado, Casa Huerta - San Isidro, Esmeralda, Irrigación La Cano, Irrigación San Isidro, Joia Morena, La Cano II, Las Fincas, San Luis La Cano, 9 de febrero, Barrio Nuevo Zona "A", Cuarta Pampa, El Pacay, Irrigación Benito Lazo Sector L71-1A-3, La Caleta, Primera Pampa, San Luis, Segunda Pampa, Sotillo, Tercera Pampa, Valencia Chico, Valencia Grande, Virgen de Chapi.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 8:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5915&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>f98fc78cea30b054d29f43809207d2a62529bda171a96bcaead4455dba69710b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, Yanahuara, de Arequipa, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones de distrito de Arequipa: Club Internacional. Urbanizaciones del distrito de Yanahuara: Quinta Santa Luiza, Yanahuara.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Inserción de subestación de distribución y otros mantenimientos de redes en media tensión.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [207] SAGA.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+Circuito : [207] SAGA.
+Hora : 06:00 a 13:00 Hrs.
+Motivo : Inserción de subestación de distribución y otros mantenimientos de redes en media tensión.
+Zonas afectadas: Urbanizaciones de distrito de Arequipa: Club Internacional. Urbanizaciones del distrito de Yanahuara: Quinta Santa Luiza, Yanahuara.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 09/07/2026 18:24 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 18:24</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5916&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>e65c35bf2bf7c7a277d21b077d30d1dcae0354a3c58d873a454d7a3dce2b4cff</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5914</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Islay, Mollendo, de Islay, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio e instalación de postes, cambio de armado, cambio de conductor a 120 mm2).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [3502] TISUR.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 12 DE JULIO DE 2026:
+Circuito : [3502] TISUR.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio e instalación de postes, cambio de armado, cambio de conductor a 120 mm2).
+Zonas Afectadas: Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.
+Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>el 06/07/2026 8:07 por Cuenta del sistema</t>
+          <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026 8:07</t>
+          <t>09/07/2026 8:41</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5904&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5914&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>946b20909abaf56343358a2b8246ca27cc6f417123c11a409dccb58477cf575a</t>
+          <t>fcce4dfb3762f9f20e86e81dbf35f4a3b921e74fd0ecbf90e824f95810c8d6ba</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1711,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08 11:59:11</t>
+          <t>2026-07-10 12:38:18</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1735,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1747,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1759,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1807,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1819,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P14" headerRowCount="1">
-  <autoFilter ref="A1:P14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
+  <autoFilter ref="A1:P11"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>José Luis Bustamante, Rivero, de José Luis Bustamante</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.</t>
+          <t>Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
+          <t>Cambio de transformador a 160 KVA</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Valle Blanco desde BC - 200577.</t>
+          <t>Circuito : SED 3245.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,260 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 09 DE JULIO DE 2026:
-Circuito : Valle Blanco desde BC - 200577.
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Subsanación de deficiencias de acuerdo al Proc. 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Semi Rural Pachacutec Grupo 10, Grupo 16, Grupo 18, Grupo 19.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1123, 1366, 1626, 2346, 2979, 3371, 3697, 4484, 4656, 5610, 5732, 5936.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:05 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:05</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5901&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>eec06c9e26677b0d6945206bf673da94dc85413acbd5c05c83a93e08fd578b53</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5902</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Lomas, de Lomas</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Chala desde REC - 200157.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 09 DE JULIO DE 2026:
-Circuito : Chala desde REC - 200157.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Lomas: Costa Azul, Los Jazmines, Puerto Lomas.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9655, 9882, 9654, 9626, 9349, 9827, 9847.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:06</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5902&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>3a3feafd29901401df7aed9c45921fcc59d37fb98ad972591efa5d166db4dfac</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5900</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cocachacra</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito Cocachacra: El Fiscal.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de transformador y limpieza de aisladores).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Fiscal desde CC - 200243.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8222 8223 8512 8224 8513.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 09 DE JULIO DE 2026:
-Circuito : Fiscal desde CC - 200243.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de transformador y limpieza de aisladores).
-Zonas afectadas: Urbanizaciones del distrito Cocachacra: El Fiscal.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8222 8223 8512 8224 8513.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:04 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:04</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5900&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>74a48a1e37cadf8f292836fb6f4ea66db71a266cf5d7511741e0d825f76963f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5903</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>José Luis Bustamante, Rivero, de José Luis Bustamante</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 160 KVA</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3245.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026.
@@ -899,80 +647,80 @@
 Zonas afectadas: Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:06</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5903&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>4113bd84b32737addd1cd18cfbb0c5599a9ce1250d3715761149a382910f9c51</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5904</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Bella Unión, Jaqui, Yauca, de Bella Unión, de Jaqui, de Yauca</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5603] PLATINOS.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 10 DE JULIO DE 2026:
@@ -983,80 +731,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 06/07/2026 8:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06/07/2026 8:07</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5904&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>946b20909abaf56343358a2b8246ca27cc6f417123c11a409dccb58477cf575a</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5909</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SET : [87] ORCOPAMPA.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1067,80 +815,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:37</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5909&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>7d58f363bf64144821431759edcbb8f866d296a817760c894a06a4dfb2b6750c</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5910</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1151,80 +899,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:38</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5910&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>758906cc21e11fc8945b62a938e206dbffbe255ed8f0b32a66a3fc7ca960a89c</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5911</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SET : [91] CALLALLI.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1235,80 +983,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:39</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5911&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>b801cd78fbaf1af4c2ba4ec99483767d7ba33ef79791d5c4af306df7f1432c3d</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5912</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>SET : [93] SAN ANTONIO.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1319,76 +1067,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:39</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5912&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>df96400307be0b6b48b6e1ea0f19096408e7898428c64d68f70190b7ba5c21f4</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5913</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Caylloma, de Caylloma</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1397,80 +1145,80 @@
 Zonas afectadas: Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:40</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5913&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>952a86417f2929701403cebfbf01c802cef8bf172ef6f7dea7eef0d3906986cd</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5915</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>La Joya, Mollendo, Vitor, de La Joya, de Mollendo, de Vitor</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: A.H. Santa Rosa, Asentamiento 6, Avpi Señales de Esperanza, Cristo Rey Zona 1, Cristo Rey Zona 2, Irrigación San Isidro, Progreso Km48, San José, Sector Gloria Irrigación La Joya, Sor Ana de Los Ángeles Monteagudo, Villa Esperanza San Jose II, Villa Hermosa, Cerrito Buena Vista, Cesar Garrido Lecca Soto, El Ramal, El Triunfo II, El Triunfo Zona "A", El Triunfo Zona "B", El Triunfo Zona "C", Héroes Anónimos, La Curva, La Florida, La Joya Antigua Sector 1, La Joya Antigua Sector 3, La Pradera del Lago, La Victoria, Las Casuarinas, Las Dunas, Leche Gloria, Los Girasoles de La Joya, Los Laureles, Los Médanos Zona A, Los Médanos Zona B, Los Milagros, Los Patriotas, Los Rosales, Marko Jara Schenone, Mirador La Victoria, Mirador La Victoria II, P.J. El Paraíso, Palca, primavera, San Francisco, Villa San Juan. Urbanizaciones del distrito de Mollendo: A.H. Villa Panamericana, Asentamiento 5, Asentamiento 7, Centro de Servicios Estrellita de Oro, Colonización La Joya - Asentamiento 5, La Cruz del Cerrito San Camilo, Nuevo Amanecer Irrigación San Camilo, Urbanizaciones del distrito de Vitor: Alto La Cano, Asoc de Viv Centro de Servicios San Isidro Valle Encantado, Casa Huerta - San Isidro, Esmeralda, Irrigación La Cano, Irrigación San Isidro, Joia Morena, La Cano II, Las Fincas, San Luis La Cano, 9 de febrero, Barrio Nuevo Zona "A", Cuarta Pampa, El Pacay, Irrigación Benito Lazo Sector L71-1A-3, La Caleta, Primera Pampa, San Luis, Segunda Pampa, Sotillo, Tercera Pampa, Valencia Chico, Valencia Grande, Virgen de Chapi.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de Subestación y Pruebas a transformador de Potencia.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : [26] REPARTICION, [27] EL CRUCE.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1483,80 +1231,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:41</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5915&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>f98fc78cea30b054d29f43809207d2a62529bda171a96bcaead4455dba69710b</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>5916</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Arequipa, Yanahuara, de Arequipa, de Yanahuara</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de distrito de Arequipa: Club Internacional. Urbanizaciones del distrito de Yanahuara: Quinta Santa Luiza, Yanahuara.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Inserción de subestación de distribución y otros mantenimientos de redes en media tensión.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : [207] SAGA.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1567,76 +1315,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 18:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 18:24</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5916&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>e65c35bf2bf7c7a277d21b077d30d1dcae0354a3c58d873a454d7a3dce2b4cff</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>5914</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Islay, Mollendo, de Islay, de Mollendo</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio e instalación de postes, cambio de armado, cambio de conductor a 120 mm2).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : [3502] TISUR.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1647,30 +1395,30 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:41</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5914&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>fcce4dfb3762f9f20e86e81dbf35f4a3b921e74fd0ecbf90e824f95810c8d6ba</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1711,7 +1459,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10 12:38:18</t>
+          <t>2026-07-11 11:27:09</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1483,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1495,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1507,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1579,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1606,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
-  <autoFilter ref="A1:P11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>José Luis Bustamante, Rivero, de José Luis Bustamante</t>
+          <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
+          <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de transformador a 160 KVA</t>
+          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 3245.</t>
+          <t>SET : [87] ORCOPAMPA.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,175 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 10 DE JULIO DE 2026.
-Circuito : SED 3245.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Cambio de transformador a 160 KVA
-Zonas afectadas: Bancarios, Calle Los Cedros, Calle Los Pinos (Distrito de José Luis Bustamante y Rivero).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:06</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5903&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>4113bd84b32737addd1cd18cfbb0c5599a9ce1250d3715761149a382910f9c51</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Bella Unión, Jaqui, Yauca, de Bella Unión, de Jaqui, de Yauca</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [5603] PLATINOS.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 10 DE JULIO DE 2026:
-Circuito : [5603] PLATINOS.
-Hora : 07:30 a 13:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Bella Unión: Fundo La Pampita, Lateral 1, Lateral 2, Sector San Pablo. Urbanizaciones del distrito de Jaqui: Jaqui, Lampilla, Mochica, Mochica Baja, Patahuasi. Urbanizaciones del distrito de Yauca: Mochica Baja, Villa El Sol, Yauca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9675, 9674, 9676, 9677, 9656, 9634, 9633, 9632, 9631, 9628, 9629, 9630, 9687, 9824, 9826, 9829, 9831, 9835, 9838, 9853, 9854, 9855, 9858, 9871, 9877, 9881, 7988, 9891, 9892, 9893, 9890, 9894, 9954, 9956, 9955, 9957, 9961, 9962, 9964, 9992, 9555, 9560, 9561, 9559, 9556, 9557, 9558, 9570, 9965, 9589, 9394, 9389, 9399, 9410, 9418, 10148, 9887.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 06/07/2026 8:07 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>06/07/2026 8:07</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5904&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>946b20909abaf56343358a2b8246ca27cc6f417123c11a409dccb58477cf575a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5909</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SET : [87] ORCOPAMPA.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -815,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:37 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:37</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5909&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>7d58f363bf64144821431759edcbb8f866d296a817760c894a06a4dfb2b6750c</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5910</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -899,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:38 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:38</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5910&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>758906cc21e11fc8945b62a938e206dbffbe255ed8f0b32a66a3fc7ca960a89c</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5911</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SET : [91] CALLALLI.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -983,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:39</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5911&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>b801cd78fbaf1af4c2ba4ec99483767d7ba33ef79791d5c4af306df7f1432c3d</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5912</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SET : [93] SAN ANTONIO.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1067,76 +904,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:39</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5912&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>df96400307be0b6b48b6e1ea0f19096408e7898428c64d68f70190b7ba5c21f4</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5913</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Caylloma, de Caylloma</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1145,80 +982,80 @@
 Zonas afectadas: Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:40 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:40</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5913&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>952a86417f2929701403cebfbf01c802cef8bf172ef6f7dea7eef0d3906986cd</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5915</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>La Joya, Mollendo, Vitor, de La Joya, de Mollendo, de Vitor</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de La Joya: A.H. Santa Rosa, Asentamiento 6, Avpi Señales de Esperanza, Cristo Rey Zona 1, Cristo Rey Zona 2, Irrigación San Isidro, Progreso Km48, San José, Sector Gloria Irrigación La Joya, Sor Ana de Los Ángeles Monteagudo, Villa Esperanza San Jose II, Villa Hermosa, Cerrito Buena Vista, Cesar Garrido Lecca Soto, El Ramal, El Triunfo II, El Triunfo Zona "A", El Triunfo Zona "B", El Triunfo Zona "C", Héroes Anónimos, La Curva, La Florida, La Joya Antigua Sector 1, La Joya Antigua Sector 3, La Pradera del Lago, La Victoria, Las Casuarinas, Las Dunas, Leche Gloria, Los Girasoles de La Joya, Los Laureles, Los Médanos Zona A, Los Médanos Zona B, Los Milagros, Los Patriotas, Los Rosales, Marko Jara Schenone, Mirador La Victoria, Mirador La Victoria II, P.J. El Paraíso, Palca, primavera, San Francisco, Villa San Juan. Urbanizaciones del distrito de Mollendo: A.H. Villa Panamericana, Asentamiento 5, Asentamiento 7, Centro de Servicios Estrellita de Oro, Colonización La Joya - Asentamiento 5, La Cruz del Cerrito San Camilo, Nuevo Amanecer Irrigación San Camilo, Urbanizaciones del distrito de Vitor: Alto La Cano, Asoc de Viv Centro de Servicios San Isidro Valle Encantado, Casa Huerta - San Isidro, Esmeralda, Irrigación La Cano, Irrigación San Isidro, Joia Morena, La Cano II, Las Fincas, San Luis La Cano, 9 de febrero, Barrio Nuevo Zona "A", Cuarta Pampa, El Pacay, Irrigación Benito Lazo Sector L71-1A-3, La Caleta, Primera Pampa, San Luis, Segunda Pampa, Sotillo, Tercera Pampa, Valencia Chico, Valencia Grande, Virgen de Chapi.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de Subestación y Pruebas a transformador de Potencia.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : [26] REPARTICION, [27] EL CRUCE.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1231,80 +1068,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:41</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5915&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>f98fc78cea30b054d29f43809207d2a62529bda171a96bcaead4455dba69710b</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5916</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Arequipa, Yanahuara, de Arequipa, de Yanahuara</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de distrito de Arequipa: Club Internacional. Urbanizaciones del distrito de Yanahuara: Quinta Santa Luiza, Yanahuara.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Inserción de subestación de distribución y otros mantenimientos de redes en media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : [207] SAGA.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1315,76 +1152,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 18:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 18:24</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5916&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>e65c35bf2bf7c7a277d21b077d30d1dcae0354a3c58d873a454d7a3dce2b4cff</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5914</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Islay, Mollendo, de Islay, de Mollendo</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio e instalación de postes, cambio de armado, cambio de conductor a 120 mm2).</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : [3502] TISUR.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 12 DE JULIO DE 2026:
@@ -1395,30 +1232,30 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>09/07/2026 8:41</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5914&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>fcce4dfb3762f9f20e86e81dbf35f4a3b921e74fd0ecbf90e824f95810c8d6ba</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1459,7 +1296,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11 11:27:09</t>
+          <t>2026-07-12 11:33:36</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1320,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1332,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1344,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1416,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1443,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 11:33:36</t>
+          <t>2026-07-13 12:56:03</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P17" headerRowCount="1">
+  <autoFilter ref="A1:P17"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayarani, Chilcaymarca, Orcopampa, de Cayarani, de Chilcaymarca, de Orcopampa</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.</t>
+          <t>Cerro viejo, Calle comandante Canga, Calle Inca, Calle Arequipa, Calle Intendente Salamanca, Calle General Moran, Psj. Lozada (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+          <t>Cambio de posición de conmutador.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SET : [87] ORCOPAMPA.</t>
+          <t>Circuito : SED 1241.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,83 +636,78 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-SET : [87] ORCOPAMPA.
-Hora : 06:00 a 11:00 Hrs.
-Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
-Zonas afectadas: Urbanizaciones del distrito de Cayarani: Cucho Rancho, Palcuyo, Sancomarca, Umachulcco. Urbanizaciones del distrito de Chilcaymarca: Chilcaymarca, Huilluco. Urbanizaciones del distrito de Orcopampa: Allhuire, Cercado, Condorhuayco, Huancarama, Huinpilca, La Calera, La Laguna, Las Tejas, Lontojoya, Misahuanca, Misapuquio, Panahua, Piscina Huancarama, Rumihuasi, Rupaspucro, San Gregorio, San Lazaro, Sarpane, Sausa, Tintaymarca, Vista Alegre, Zarpane.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7447, 7445, 7446, 7450, 7442, 7441, 7449, 7448, 7443, 7440, 7456, 7464, 7461, 7465, 7455, 7457, 7458, 7454, 7460, 7459, 7462, 7467, 7468, 7469, 7470, 7474, 7352, 7353, 7354, 7359, 7704, 7961, 7962, 7963, 7960, 7764, 7760, 7759, 7758, 7756, 7763, 7762, 7761, 7791, 7792, 7757, 7968, 8793, 8792, 8787, 8794, 8790, 8786, 8788, 8789, 8791, 10189, 7453.</t>
+LUNES, 13 DE JULIO DE 2026.
+Circuito : SED 1241.
+Hora : 08:00 a 08:30 Hrs.
+Motivo : Cambio de posición de conmutador.
+Zonas afectadas: Cerro viejo, Calle comandante Canga, Calle Inca, Calle Arequipa, Calle Intendente Salamanca, Calle General Moran, Psj. Lozada (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 8:37 por Cuenta del sistema</t>
+          <t>el 13/07/2026 8:03 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 8:37</t>
+          <t>13/07/2026 8:03</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5909&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5922&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>7d58f363bf64144821431759edcbb8f866d296a817760c894a06a4dfb2b6750c</t>
+          <t>78dd6d58f577469f88dcb67a4eecb2857db477551ba246e3048e92befcc499b0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="70" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de Puyca</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
+          <t>Asociación Casa Granja Villa Arapa, Peruarbo Zona II, Zona III (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+          <t>Mantenimientos de redes en media tensión.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SET : [70] COTAHUASI.</t>
+          <t>Circuito : Autopista desde EMT 17567.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -722,81 +717,81 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
+          <t>4233, 5408.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-SET : [70] COTAHUASI.
-Hora : 06:00 a 11:00 Hrs.
-Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
-Zonas afectadas: Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
+LUNES, 13 DE JULIO DE 2026.
+Circuito : Autopista desde EMT 17567.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Mantenimientos de redes en media tensión.
+Zonas afectadas: Asociación Casa Granja Villa Arapa, Peruarbo Zona II, Zona III (Distrito de Cerro Colorado).
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4233, 5408.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 8:38 por Cuenta del sistema</t>
+          <t>el 13/07/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 8:38</t>
+          <t>13/07/2026 8:06</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5910&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5927&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>758906cc21e11fc8945b62a938e206dbffbe255ed8f0b32a66a3fc7ca960a89c</t>
+          <t>7f73a60178252127f05fbcfd0b2aa8c3c59e41033307bd6271fbaf329dbf26cd</t>
         </is>
       </c>
     </row>
     <row r="4" ht="70" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Achoma, Cabanaconde, Callalli, Chivay, Choco, Coporaque, Huambo, Ichupampa, Lari, Maca, Madrigal, San Antonio de Chuca, Sibayo, Tapay, Tisco, Tuti, Yanque, de Achoma, de Cabanaconde, de Callalli, de Chivay, de Choco, de Coporaque, de Huambo, de Ichupampa, de Lari, de Maca, de Madrigal, de San Antonio de Chuca, de Sibayo, de Tapay, de Tisco, de Tuti, de Yanque</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.</t>
+          <t>Av. José Carlos Mariátegui, Av. Manco Cápac, Calle General Ollantay, Calle 30 de Agosto, Calle 28 de Julio, Calle Chiclayo, Calle Unión (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+          <t>Cambio de posición de conmutador.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SET : [91] CALLALLI.</t>
+          <t>Circuito : SED 2845.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -804,58 +799,53 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-SET : [91] CALLALLI.
-Hora : 06:00 a 11:00 Hrs.
-Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
-Zonas afectadas : Urbanizaciones del distrito de Achoma: Achoma. Urbanizaciones del distrito de Cabanaconde: Cabanaconde, Cerro El Mirador, Joyas, Media Luna, Pinchollo, Pirachapampa, Sangalle, Villa El Colca. Urbanizaciones del distrito de Callalli: Callalli, Pulpera, Santa Barbara. Urbanizaciones del distrito de Chivay: Canacota, Chivay, Guillermo Manrique Guzman, Mirador del Colca. Urbanizaciones del distrito de Choco: Choco, Gilla, Humahuato, Llanca, Llatica, Miña, Pachauma, Pallca, Sihuincha, Soro, Ucuchachas. Urbanizaciones del distrito de Coporaque: Coporaque, Nido de Halcon, Sol de Sacsayhuaman. Urbanizaciones del distrito de Huambo: Chinini, Huambo. Urbanizaciones del distrito de Ichupampa: Ichupampa. Urbanizaciones del distrito de Lari: Lari. Urbanizaciones del distrito de Maca: Maca. Urbanizaciones del distrito de Madrigal: Madrigal. Urbanizaciones del distrito de San Antonio de Chuca: Colca, Estación Pillones, Imata. Urbanizaciones del distrito de Sibayo: Sibayo. Urbanizaciones del distrito de Tapay: Anexo El Fure, Anexo San Juan de Chuccho, Barrio Santiago, Belen, Cosñirhua, Malata, Paclla, Puquio, San Juan de Chuccho, Tapay, Tocallo, Turuña. Urbanizaciones del distrito de Tisco: Cotacota, Tisco. Urbanizaciones del distrito de Tuti: Tuti. Urbanizaciones del distrito de Yanque: Chalhuanca, Yanque.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7546, 7540, 7534, 7549, 7523, 7539, 7508, 7513, 7533, 7532, 7524, 7525, 7522, 7521, 7518, 7519, 7511, 7509, 7512, 7510, 7507, 7506, 7542, 7541, 7548, 7560, 7559, 7561, 7579, 7551, 7552, 7553, 7562, 7569, 7570, 7566, 7567, 7558, 7573, 7574, 7575, 7572, 7571, 7563, 7564, 7577, 7576, 7568, 7550, 7580, 7581, 7582, 7557, 7555, 7547, 7585, 7543, 7556, 7515, 7514, 7526, 7537, 7535, 7536, 7531, 7529, 7527, 7517, 7516, 7503, 7545, 7520, 7544, 7584, 7587, 7502, 7501, 7504, 7505, 7590, 7592, 7591, 7593, 7595, 7597, 7598, 7599, 7589, 7600, 7583, 7601, 7613, 7642, 7652, 7662, 7626, 7686, 7673, 7674, 7711, 7818, 7827, 7702, 7828, 7829, 7833, 7832, 7831, 7834, 7869, 7879, 7874, 7875, 7876, 7877, 7878, 7881, 7880, 7882, 7883, 7884, 7885, 7886, 7835, 7889, 7999, 9796, 9789, 9579, 9580, 7890, 9581, 9582, 9578, 9374, 9375, 9788, 9376, 9377, 9396, 9430, 8795, 7554, 7530, 7578, 7565, 7538, 7612, 7666, 10126, 10339.</t>
+LUNES, 13 DE JULIO DE 2026.
+Circuito : SED 2845.
+Hora : 09:30 a 10:00 Hrs.
+Motivo : Cambio de posición de conmutador.
+Zonas afectadas: Av. José Carlos Mariátegui, Av. Manco Cápac, Calle General Ollantay, Calle 30 de Agosto, Calle 28 de Julio, Calle Chiclayo, Calle Unión (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
+          <t>el 13/07/2026 8:03 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 8:39</t>
+          <t>13/07/2026 8:03</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5911&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5923&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>b801cd78fbaf1af4c2ba4ec99483767d7ba33ef79791d5c4af306df7f1432c3d</t>
+          <t>2a8561e2e5446c89e738db3b1c45e13972727e99513a458a3cbc769d10d4972e</t>
         </is>
       </c>
     </row>
     <row r="5" ht="70" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -865,22 +855,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
+          <t>Av. Alto Cayma, Calle José Santos Chocano, Calle José Abelardo Quiñones (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+          <t>Cambio de posición de conmutador.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SET : [93] SAN ANTONIO.</t>
+          <t>Circuito : SED 1902.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -888,83 +878,78 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
-        </is>
-      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-SET : [93] SAN ANTONIO.
-Hora : 06:00 a 11:00 Hrs.
-Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
-Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+LUNES, 13 DE JULIO DE 2026.
+Circuito : SED 1902.
+Hora : 10:30 a 11:00 Hrs.
+Motivo : Cambio de posición de conmutador.
+Zonas afectadas: Av. Alto Cayma, Calle José Santos Chocano, Calle José Abelardo Quiñones (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 8:39 por Cuenta del sistema</t>
+          <t>el 13/07/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 8:39</t>
+          <t>13/07/2026 8:04</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5912&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5924&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>df96400307be0b6b48b6e1ea0f19096408e7898428c64d68f70190b7ba5c21f4</t>
+          <t>53ee606488201bb1b361d691940735a46c458dc522cb31b17bb32987b640208c</t>
         </is>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Caylloma, de Caylloma</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
+          <t>Calle tres volcanes, Jr. Víctor Andrés Belaunde, Jr. Tacna, Jr. 7 de junio, Jr. Misti, Jr. Abancay, Jr. Progreso, Jr. Simón Bolívar, Jr. Independencia, Jr. Zela, Av. Arequipa (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+          <t>Cambio de posición de conmutador.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020</t>
+          <t>Circuito : SED 1661.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -976,73 +961,74 @@
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-Hora : 06:00 a 11:00 Hrs.
-Motivo : Afectado por corte programado de REP ‘Red de Energía del Perú’ para Mantenimiento Correctivo, reposición del SA-4259 fase “R” L-1020
-Zonas afectadas: Urbanizaciones del distrito de Caylloma: MUNICIPALIDAD DISTRITAL DE CAYLLOMA (SUMINISTRO EN BLOQUE).</t>
+LUNES, 13 DE JULIO DE 2026.
+Circuito : SED 1661.
+Hora : 11:30 a 12:00 Hrs.
+Motivo : Cambio de posición de conmutador.
+Zonas afectadas: Calle tres volcanes, Jr. Víctor Andrés Belaunde, Jr. Tacna, Jr. 7 de junio, Jr. Misti, Jr. Abancay, Jr. Progreso, Jr. Simón Bolívar, Jr. Independencia, Jr. Zela, Av. Arequipa (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 8:40 por Cuenta del sistema</t>
+          <t>el 13/07/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 8:40</t>
+          <t>13/07/2026 8:05</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5913&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5925&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>952a86417f2929701403cebfbf01c802cef8bf172ef6f7dea7eef0d3906986cd</t>
+          <t>1a1f26c0e73f288abca8e9ba622dd79772d0609b174edef444a69a3d1aa2b65a</t>
         </is>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>La Joya, Mollendo, Vitor, de La Joya, de Mollendo, de Vitor</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de La Joya: A.H. Santa Rosa, Asentamiento 6, Avpi Señales de Esperanza, Cristo Rey Zona 1, Cristo Rey Zona 2, Irrigación San Isidro, Progreso Km48, San José, Sector Gloria Irrigación La Joya, Sor Ana de Los Ángeles Monteagudo, Villa Esperanza San Jose II, Villa Hermosa, Cerrito Buena Vista, Cesar Garrido Lecca Soto, El Ramal, El Triunfo II, El Triunfo Zona "A", El Triunfo Zona "B", El Triunfo Zona "C", Héroes Anónimos, La Curva, La Florida, La Joya Antigua Sector 1, La Joya Antigua Sector 3, La Pradera del Lago, La Victoria, Las Casuarinas, Las Dunas, Leche Gloria, Los Girasoles de La Joya, Los Laureles, Los Médanos Zona A, Los Médanos Zona B, Los Milagros, Los Patriotas, Los Rosales, Marko Jara Schenone, Mirador La Victoria, Mirador La Victoria II, P.J. El Paraíso, Palca, primavera, San Francisco, Villa San Juan. Urbanizaciones del distrito de Mollendo: A.H. Villa Panamericana, Asentamiento 5, Asentamiento 7, Centro de Servicios Estrellita de Oro, Colonización La Joya - Asentamiento 5, La Cruz del Cerrito San Camilo, Nuevo Amanecer Irrigación San Camilo, Urbanizaciones del distrito de Vitor: Alto La Cano, Asoc de Viv Centro de Servicios San Isidro Valle Encantado, Casa Huerta - San Isidro, Esmeralda, Irrigación La Cano, Irrigación San Isidro, Joia Morena, La Cano II, Las Fincas, San Luis La Cano, 9 de febrero, Barrio Nuevo Zona "A", Cuarta Pampa, El Pacay, Irrigación Benito Lazo Sector L71-1A-3, La Caleta, Primera Pampa, San Luis, Segunda Pampa, Sotillo, Tercera Pampa, Valencia Chico, Valencia Grande, Virgen de Chapi.</t>
+          <t>Calle Prolongación Amazonas, Av. Amazonas, Calle Garcilaso de la Vega, Calle Copacabana, Jr. Begazo, Psj. Reynoso, Psj. Begazo, Psj. Trujillo, Calle Zoraida Montes Revilla (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de Subestación y Pruebas a transformador de Potencia.</t>
+          <t>Cambio de posición de conmutador.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [26] REPARTICION, [27] EL CRUCE.</t>
+          <t>Circuito : SED 1735.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1050,85 +1036,78 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
-        </is>
-      </c>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-Circuito : [26] REPARTICION, [27] EL CRUCE.
-Hora : 06:00 a 14:00 Hrs.
-Motivo : Mantenimiento de Subestación y Pruebas a transformador de Potencia.
-Zonas afectadas: Urbanizaciones del distrito de La Joya: A.H. Santa Rosa, Asentamiento 6, Avpi Señales de Esperanza, Cristo Rey Zona 1, Cristo Rey Zona 2, Irrigación San Isidro, Progreso Km48, San José, Sector Gloria Irrigación La Joya, Sor Ana de Los Ángeles Monteagudo, Villa Esperanza San Jose II, Villa Hermosa, Cerrito Buena Vista, Cesar Garrido Lecca Soto, El Ramal, El Triunfo II, El Triunfo Zona "A", El Triunfo Zona "B", El Triunfo Zona "C", Héroes Anónimos, La Curva, La Florida, La Joya Antigua Sector 1, La Joya Antigua Sector 3, La Pradera del Lago, La Victoria, Las Casuarinas, Las Dunas, Leche Gloria, Los Girasoles de La Joya, Los Laureles, Los Médanos Zona A, Los Médanos Zona B, Los Milagros, Los Patriotas, Los Rosales, Marko Jara Schenone, Mirador La Victoria, Mirador La Victoria II, P.J. El Paraíso, Palca, primavera, San Francisco, Villa San Juan.
-Urbanizaciones del distrito de Mollendo: A.H. Villa Panamericana, Asentamiento 5, Asentamiento 7, Centro de Servicios Estrellita de Oro, Colonización La Joya - Asentamiento 5, La Cruz del Cerrito San Camilo, Nuevo Amanecer Irrigación San Camilo,
-Urbanizaciones del distrito de Vitor: Alto La Cano, Asoc de Viv Centro de Servicios San Isidro Valle Encantado, Casa Huerta - San Isidro, Esmeralda, Irrigación La Cano, Irrigación San Isidro, Joia Morena, La Cano II, Las Fincas, San Luis La Cano, 9 de febrero, Barrio Nuevo Zona "A", Cuarta Pampa, El Pacay, Irrigación Benito Lazo Sector L71-1A-3, La Caleta, Primera Pampa, San Luis, Segunda Pampa, Sotillo, Tercera Pampa, Valencia Chico, Valencia Grande, Virgen de Chapi.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6790, 6795, 6794, 6793, 6930, 6927, 6872, 6873, 6874, 6863, 6880, 6866, 6876, 6871, 6865, 6862, 6870, 6869, 6875, 6878, 6879, 6868, 6864, 6877, 6936, 6857, 6858, 6861, 6928, 6796, 6818, 6931, 6910, 6913, 6907, 6922, 6917, 6916, 6912, 6911, 6903, 6904, 6797, 6798, 6867, 6860, 6859, 6943, 6938, 6929, 6919, 6926, 6906, 6918, 6914, 6915, 6902, 6909, 6908, 6900, 6901, 6799, 6699, 6920, 6937, 6855, 6887, 6848, 6898, 6984, 6825, 6987, 6992, 6993, 6952, 6630, 6650, 6651, 6652, 6653, 6654, 6655, 6656, 6657, 6658, 6659, 6642, 6644, 6643, 6666, 6667, 6665, 6669, 6664, 6668, 6925, 6634, 6633, 6631, 6632, 6635, 6639, 6660, 6663, 6662, 6661, 6636, 6637, 6638, 6640, 6641, 6671, 6672, 6670, 6645, 6646, 6648, 6647, 6649, 6526, 6529, 6692, 6693, 6694, 6695, 6698, 6696, 6697, 6686, 6687, 6688, 6689, 6690, 6691, 6680, 6681, 6682, 6683, 6684, 6685, 6674, 6675, 6676, 6677, 6678, 6679, 6516, 6517, 6518, 6519, 6520, 6521, 6522, 6523, 6673, 6530, 6531, 6543, 6544, 6548, 6547, 6541, 6550, 6551, 6558, 6566, 6580, 6585, 6588, 6592, 6612, 7629, 7616, 7618, 7617, 7646, 7659, 7675, 7680, 7685, 7696, 7699, 7819, 7708, 7929, 7932, 7931, 7893, 7894, 7895, 7896, 7898, 7899, 7900, 7901, 7902, 7897, 7904, 7903, 7905, 4784, 4782, 4783, 4787, 4785, 4786, 7914, 7913, 7927, 7948, 7934, 7935, 7920, 7873, 7844, 7868, 7842, 8804, 8803, 8805, 8802, 8801, 7991, 8813, 7870, 7871, 8815, 7839, 8828, 8834, 8826, 7841, 8860, 8865, 8870, 8872, 8879, 8878, 8876, 8864, 8863, 8862, 8874, 8819, 8869, 8915, 8916, 8917, 8537, 8549, 8550, 8551, 8922, 8921, 8923, 8928, 8924, 8926, 8925, 8927, 8936, 8933, 8931, 8940, 8941, 8937, 8938, 8935, 8929, 8930, 8939, 8583, 8567, 8946, 8945, 8595, 8602, 8555, 8683, 8684, 8691, 8724, 8596, 8597, 8867, 8868, 7639, 7679, 7678, 7693, 7694, 7695, 7813, 7814, 7812, 7815, 10127, 10025, 9438, 9439, 9441, 9440, 8780, 8779, 8778, 9442, 10024, 8800, 8798, 8799, 10206, 10205, 8732, 8733, 8730, 8731, 10255, 10160, 10278, 10300, 10313, 10314, 6932, 6956, 6981, 6546, 6560, 7658, 4780, 4781, 8806, 8934, 8932. 6739, 6738, 6732, 6721, 6722, 6723, 6791, 6775, 6773, 6771, 6769, 6766, 6774, 6761, 6760, 6786, 6784, 6782, 6749, 6748, 6747, 6753, 6752, 6745, 6746, 6742, 6755, 6754, 6756, 6724, 6720, 8900, 6715, 6707, 6737, 6731, 6730, 6725, 6716, 6706, 6702, 6822, 6821, 6826, 6827, 6828, 6824, 6851, 6852, 6853, 6854, 6831, 6807, 6819, 6893, 6816, 6817, 6813, 6808, 6804, 6806, 6802, 6965, 6889, 6883, 6884, 6856, 6839, 6841, 6842, 6843, 6844, 6845, 6846, 6847, 6840, 6850, 6832, 6833, 6834, 6835, 6838, 6836, 6934, 6933, 6967, 6966, 6939, 6942, 6734, 6733, 6728, 6777, 6764, 6763, 6762, 6759, 6758, 6757, 6787, 6789, 6788, 6785, 6783, 6751, 6750, 6741, 6740, 6743, 6744, 6735, 6729, 6719, 6718, 6708, 6705, 6810, 6533, 6812, 6815, 6803, 6801, 6886, 6935, 6972, 7500, 6954, 6897, 6977, 6978, 6979, 6892, 6823, 6894, 6895, 6896, 6767, 6792, 6881, 6891, 6982, 6983, 6800, 6849, 6985, 6986, 6990, 6994, 6991, 6953, 6811, 6701, 6995, 6944, 6946, 6999, 6947, 6525, 6528, 6524, 6538, 6540, 6534, 6537, 6542, 6545, 6809, 6549, 6562, 6563, 6564, 6565, 6568, 6572, 6573, 6574, 6561, 6570, 6571, 6575, 6584, 6583, 6586, 6576, 6577, 6578, 6579, 6589, 6594, 6593, 6598, 6599, 6596, 7615, 7627, 7632, 7633, 7634, 7346, 7635, 7981, 7636, 7619, 7637, 7657, 7667, 7670, 7703, 7709, 8642, 7823, 7822, 7922, 7930, 7925, 7926, 4790, 4804, 7924, 9523, 9525, 9527, 9522, 9519, 7938, 7947, 7939, 7933, 7992, 7845, 7846, 7847, 7848, 7849, 7865, 7866, 7851, 7855, 7850, 7854, 7853, 7852, 7856, 7857, 7858, 7859, 7860, 7861, 7863, 7862, 7864, 7872, 7888, 8833, 8861, 7976, 8871, 8814, 8825, 8877, 8875, 8880, 8888, 8893, 6717, 8907, 8903, 8909, 8910, 8944, 8914, 8531, 8527, 8530, 8529, 8528, 8554, 8854, 8570, 8569, 8548, 8568, 8896, 8897, 8621, 8616, 8615, 8617, 6704, 8645, 8651, 8663, 8681, 8661, 8584, 8675, 8677, 8676, 8742, 10049, 10116, 8782, 8783, 10202, 9437, 10230, 10282, 6726, 6712, 6713, 6714, 6820, 6736, 6772, 6770, 6709, 6710, 6711, 6973, 6765, 6527, 6590, 4788, 4789, 8918, 8919, 8920, 8634, 8713, 8781.</t>
+LUNES, 13 DE JULIO DE 2026.
+Circuito : SED 1735.
+Hora : 12:30 a 13:00 Hrs.
+Motivo : Cambio de posición de conmutador.
+Zonas afectadas: Calle Prolongación Amazonas, Av. Amazonas, Calle Garcilaso de la Vega, Calle Copacabana, Jr. Begazo, Psj. Reynoso, Psj. Begazo, Psj. Trujillo, Calle Zoraida Montes Revilla (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
+          <t>el 13/07/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 8:41</t>
+          <t>13/07/2026 8:05</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5915&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5926&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>f98fc78cea30b054d29f43809207d2a62529bda171a96bcaead4455dba69710b</t>
+          <t>68b7f1f8856d44296872c9e777fce48b1f9f513f36616e57e1d329278591aa3b</t>
         </is>
       </c>
     </row>
     <row r="8" ht="70" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Arequipa, Yanahuara, de Arequipa, de Yanahuara</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones de distrito de Arequipa: Club Internacional. Urbanizaciones del distrito de Yanahuara: Quinta Santa Luiza, Yanahuara.</t>
+          <t>Asoc.Urb. José Luis Bustamante y Rivero Sector VII, Sector IV, Asociación Apipa Sector IX (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Inserción de subestación de distribución y otros mantenimientos de redes en media tensión.</t>
+          <t>Reubicación de Subestación de Distribución y otros mantenimientos de línea en media tensión.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [207] SAGA.</t>
+          <t>Circuito : P. Yura desde EMT 19786.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1138,81 +1117,81 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
+          <t>4517, 4516, 4513, 4514, 5012.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-Circuito : [207] SAGA.
-Hora : 06:00 a 13:00 Hrs.
-Motivo : Inserción de subestación de distribución y otros mantenimientos de redes en media tensión.
-Zonas afectadas: Urbanizaciones de distrito de Arequipa: Club Internacional. Urbanizaciones del distrito de Yanahuara: Quinta Santa Luiza, Yanahuara.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1218, 1217, 3312, 3269, 3003, 2401, 3004, 1694, 3272, 3271, 2535, 3541, 3268, 1820, 1236, 2612, 2977, 3005, 3026, 1213, 1062, 3388, 1214, 1348, 3006, 3256, 3795, 2430, 4651, 3265, 4698, 4901, 4754, 4806, 5062, 5647, 5846, 5848, 5817, 10130.</t>
+MARTES, 14 DE JULIO DE 2026.
+Circuito : P. Yura desde EMT 19786.
+Hora : 07:30 a 15:00 Hrs.
+Motivo : Reubicación de Subestación de Distribución y otros mantenimientos de línea en media tensión.
+Zonas afectadas: Asoc.Urb. José Luis Bustamante y Rivero Sector VII, Sector IV, Asociación Apipa Sector IX (Distrito de Cerro Colorado).
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4517, 4516, 4513, 4514, 5012.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 18:24 por Cuenta del sistema</t>
+          <t>el 13/07/2026 8:07 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 18:24</t>
+          <t>13/07/2026 8:07</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5916&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5928&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>e65c35bf2bf7c7a277d21b077d30d1dcae0354a3c58d873a454d7a3dce2b4cff</t>
+          <t>bccbaefdcd58a0070d9e059a78293fbf2639e346ab742cddda051c75092c189a</t>
         </is>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Islay, Mollendo, de Islay, de Mollendo</t>
+          <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
+          <t>Urbanizaciones del distrito de Cocachacra: Pampa Blanca.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (cambio e instalación de postes, cambio de armado, cambio de conductor a 120 mm2).</t>
+          <t>Mantenimiento de redes de media tensión (cambio de transformador, instalación de poste, limpieza de aisladores, podado de ramas de árboles cercanas a la línea).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [3502] TISUR.</t>
+          <t>Circuito : [3801] PAMPA BLANCA</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1224,38 +1203,683 @@
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 12 DE JULIO DE 2026:
-Circuito : [3502] TISUR.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio e instalación de postes, cambio de armado, cambio de conductor a 120 mm2).
-Zonas Afectadas: Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.
-Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
+MIÉRCOLES, 15 DE JULIO DE 2026:
+Circuito : [3801] PAMPA BLANCA.
+Hora : 07:00 a 13:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de transformador, instalación de poste, limpieza de aisladores, podado de ramas de árboles cercanas a la línea).
+Zonas afectadas : Urbanizaciones del distrito de Cocachacra: Pampa Blanca.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>el 09/07/2026 8:41 por Cuenta del sistema</t>
+          <t>el 13/07/2026 7:59 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 8:41</t>
+          <t>13/07/2026 7:59</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5914&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5917&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>fcce4dfb3762f9f20e86e81dbf35f4a3b921e74fd0ecbf90e824f95810c8d6ba</t>
+          <t>64565ce157a6c3acb432acfd9a4d59f9d230f18676afc26e97313633ac894362</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5929</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 200KVA.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1420.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 15 DE JULIO DE 2026.
+Circuito : SED 1420.
+Hora : 07:30 a 12:30 Hrs.
+Motivo : Cambio de transformador a 200KVA.
+Zonas afectadas: Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:09</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5929&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>cac9876d02e0c202e1b676bd0b8c997ee04bf4adf41e7254fe3f50460cf1673f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador de distribución.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5024.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 15 DE JULIO DE 2026.
+Circuito : SED 5024.
+Hora : 07:30 a 12:30 Hrs.
+Motivo : Cambio de transformador de distribución.
+Zonas afectadas: Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:09</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5930&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>09f5f3073ff5a8061115c4764746bca5ab2a0d94d9134d5b4998a5e6c805b668</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>La Isla (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador y tablero de distribución.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5938.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 15 DE JULIO DE 2026.
+Circuito : SED 5938.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de transformador y tablero de distribución.
+Zonas afectadas: La Isla (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:10</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5931&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>06872d53187898a7821eba381c5e8bba5a133d3d43ecae76b2bb97583b3146cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Atiquipa, Chala, Yauca, de Atiquipa, de Chala, de Yauca</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Chala: Imperial Aguada. Urbanizaciones del distrito de Yauca: Tanaka.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [5801] AGUA SALADA</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIERCOLES, 15 DE JULIO DE 2026:
+Circuito : [5801] AGUA SALADA.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas : Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Chala: Imperial Aguada. Urbanizaciones del distrito de Yauca: Tanaka.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9960, 9805, 9828, 9681, 9989, 9819, 9664, 9689, 9820, 9821, 9836, 9415, 9647, 9650, 9639, 10159, 9379, 9976, 9875, 9637, 9876, 9638, 9649, 9636, 9818.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:17 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:17</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5932&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>59d5c56bf9d3ea3ed45012554a3c6179103b7bf83080e8b11d1deea5709ed92d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5918</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [802] CIUDAD DE DIOS.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 16 DE JULIO DE 2026:
+Circuito : [802] CIUDAD DE DIOS.
+Hora : 07:30 a 15:00 Hrs.
+Motivo : Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.
+Zonas afectadas : Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3839, 4357, 4358, 5063.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5918&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>85e1dd63a41bf4c9ceb0bc0de88ea6b5e6d49b77009ddbec9fbe381260fe86ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>5919</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Peruarbo zona III, Peruarbo Sector II, Av. 20 de marzo Asoc. José Luis Bustamante y Rivero (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia de carga al Alimentador Ciudad de Dios</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ciudad Municipal desde EMT 28361.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4478, 3840, 3384, 4766, 2279.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 16 DE JULIO DE 2026.
+Circuito : Ciudad Municipal desde EMT 28361.
+Hora : 07:30 a 15:00 Hrs.
+Motivo : Transferencia de carga al Alimentador Ciudad de Dios
+Zonas afectadas: Peruarbo zona III, Peruarbo Sector II, Av. 20 de marzo Asoc. José Luis Bustamante y Rivero (Distrito de Cerro Colorado).
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4478, 3840, 3384, 4766, 2279.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:00</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5919&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>4db1a5f5383004e74207d0935782370f1b0d6a36b6ca7d677a77831330c97976</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Pedregal 2 desde REC-200555.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 17 DE JULIO DE 2026:
+Circuito : Pedregal 2 desde REC-200555.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión.
+Zonas afectadas : Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 6018, 6020, 6023, 6024, 6232, 7887, 8821, 6017, 6016, 6960, 6021, 6022, 6015</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:01 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5920&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3272ac5c958a89c641b29d9a224325b2ceb1b6da4a4188743da05c1627a1341a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>5921</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Chala, de Chala</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [5804] MANUEL PRADO.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 17 DE JULIO DE 2026:
+Circuito : [5804] MANUEL PRADO.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 13/07/2026 8:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026 8:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5921&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>9029df95dd84199925b660d57a1c2e7e39c6a4f69441ab5195af465ad8d0f30a</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1296,7 +1920,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13 12:56:03</t>
+          <t>2026-07-14 11:46:36</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1944,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1956,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1968,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1392,7 +2016,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -1404,7 +2028,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -1416,7 +2040,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1443,7 +2067,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P17" headerRowCount="1">
-  <autoFilter ref="A1:P17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,22 +593,22 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Cerro viejo, Calle comandante Canga, Calle Inca, Calle Arequipa, Calle Intendente Salamanca, Calle General Moran, Psj. Lozada (Distrito de Cerro Colorado).</t>
+          <t>Asoc.Urb. José Luis Bustamante y Rivero Sector VII, Sector IV, Asociación Apipa Sector IX (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de posición de conmutador.</t>
+          <t>Reubicación de Subestación de Distribución y otros mantenimientos de línea en media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 1241.</t>
+          <t>Circuito : P. Yura desde EMT 19786.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,491 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4517, 4516, 4513, 4514, 5012.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 13 DE JULIO DE 2026.
-Circuito : SED 1241.
-Hora : 08:00 a 08:30 Hrs.
-Motivo : Cambio de posición de conmutador.
-Zonas afectadas: Cerro viejo, Calle comandante Canga, Calle Inca, Calle Arequipa, Calle Intendente Salamanca, Calle General Moran, Psj. Lozada (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:03 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:03</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5922&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>78dd6d58f577469f88dcb67a4eecb2857db477551ba246e3048e92befcc499b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5927</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Asociación Casa Granja Villa Arapa, Peruarbo Zona II, Zona III (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimientos de redes en media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Autopista desde EMT 17567.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4233, 5408.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 13 DE JULIO DE 2026.
-Circuito : Autopista desde EMT 17567.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Mantenimientos de redes en media tensión.
-Zonas afectadas: Asociación Casa Granja Villa Arapa, Peruarbo Zona II, Zona III (Distrito de Cerro Colorado).
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4233, 5408.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:06</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5927&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>7f73a60178252127f05fbcfd0b2aa8c3c59e41033307bd6271fbaf329dbf26cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5923</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Av. José Carlos Mariátegui, Av. Manco Cápac, Calle General Ollantay, Calle 30 de Agosto, Calle 28 de Julio, Calle Chiclayo, Calle Unión (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición de conmutador.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 2845.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 13 DE JULIO DE 2026.
-Circuito : SED 2845.
-Hora : 09:30 a 10:00 Hrs.
-Motivo : Cambio de posición de conmutador.
-Zonas afectadas: Av. José Carlos Mariátegui, Av. Manco Cápac, Calle General Ollantay, Calle 30 de Agosto, Calle 28 de Julio, Calle Chiclayo, Calle Unión (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:03 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:03</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5923&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2a8561e2e5446c89e738db3b1c45e13972727e99513a458a3cbc769d10d4972e</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5924</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Av. Alto Cayma, Calle José Santos Chocano, Calle José Abelardo Quiñones (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición de conmutador.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1902.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 13 DE JULIO DE 2026.
-Circuito : SED 1902.
-Hora : 10:30 a 11:00 Hrs.
-Motivo : Cambio de posición de conmutador.
-Zonas afectadas: Av. Alto Cayma, Calle José Santos Chocano, Calle José Abelardo Quiñones (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:04 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:04</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5924&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>53ee606488201bb1b361d691940735a46c458dc522cb31b17bb32987b640208c</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5925</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Calle tres volcanes, Jr. Víctor Andrés Belaunde, Jr. Tacna, Jr. 7 de junio, Jr. Misti, Jr. Abancay, Jr. Progreso, Jr. Simón Bolívar, Jr. Independencia, Jr. Zela, Av. Arequipa (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición de conmutador.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1661.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 13 DE JULIO DE 2026.
-Circuito : SED 1661.
-Hora : 11:30 a 12:00 Hrs.
-Motivo : Cambio de posición de conmutador.
-Zonas afectadas: Calle tres volcanes, Jr. Víctor Andrés Belaunde, Jr. Tacna, Jr. 7 de junio, Jr. Misti, Jr. Abancay, Jr. Progreso, Jr. Simón Bolívar, Jr. Independencia, Jr. Zela, Av. Arequipa (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:05 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:05</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5925&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1a1f26c0e73f288abca8e9ba622dd79772d0609b174edef444a69a3d1aa2b65a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5926</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Calle Prolongación Amazonas, Av. Amazonas, Calle Garcilaso de la Vega, Calle Copacabana, Jr. Begazo, Psj. Reynoso, Psj. Begazo, Psj. Trujillo, Calle Zoraida Montes Revilla (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición de conmutador.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1735.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 13 DE JULIO DE 2026.
-Circuito : SED 1735.
-Hora : 12:30 a 13:00 Hrs.
-Motivo : Cambio de posición de conmutador.
-Zonas afectadas: Calle Prolongación Amazonas, Av. Amazonas, Calle Garcilaso de la Vega, Calle Copacabana, Jr. Begazo, Psj. Reynoso, Psj. Begazo, Psj. Trujillo, Calle Zoraida Montes Revilla (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:05 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:05</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5926&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>68b7f1f8856d44296872c9e777fce48b1f9f513f36616e57e1d329278591aa3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5928</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Asoc.Urb. José Luis Bustamante y Rivero Sector VII, Sector IV, Asociación Apipa Sector IX (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Reubicación de Subestación de Distribución y otros mantenimientos de línea en media tensión.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : P. Yura desde EMT 19786.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4517, 4516, 4513, 4514, 5012.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 14 DE JULIO DE 2026.
@@ -1131,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4517, 4516, 4513, 4514, 5012.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:07 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:07</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5928&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>bccbaefdcd58a0070d9e059a78293fbf2639e346ab742cddda051c75092c189a</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5917</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cocachacra: Pampa Blanca.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de transformador, instalación de poste, limpieza de aisladores, podado de ramas de árboles cercanas a la línea).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [3801] PAMPA BLANCA</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 15 DE JULIO DE 2026:
@@ -1211,76 +732,76 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 7:59 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 7:59</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5917&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>64565ce157a6c3acb432acfd9a4d59f9d230f18676afc26e97313633ac894362</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5929</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 200KVA.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1420.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026.
@@ -1290,76 +811,76 @@
 Zonas afectadas: Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5929&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>cac9876d02e0c202e1b676bd0b8c997ee04bf4adf41e7254fe3f50460cf1673f</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5930</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5024.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026.
@@ -1369,76 +890,76 @@
 Zonas afectadas: Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5930&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>09f5f3073ff5a8061115c4764746bca5ab2a0d94d9134d5b4998a5e6c805b668</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5931</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>La Isla (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador y tablero de distribución.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5938.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026.
@@ -1448,76 +969,76 @@
 Zonas afectadas: La Isla (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5931&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>06872d53187898a7821eba381c5e8bba5a133d3d43ecae76b2bb97583b3146cb</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5932</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Atiquipa, Chala, Yauca, de Atiquipa, de Chala, de Yauca</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Chala: Imperial Aguada. Urbanizaciones del distrito de Yauca: Tanaka.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5801] AGUA SALADA</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026:
@@ -1528,76 +1049,76 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9960, 9805, 9828, 9681, 9989, 9819, 9664, 9689, 9820, 9821, 9836, 9415, 9647, 9650, 9639, 10159, 9379, 9976, 9875, 9637, 9876, 9638, 9649, 9636, 9818.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:17</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5932&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>59d5c56bf9d3ea3ed45012554a3c6179103b7bf83080e8b11d1deea5709ed92d</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5918</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : [802] CIUDAD DE DIOS.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 16 DE JULIO DE 2026:
@@ -1608,80 +1129,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3839, 4357, 4358, 5063.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:00</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5918&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>85e1dd63a41bf4c9ceb0bc0de88ea6b5e6d49b77009ddbec9fbe381260fe86ab</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5919</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Peruarbo zona III, Peruarbo Sector II, Av. 20 de marzo Asoc. José Luis Bustamante y Rivero (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Transferencia de carga al Alimentador Ciudad de Dios</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde EMT 28361.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>4478, 3840, 3384, 4766, 2279.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 16 DE JULIO DE 2026.
@@ -1692,76 +1213,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4478, 3840, 3384, 4766, 2279.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:00</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5919&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>4db1a5f5383004e74207d0935782370f1b0d6a36b6ca7d677a77831330c97976</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>5920</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pedregal 2 desde REC-200555.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1772,80 +1293,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 6018, 6020, 6023, 6024, 6232, 7887, 8821, 6017, 6016, 6960, 6021, 6022, 6015</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:01</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5920&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3272ac5c958a89c641b29d9a224325b2ceb1b6da4a4188743da05c1627a1341a</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>5921</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Chala, de Chala</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5804] MANUEL PRADO.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1856,30 +1377,114 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:02</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5921&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>9029df95dd84199925b660d57a1c2e7e39c6a4f69441ab5195af465ad8d0f30a</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5933</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Deán Valdivia, de Deán Valdivia</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Deán Valdivia: Quebrada de Quelaque.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, mantenimiento de</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Mejía desde BC - 360102.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8227, 8229, 8230, 8535, 8587.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 17 DE JULIO DE 2026:
+Circuito : Mejía desde BC - 360102.
+Hora : 08:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, mantenimiento de subestaciones).
+Zonas afectadas: Urbanizaciones del distrito de Deán Valdivia: Quebrada de Quelaque.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8229, 8230, 8535, 8587.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 14/07/2026 18:15 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14/07/2026 18:15</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5933&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>30aa7d9c22f44f0528ce10e1e4708f7d9a8ffe86c54798d192152ec546df2ac5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P17"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1920,7 +1525,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14 11:46:36</t>
+          <t>2026-07-15 11:51:14</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1549,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1561,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1573,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -2016,7 +1621,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -2028,7 +1633,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -2040,7 +1645,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2067,7 +1672,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
+  <autoFilter ref="A1:P11"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Cocachacra, de Cocachacra</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Asoc.Urb. José Luis Bustamante y Rivero Sector VII, Sector IV, Asociación Apipa Sector IX (Distrito de Cerro Colorado).</t>
+          <t>Urbanizaciones del distrito de Cocachacra: Pampa Blanca.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reubicación de Subestación de Distribución y otros mantenimientos de línea en media tensión.</t>
+          <t>Mantenimiento de redes de media tensión (cambio de transformador, instalación de poste, limpieza de aisladores, podado de ramas de árboles cercanas a la línea).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : P. Yura desde EMT 19786.</t>
+          <t>Circuito : [3801] PAMPA BLANCA</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,92 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>4517, 4516, 4513, 4514, 5012.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 14 DE JULIO DE 2026.
-Circuito : P. Yura desde EMT 19786.
-Hora : 07:30 a 15:00 Hrs.
-Motivo : Reubicación de Subestación de Distribución y otros mantenimientos de línea en media tensión.
-Zonas afectadas: Asoc.Urb. José Luis Bustamante y Rivero Sector VII, Sector IV, Asociación Apipa Sector IX (Distrito de Cerro Colorado).
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4517, 4516, 4513, 4514, 5012.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:07 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:07</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5928&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>bccbaefdcd58a0070d9e059a78293fbf2639e346ab742cddda051c75092c189a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5917</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cocachacra, de Cocachacra</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cocachacra: Pampa Blanca.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de transformador, instalación de poste, limpieza de aisladores, podado de ramas de árboles cercanas a la línea).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [3801] PAMPA BLANCA</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 15 DE JULIO DE 2026:
@@ -732,76 +648,76 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 7:59 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 7:59</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5917&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>64565ce157a6c3acb432acfd9a4d59f9d230f18676afc26e97313633ac894362</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5929</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 200KVA.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1420.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026.
@@ -811,76 +727,76 @@
 Zonas afectadas: Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5929&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>cac9876d02e0c202e1b676bd0b8c997ee04bf4adf41e7254fe3f50460cf1673f</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5930</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador de distribución.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5024.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026.
@@ -890,76 +806,76 @@
 Zonas afectadas: Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:09</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5930&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>09f5f3073ff5a8061115c4764746bca5ab2a0d94d9134d5b4998a5e6c805b668</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5931</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>La Isla (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador y tablero de distribución.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5938.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026.
@@ -969,76 +885,76 @@
 Zonas afectadas: La Isla (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:10</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5931&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>06872d53187898a7821eba381c5e8bba5a133d3d43ecae76b2bb97583b3146cb</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5932</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Atiquipa, Chala, Yauca, de Atiquipa, de Chala, de Yauca</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Chala: Imperial Aguada. Urbanizaciones del distrito de Yauca: Tanaka.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5801] AGUA SALADA</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIERCOLES, 15 DE JULIO DE 2026:
@@ -1049,76 +965,76 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9960, 9805, 9828, 9681, 9989, 9819, 9664, 9689, 9820, 9821, 9836, 9415, 9647, 9650, 9639, 10159, 9379, 9976, 9875, 9637, 9876, 9638, 9649, 9636, 9818.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:17</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5932&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>59d5c56bf9d3ea3ed45012554a3c6179103b7bf83080e8b11d1deea5709ed92d</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5918</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : [802] CIUDAD DE DIOS.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 16 DE JULIO DE 2026:
@@ -1129,80 +1045,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3839, 4357, 4358, 5063.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:00</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5918&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>85e1dd63a41bf4c9ceb0bc0de88ea6b5e6d49b77009ddbec9fbe381260fe86ab</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5919</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Peruarbo zona III, Peruarbo Sector II, Av. 20 de marzo Asoc. José Luis Bustamante y Rivero (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Transferencia de carga al Alimentador Ciudad de Dios</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde EMT 28361.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>4478, 3840, 3384, 4766, 2279.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 16 DE JULIO DE 2026.
@@ -1213,76 +1129,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4478, 3840, 3384, 4766, 2279.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:00</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5919&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>4db1a5f5383004e74207d0935782370f1b0d6a36b6ca7d677a77831330c97976</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5920</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pedregal 2 desde REC-200555.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1293,80 +1209,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 6018, 6020, 6023, 6024, 6232, 7887, 8821, 6017, 6016, 6960, 6021, 6022, 6015</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:01</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5920&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>3272ac5c958a89c641b29d9a224325b2ceb1b6da4a4188743da05c1627a1341a</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>5921</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Chala, de Chala</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5804] MANUEL PRADO.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1377,80 +1293,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:02</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5921&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>9029df95dd84199925b660d57a1c2e7e39c6a4f69441ab5195af465ad8d0f30a</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>5933</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Deán Valdivia, de Deán Valdivia</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Deán Valdivia: Quebrada de Quelaque.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (limpieza de aisladores, mantenimiento de</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : Mejía desde BC - 360102.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>8227, 8229, 8230, 8535, 8587.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1461,30 +1377,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8229, 8230, 8535, 8587.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 14/07/2026 18:15 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>14/07/2026 18:15</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5933&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>30aa7d9c22f44f0528ce10e1e4708f7d9a8ffe86c54798d192152ec546df2ac5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1525,7 +1441,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15 11:51:14</t>
+          <t>2026-07-16 11:55:19</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1465,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1477,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1489,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1561,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1588,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
-  <autoFilter ref="A1:P11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
+  <autoFilter ref="A1:P10"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cocachacra, de Cocachacra</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cocachacra: Pampa Blanca.</t>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (cambio de transformador, instalación de poste, limpieza de aisladores, podado de ramas de árboles cercanas a la línea).</t>
+          <t>Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [3801] PAMPA BLANCA</t>
+          <t>Circuito : [802] CIUDAD DE DIOS.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,403 +638,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 15 DE JULIO DE 2026:
-Circuito : [3801] PAMPA BLANCA.
-Hora : 07:00 a 13:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de transformador, instalación de poste, limpieza de aisladores, podado de ramas de árboles cercanas a la línea).
-Zonas afectadas : Urbanizaciones del distrito de Cocachacra: Pampa Blanca.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 8215, 8658, 8657.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 7:59 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 7:59</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5917&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>64565ce157a6c3acb432acfd9a4d59f9d230f18676afc26e97313633ac894362</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5929</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 200KVA.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1420.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 15 DE JULIO DE 2026.
-Circuito : SED 1420.
-Hora : 07:30 a 12:30 Hrs.
-Motivo : Cambio de transformador a 200KVA.
-Zonas afectadas: Alto Libertad Av. Lima, Calle 28 de julio, Calle Manco Capac, Calle 15 de agosto, Calle Jorge Chávez y Jr. Ancash (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:09</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5929&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>cac9876d02e0c202e1b676bd0b8c997ee04bf4adf41e7254fe3f50460cf1673f</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5930</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador de distribución.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5024.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 15 DE JULIO DE 2026.
-Circuito : SED 5024.
-Hora : 07:30 a 12:30 Hrs.
-Motivo : Cambio de transformador de distribución.
-Zonas afectadas: Urbanización Mirasol de Cayma (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:09 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:09</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5930&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>09f5f3073ff5a8061115c4764746bca5ab2a0d94d9134d5b4998a5e6c805b668</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Arequipa, de Arequipa</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>La Isla (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador y tablero de distribución.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5938.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 15 DE JULIO DE 2026.
-Circuito : SED 5938.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Cambio de transformador y tablero de distribución.
-Zonas afectadas: La Isla (Distrito de Arequipa).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:10 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:10</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5931&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>06872d53187898a7821eba381c5e8bba5a133d3d43ecae76b2bb97583b3146cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5932</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Atiquipa, Chala, Yauca, de Atiquipa, de Chala, de Yauca</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Chala: Imperial Aguada. Urbanizaciones del distrito de Yauca: Tanaka.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [5801] AGUA SALADA</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIERCOLES, 15 DE JULIO DE 2026:
-Circuito : [5801] AGUA SALADA.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas : Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Chala: Imperial Aguada. Urbanizaciones del distrito de Yauca: Tanaka.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 9960, 9805, 9828, 9681, 9989, 9819, 9664, 9689, 9820, 9821, 9836, 9415, 9647, 9650, 9639, 10159, 9379, 9976, 9875, 9637, 9876, 9638, 9649, 9636, 9818.</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:17 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:17</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5932&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>59d5c56bf9d3ea3ed45012554a3c6179103b7bf83080e8b11d1deea5709ed92d</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5918</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>16/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [802] CIUDAD DE DIOS.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 16 DE JULIO DE 2026:
@@ -1045,80 +648,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3839, 4357, 4358, 5063.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:00</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5918&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>85e1dd63a41bf4c9ceb0bc0de88ea6b5e6d49b77009ddbec9fbe381260fe86ab</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5919</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Peruarbo zona III, Peruarbo Sector II, Av. 20 de marzo Asoc. José Luis Bustamante y Rivero (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Transferencia de carga al Alimentador Ciudad de Dios</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde EMT 28361.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>4478, 3840, 3384, 4766, 2279.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 16 DE JULIO DE 2026.
@@ -1129,76 +732,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4478, 3840, 3384, 4766, 2279.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:00</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5919&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>4db1a5f5383004e74207d0935782370f1b0d6a36b6ca7d677a77831330c97976</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5920</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Pedregal 2 desde REC-200555.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1209,80 +812,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 6018, 6020, 6023, 6024, 6232, 7887, 8821, 6017, 6016, 6960, 6021, 6022, 6015</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:01</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16/07/2026 17:53</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5920&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>3272ac5c958a89c641b29d9a224325b2ceb1b6da4a4188743da05c1627a1341a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>8af5ff496d7647701974e5c9cf7032eda975a10b52aa455091d361ebdd35f2f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5921</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Chala, de Chala</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5804] MANUEL PRADO.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1293,80 +896,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:02</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5921&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>9029df95dd84199925b660d57a1c2e7e39c6a4f69441ab5195af465ad8d0f30a</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5933</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Deán Valdivia, de Deán Valdivia</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Deán Valdivia: Quebrada de Quelaque.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (limpieza de aisladores, mantenimiento de</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Mejía desde BC - 360102.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>8227, 8229, 8230, 8535, 8587.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -1377,30 +980,359 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8229, 8230, 8535, 8587.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 14/07/2026 18:15 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>14/07/2026 18:15</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5933&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>30aa7d9c22f44f0528ce10e1e4708f7d9a8ffe86c54798d192152ec546df2ac5</t>
         </is>
       </c>
     </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Islay, Mollendo, de Islay, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [3502] TISUR.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+SABADO, 18 DE JULIO DE 2026:
+Circuito : [3502] TISUR.
+Hora : 07:00 a 11:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión.
+Zonas Afectadas: Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.
+Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 16/07/2026 15:27 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:27</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5935&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>ab0909618762ef3322a73108d4098b07486c535ec832a5f790e1f254f4dc1fe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5936</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Islay, de Islay</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización del Distrito de Islay: Asoc.Viv.Tall.Villa El Pescador.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Afectado por corte de Alimentador Tisur.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Matarani desde REC - 350105.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+SABADO, 18 DE JULIO DE 2026:
+Circuito : Matarani desde REC - 350105.
+Hora : 07:00 a 11:00 Hrs.
+Motivo : Afectado por corte de Alimentador Tisur.
+Zonas Afectadas: Urbanización del Distrito de Islay: Asoc.Viv.Tall.Villa El Pescador.
+Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8266, 8124, 8123, 8290, 8291, 8332, 8394, 8471, 8475, 8125, 8257, 8601, 8668, 8331.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 16/07/2026 15:28 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:28</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5936&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>d36f65d834212bf14b36910b32d8db613dbcbabf81ae3182043881feedd0044e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5934</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Atico, Mariano Nicolas Valcarcel, Ocoña, Rio Grande, Yanaquihua, de Atico, de Mariano Nicolas Valcarcel, de Ocoña, de Rio Grande, de Yanaquihua</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>LÍNEA : L-3094 JAHUAY - OCOÑA. SET : [45] OCOÑA</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 19 DE JULIO DE 2026:
+LÍNEA : L-3094 JAHUAY - OCOÑA.
+SET : [45] OCOÑA
+Hora : 06:00 a 13:00 Hrs.
+Motivo : Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.
+Zonas afectadas: Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 16/07/2026 15:25 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:25</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5934&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>37ebdb6a7897d7c56a6b69fd77359c1e44909fba3818296fcb35b968e0755400</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5937</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al Procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : La Marina desde REC - 200529.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 19 DE JULIO DE 2026:
+Circuito : La Marina desde REC - 200529.
+Hora : 06:00 a 13:00 Hrs.
+Motivo : Subsanación de deficiencias en atención al Procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 16/07/2026 15:29 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:29</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5937&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>577ab16376cc2b4b204cfed6d8b1f16a88bf54c61e47dd4d4a6d5553337625ae</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1441,7 +1373,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16 11:55:19</t>
+          <t>2026-07-17 11:43:20</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1397,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1409,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1421,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1469,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1481,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1493,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1520,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
-  <autoFilter ref="A1:P10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
+  <autoFilter ref="A1:P8"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,17 +593,17 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -613,195 +613,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Majes, de Majes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.</t>
+          <t>Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.</t>
+          <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [802] CIUDAD DE DIOS.</t>
+          <t>Circuito : Pedregal 2 desde REC-200555.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 16 DE JULIO DE 2026:
-Circuito : [802] CIUDAD DE DIOS.
-Hora : 07:30 a 15:00 Hrs.
-Motivo : Transferencia de carga del Alimentador Ciudad Municipal, conexión de red de media tensión y otros mantenimientos de media tensión.
-Zonas afectadas : Urbanizaciones del distrito de Cerro Colorado: Peruano-Argentino-Boliviano Sector Bolivia I, Peruano-Argentino-Boliviano Zona III.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3839, 4357, 4358, 5063.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:00</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5918&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>85e1dd63a41bf4c9ceb0bc0de88ea6b5e6d49b77009ddbec9fbe381260fe86ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5919</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>16/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Peruarbo zona III, Peruarbo Sector II, Av. 20 de marzo Asoc. José Luis Bustamante y Rivero (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Transferencia de carga al Alimentador Ciudad de Dios</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Ciudad Municipal desde EMT 28361.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4478, 3840, 3384, 4766, 2279.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 16 DE JULIO DE 2026.
-Circuito : Ciudad Municipal desde EMT 28361.
-Hora : 07:30 a 15:00 Hrs.
-Motivo : Transferencia de carga al Alimentador Ciudad de Dios
-Zonas afectadas: Peruarbo zona III, Peruarbo Sector II, Av. 20 de marzo Asoc. José Luis Bustamante y Rivero (Distrito de Cerro Colorado).
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4478, 3840, 3384, 4766, 2279.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:00 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:00</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5919&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>4db1a5f5383004e74207d0935782370f1b0d6a36b6ca7d677a77831330c97976</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5920</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Pedregal 2 desde REC-200555.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -812,80 +648,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 6018, 6020, 6023, 6024, 6232, 7887, 8821, 6017, 6016, 6960, 6021, 6022, 6015</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 17:53</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5920&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>8af5ff496d7647701974e5c9cf7032eda975a10b52aa455091d361ebdd35f2f3</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5921</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Chala, de Chala</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [5804] MANUEL PRADO.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -896,80 +732,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 13/07/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>13/07/2026 8:02</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5921&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>9029df95dd84199925b660d57a1c2e7e39c6a4f69441ab5195af465ad8d0f30a</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5933</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Deán Valdivia, de Deán Valdivia</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Deán Valdivia: Quebrada de Quelaque.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (limpieza de aisladores, mantenimiento de</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Mejía desde BC - 360102.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8227, 8229, 8230, 8535, 8587.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 17 DE JULIO DE 2026:
@@ -980,76 +816,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8229, 8230, 8535, 8587.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 14/07/2026 18:15 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14/07/2026 18:15</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5933&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>30aa7d9c22f44f0528ce10e1e4708f7d9a8ffe86c54798d192152ec546df2ac5</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5935</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Islay, Mollendo, de Islay, de Mollendo</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : [3502] TISUR.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SABADO, 18 DE JULIO DE 2026:
@@ -1060,76 +896,76 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:27 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:27</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5935&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>ab0909618762ef3322a73108d4098b07486c535ec832a5f790e1f254f4dc1fe6</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5936</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Islay, de Islay</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanización del Distrito de Islay: Asoc.Viv.Tall.Villa El Pescador.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte de Alimentador Tisur.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Matarani desde REC - 350105.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SABADO, 18 DE JULIO DE 2026:
@@ -1140,80 +976,80 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8266, 8124, 8123, 8290, 8291, 8332, 8394, 8471, 8475, 8125, 8257, 8601, 8668, 8331.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:28 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:28</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5936&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>d36f65d834212bf14b36910b32d8db613dbcbabf81ae3182043881feedd0044e</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5934</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Atico, Mariano Nicolas Valcarcel, Ocoña, Rio Grande, Yanaquihua, de Atico, de Mariano Nicolas Valcarcel, de Ocoña, de Rio Grande, de Yanaquihua</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>LÍNEA : L-3094 JAHUAY - OCOÑA. SET : [45] OCOÑA</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 19 DE JULIO DE 2026:
@@ -1225,80 +1061,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:25</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5934&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>37ebdb6a7897d7c56a6b69fd77359c1e44909fba3818296fcb35b968e0755400</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5937</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Marina desde REC - 200529.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 19 DE JULIO DE 2026:
@@ -1309,30 +1145,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:29</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5937&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>577ab16376cc2b4b204cfed6d8b1f16a88bf54c61e47dd4d4a6d5553337625ae</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1373,7 +1209,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17 11:43:20</t>
+          <t>2026-07-18 11:19:29</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1233,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1245,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1257,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1329,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1356,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
-  <autoFilter ref="A1:P8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
+  <autoFilter ref="A1:P5"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>Islay, Mollendo, de Islay, de Mollendo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.</t>
+          <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -628,264 +628,16 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Pedregal 2 desde REC-200555.</t>
+          <t>Circuito : [3502] TISUR.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+          <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 17 DE JULIO DE 2026:
-Circuito : Pedregal 2 desde REC-200555.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión.
-Zonas afectadas : Urbanizaciones del Distrito de Majes: Futuro Majes, Las Malvinas, Pedregal, Pedregal Norte.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 6018, 6020, 6023, 6024, 6232, 7887, 8821, 6017, 6016, 6960, 6021, 6022, 6015</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:01 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>16/07/2026 17:53</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5920&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>8af5ff496d7647701974e5c9cf7032eda975a10b52aa455091d361ebdd35f2f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5921</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Chala, de Chala</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [5804] MANUEL PRADO.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 17 DE JULIO DE 2026:
-Circuito : [5804] MANUEL PRADO.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del Distrito de Chala: Chala, Imperial Aguada, Imperial La Aguadita, Las Brisas, Las Flores de Chala, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9414, 9645, 10166, 10236, 10257.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 13/07/2026 8:02 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026 8:02</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5921&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>9029df95dd84199925b660d57a1c2e7e39c6a4f69441ab5195af465ad8d0f30a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5933</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Deán Valdivia, de Deán Valdivia</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Deán Valdivia: Quebrada de Quelaque.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, mantenimiento de</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Mejía desde BC - 360102.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8227, 8229, 8230, 8535, 8587.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 17 DE JULIO DE 2026:
-Circuito : Mejía desde BC - 360102.
-Hora : 08:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, mantenimiento de subestaciones).
-Zonas afectadas: Urbanizaciones del distrito de Deán Valdivia: Quebrada de Quelaque.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8227, 8229, 8230, 8535, 8587.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 14/07/2026 18:15 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14/07/2026 18:15</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5933&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>30aa7d9c22f44f0528ce10e1e4708f7d9a8ffe86c54798d192152ec546df2ac5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5935</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Islay, Mollendo, de Islay, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [3502] TISUR.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SABADO, 18 DE JULIO DE 2026:
@@ -896,76 +648,76 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:27 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:27</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5935&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>ab0909618762ef3322a73108d4098b07486c535ec832a5f790e1f254f4dc1fe6</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5936</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>18/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Islay, de Islay</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanización del Distrito de Islay: Asoc.Viv.Tall.Villa El Pescador.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Afectado por corte de Alimentador Tisur.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Matarani desde REC - 350105.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SABADO, 18 DE JULIO DE 2026:
@@ -976,80 +728,80 @@
 Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8266, 8124, 8123, 8290, 8291, 8332, 8394, 8471, 8475, 8125, 8257, 8601, 8668, 8331.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:28 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:28</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5936&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>d36f65d834212bf14b36910b32d8db613dbcbabf81ae3182043881feedd0044e</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5934</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Atico, Mariano Nicolas Valcarcel, Ocoña, Rio Grande, Yanaquihua, de Atico, de Mariano Nicolas Valcarcel, de Ocoña, de Rio Grande, de Yanaquihua</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>LÍNEA : L-3094 JAHUAY - OCOÑA. SET : [45] OCOÑA</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 19 DE JULIO DE 2026:
@@ -1061,80 +813,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:25</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5934&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>37ebdb6a7897d7c56a6b69fd77359c1e44909fba3818296fcb35b968e0755400</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5937</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Marina desde REC - 200529.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 19 DE JULIO DE 2026:
@@ -1145,30 +897,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:29</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5937&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>577ab16376cc2b4b204cfed6d8b1f16a88bf54c61e47dd4d4a6d5553337625ae</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
+  <autoFilter ref="A1:P5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1209,7 +961,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18 11:19:29</t>
+          <t>2026-07-19 11:32:43</t>
         </is>
       </c>
     </row>
@@ -1233,7 +985,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1245,7 +997,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1009,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1081,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1108,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
-  <autoFilter ref="A1:P5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Islay, Mollendo, de Islay, de Mollendo</t>
+          <t>Atico, Mariano Nicolas Valcarcel, Ocoña, Rio Grande, Yanaquihua, de Atico, de Mariano Nicolas Valcarcel, de Ocoña, de Rio Grande, de Yanaquihua</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.</t>
+          <t>Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión.</t>
+          <t>Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [3502] TISUR.</t>
+          <t>LÍNEA : L-3094 JAHUAY - OCOÑA. SET : [45] OCOÑA</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,172 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-SABADO, 18 DE JULIO DE 2026:
-Circuito : [3502] TISUR.
-Hora : 07:00 a 11:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión.
-Zonas Afectadas: Urbanización del Distrito de Islay: Centro poblado de Islay, Matarani, Carretera al Faro Tisur. Urbanización del Distrito de Mollendo: Ceticos Matarani.
-Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8130, 8630, 8629, 8418.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 16/07/2026 15:27 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>16/07/2026 15:27</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5935&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>ab0909618762ef3322a73108d4098b07486c535ec832a5f790e1f254f4dc1fe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5936</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Islay, de Islay</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanización del Distrito de Islay: Asoc.Viv.Tall.Villa El Pescador.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Afectado por corte de Alimentador Tisur.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Matarani desde REC - 350105.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-SABADO, 18 DE JULIO DE 2026:
-Circuito : Matarani desde REC - 350105.
-Hora : 07:00 a 11:00 Hrs.
-Motivo : Afectado por corte de Alimentador Tisur.
-Zonas Afectadas: Urbanización del Distrito de Islay: Asoc.Viv.Tall.Villa El Pescador.
-Subestaciones de Distribución (SED) involucradas según zonas afectadas líneas arriba: 8266, 8124, 8123, 8290, 8291, 8332, 8394, 8471, 8475, 8125, 8257, 8601, 8668, 8331.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 16/07/2026 15:28 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>16/07/2026 15:28</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5936&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>d36f65d834212bf14b36910b32d8db613dbcbabf81ae3182043881feedd0044e</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5934</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Atico, Mariano Nicolas Valcarcel, Ocoña, Rio Grande, Yanaquihua, de Atico, de Mariano Nicolas Valcarcel, de Ocoña, de Rio Grande, de Yanaquihua</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>LÍNEA : L-3094 JAHUAY - OCOÑA. SET : [45] OCOÑA</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 19 DE JULIO DE 2026:
@@ -813,80 +653,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:25</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5934&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>37ebdb6a7897d7c56a6b69fd77359c1e44909fba3818296fcb35b968e0755400</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5937</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al Procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Marina desde REC - 200529.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 19 DE JULIO DE 2026:
@@ -897,30 +737,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 16/07/2026 15:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>16/07/2026 15:29</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5937&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>577ab16376cc2b4b204cfed6d8b1f16a88bf54c61e47dd4d4a6d5553337625ae</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P5"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -961,7 +801,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19 11:32:43</t>
+          <t>2026-07-20 12:26:58</t>
         </is>
       </c>
     </row>
@@ -985,7 +825,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -997,7 +837,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1009,7 +849,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -1081,7 +921,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +948,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Atico, Mariano Nicolas Valcarcel, Ocoña, Rio Grande, Yanaquihua, de Atico, de Mariano Nicolas Valcarcel, de Ocoña, de Rio Grande, de Yanaquihua</t>
+          <t>Samuel Pastor, de Samuel Pastor</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.</t>
+          <t>Urbanizaciones del distrito de Samuel Pastor: Balneario Agustino, La Marina, La Punta Vieja, La Punta Nueva Zona A.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.</t>
+          <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>LÍNEA : L-3094 JAHUAY - OCOÑA. SET : [45] OCOÑA</t>
+          <t>Circuito : Costanera desde CC - 400403.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,82 +638,81 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
+          <t>9120, 9303, 9107, 9074, 9281, 9137.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 19 DE JULIO DE 2026:
-LÍNEA : L-3094 JAHUAY - OCOÑA.
-SET : [45] OCOÑA
-Hora : 06:00 a 13:00 Hrs.
-Motivo : Mantenimiento de la línea de transmisión (Cambio de retenida, cambio de aisladores, podado) y Mantenimiento de transformador de potencia, cambio de seccionadores en patio de 33KV y pruebas de Recloser.
-Zonas afectadas: Urbanizaciones del distrito de Atico: Cerro de Arena. Urbanizaciones del distrito de Mariano Nicolas Valcarcel: Alto Mirador, Anchalo-Huacan, Carlos Portocarrero Dongo, Cerro Barroso, Jayhuiche, La Tranca Platanal, Mina Posco Misky, Misky II, Piuca, San Martin, Santa Rosa, Secocha, Surita, Urasqui. Urbanizaciones del distrito de Ocoña: Alto Pueblo Viejo, Alto Pumacoto, Ceniceros, Centro Poblado Pueblo Viejo, El Puente, Hualla, Huantay, La Planchada, Mollebamba, Nuevo Chiguay, Ocoña, Pescadores, Pueblo de Chule, Santa Rita. Urbanizaciones del distrito de Rio Grande: Alto Molino, Avispa, Callanga, Chorunga, Huaca, Iquipi, Ispana, La Capilla, La Culata, Piuca, San Jose, San Juan de Churunga. Urbanizaciones del distrito de Yanaquihua: Base Rey, Cerro Rico, Chococa, Potreros, Quiscayoc, Yause.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9507, 9506, 9505, 9502, 9501, 9500, 9510, 9509, 9508, 9511, 9513, 9512, 9514, 9515, 9516, 9517, 9518, 9923, 9950, 9949, 9948, 9946, 9947, 9945, 9922, 9941, 9939, 9968, 9917, 9918, 9920, 9937, 9921, 9935, 9934, 9933, 9916, 9932, 9931, 9929, 9928, 9926, 9925, 9924, 9944, 9943, 9942, 9940, 9919, 7984, 7985, 9528, 9530, 9532, 9534, 9535, 9533, 9536, 9529, 9542, 9543, 9546, 9545, 9990, 9551, 9548, 9549, 9553, 9552, 9550, 9544, 9577, 9584, 9588, 9540, 9547, 9366, 9591, 9592, 9593, 9383, 9594, 9595, 9411, 5771, 9409, 9562, 9563, 10075, 9433, 9434, 10280, 9504, 9503, 9936, 9930, 9927, 9590, 9531, 9953, 10074.</t>
+LUNES, 20 DE JULIO DE 2026:
+Circuito : Costanera desde CC - 400403.
+Hora : 09:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Samuel Pastor: Balneario Agustino, La Marina, La Punta Vieja, La Punta Nueva Zona A.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9120, 9303, 9107, 9074, 9281, 9137.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>el 16/07/2026 15:25 por Cuenta del sistema</t>
+          <t>el 20/07/2026 8:20 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026 15:25</t>
+          <t>20/07/2026 8:20</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5934&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5939&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>37ebdb6a7897d7c56a6b69fd77359c1e44909fba3818296fcb35b968e0755400</t>
+          <t>caed7f7a96bb0aa7b9ba53ee29b45d62d4c60cb77a2020643fd4d79148142bee</t>
         </is>
       </c>
     </row>
     <row r="3" ht="70" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Arequipa, de Arequipa</t>
+          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, distrito de Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de distrito de Puyca</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa.</t>
+          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Urbanizaciones del distrito de distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Subsanación de deficiencias en atención al Procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+          <t>Subsanación de deficiencias en atención al procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Circuito : La Marina desde REC - 200529.</t>
+          <t>Circuito : [70] COTAHUASI.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -721,46 +720,780 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
-        </is>
-      </c>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 19 DE JULIO DE 2026:
-Circuito : La Marina desde REC - 200529.
-Hora : 06:00 a 13:00 Hrs.
-Motivo : Subsanación de deficiencias en atención al Procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4932, 2348, 1583, 2922, 2923, 2924, 2677, 2676, 1064, 5360, 1065, 10105, 1089, 2235, 3928, 2236, 5876, 1063, 2132, 3394, 4941, 1501, 4334, 4716, 4912, 4869, 5351, 3148, 5815.</t>
+MARTES, 21 DE JULIO DE 2026:
+Circuito : [70] COTAHUASI.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Subsanación de deficiencias en atención al procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas : Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Urbanizaciones del distrito de distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>el 16/07/2026 15:29 por Cuenta del sistema</t>
+          <t>el 20/07/2026 8:21 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026 15:29</t>
+          <t>20/07/2026 8:21</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5937&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5941&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>577ab16376cc2b4b204cfed6d8b1f16a88bf54c61e47dd4d4a6d5553337625ae</t>
+          <t>171bf9e18a935a35b37acbd27c2b7b0ca08d1a132ff039e83557187ec97ababf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5940</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mariano Melgar, de Mariano Melgar</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>AAHH Berlín, Asoc. de Vivienda Pequeños talleres Sr. De los Milagros, P.J. El Mirador Zona I, P.J. El Mirador Zona II, AA.HH. Pueblo Libre, Los Ángeles, PP.JJ. Cerrito Belén (Distrito de Mariano Melgar).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al procedimiento N° 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Galaxia desde EMT 16413.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4049, 4772, 3641, 3642, 3375, 3376, 3643, 3354.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 21 DE JULIO DE 2026.
+Circuito : Galaxia desde EMT 16413.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al procedimiento N° 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.
+Zonas afectadas: AAHH Berlín, Asoc. de Vivienda Pequeños talleres Sr. De los Milagros, P.J. El Mirador Zona I, P.J. El Mirador Zona II, AA.HH. Pueblo Libre, Los Ángeles, PP.JJ. Cerrito Belén (Distrito de Mariano Melgar).
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4049, 4772, 3641, 3642, 3375, 3376, 3643, 3354.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:20 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:20</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5940&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7f521b7b6bc216443402b78589f8dc0584b7b7398729e30bc6b3b711b96147a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5945</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Majes, de Majes</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Majes: El Pedregal - Los Molles.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de retenida y podado de ramas de árboles cercanas a línea de media tensión).</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Laive desde CC - 200497.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6007, 6032, 6031, 6030.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 22 DE JULIO DE 2026:
+Circuito : Laive desde CC - 200497.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de postes, cambio de retenida y podado de ramas de árboles cercanas a línea de media tensión).
+Zonas afectadas: Urbanizaciones del distrito de Majes: El Pedregal - Los Molles.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6007, 6032, 6031, 6030.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:24 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:24</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5945&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>ab2a4dcb3320cd2828c53623653f4f08580b31965fd0b56634a413e2e7d1dfec</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5943</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Quilca, Samuel Pastor, de Quilca, de Samuel Pastor</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Quilca: Ampliación La Caleta, El Mirador, La Caleta de Quilca, Las Higueritas, Playa San Marino, Pueblo de Quilca. Urbanizaciones del distrito de Samuel Pastor: Las Cuevas, Los Cerrillos Zona III.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al procedimiento N°228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Costanera desde SF6 - 200527.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 22 DE JULIO DE 2026:
+Circuito : Costanera desde SF6 - 200527.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al procedimiento N°228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Quilca: Ampliación La Caleta, El Mirador, La Caleta de Quilca, Las Higueritas, Playa San Marino, Pueblo de Quilca. Urbanizaciones del distrito de Samuel Pastor: Las Cuevas, Los Cerrillos Zona III.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:22</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5943&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>07c7447fc49fb30b7c52bd38145adb1948a3043fd65a5f3f78ab4dd5fad59c83</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5946</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de subestación de distribución.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1835</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 22 DE JULIO DE 2026.
+Circuito : SED 1835.
+Hora : 07:30 a 12:00 Hrs.
+Motivo : Mantenimiento de subestación de distribución.
+Zonas afectadas: Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:29 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:29</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5946&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9145cf8c249f86ef6270e01e56a12f1b3a2188eb8cf38b372c1998c2fd2f1962</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5947</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de subestación de distribución.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4486.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 22 DE JULIO DE 2026.
+Circuito : SED 4486.
+Hora : 07:30 a 12:00 Hrs.
+Motivo : Mantenimiento de subestación de distribución.
+Zonas afectadas: Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:30 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5947&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1d74dec2587e738ad1efe57ee4a5c0196ee6c5dde91c0c3892fe0e662d89a53f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa, Jacobo Hunter</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Arequipa: Casa Lago San José, Parque Industrial. Urbanizaciones del Distrito Jacobo Hunter: Cooperativa Riego Chili, Parque Industrial.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de punto caliente a salida del alimentador.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [410] LARA.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 22 DE JULIO DE 2026:
+Circuito : [410] LARA.
+Hora : 08:00 a 11:00 Hrs.
+Motivo : Subsanación de punto caliente a salida del alimentador.
+Zonas : Urbanizaciones del Distrito de Arequipa: Casa Lago San José, Parque Industrial. Urbanizaciones del Distrito Jacobo Hunter: Cooperativa Riego Chili, Parque Industrial.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 2343, 2969, 2533, 3701, 1880, 1622, 1369, 1497, 3446, 4044, 4173, 4468, 2375, 4665, 4682, 5180, 5272, 5037, 5397, 5396, 5395, 5398, 5399, 5629, 5299, 10323, 1553.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:22</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5942&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>66c9cd56cbce74366860a7a36ea0d8086cc1e8e1406f5344535eaeff414239b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5944</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cocachacra</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Desamparados, El Toro, La Pascana, Portal del Valle.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de transformador, conductor, crucetas, aisladores y podado de ramas de árboles cercanas a línea de media tensión).</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : El Fiscal desde BC - 380303.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 22 DE JULIO DE 2026:
+Circuito : El Fiscal desde BC - 380303.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de transformador, conductor, crucetas, aisladores y podado de ramas de árboles cercanas a línea de media tensión).
+Zonas afectadas: Urbanizaciones del distrito Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Desamparados, El Toro, La Pascana, Portal del Valle.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:23 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:23</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5944&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>be92ab824efff26e78993d4203683b0b8c1b44d818b0ed8294fc1671f59d5668</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5938</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Jahuay desde REC - 200452.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 24 DE JULIO DE 2026:
+Circuito : Jahuay desde REC - 200452.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas : Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:19 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:19</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5938&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>ab483a4e674f2dc992e3ea5bba15c7cf9005b1ad3e7d927bfe32def3546c3ba3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Colegio de Ingenieros, Docentes de La Católica, El Solar de Challapampa, La Libertad, Micaela Bastidas, Quinta Azores, Semi-Rural Pachacutec Grupo 14, 15, 16, 19, 23, 24, 25, 6, Tupac Amaru Zona B.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [701] PORTALES.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 24 DE JULIO DE 2026:
+Circuito : [701] PORTALES.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Colegio de Ingenieros, Docentes de La Católica, El Solar de Challapampa, La Libertad, Micaela Bastidas, Quinta Azores, Semi-Rural Pachacutec Grupo 14, 15, 16, 19, 23, 24, 25, 6, Tupac Amaru Zona B.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3743, 3742, 2908, 1623, 3430, 1671, 1773, 2893, 2972, 3610, 3611, 3631, 3912, 1560, 1700, 3822, 1624, 1531, 3600, 3202, 3200, 2812, 2486, 3207, 3400, 2422, 3726, 3201, 4149, 4293, 4545, 4568, 4577, 4825, 5058, 5184, 5289, 5291, 5004, 5504, 5510, 5576, 5588, 5565, 5956, 10191, 10194, 2978.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 20/07/2026 8:34 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026 8:34</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5948&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>0c7ca2b50a22aec22efeaed040cae1c148e06ac8432ac1f06394d35c7774cb82</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -801,7 +1534,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20 12:26:58</t>
+          <t>2026-07-21 12:02:05</t>
         </is>
       </c>
     </row>
@@ -825,7 +1558,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -837,7 +1570,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -849,7 +1582,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -897,7 +1630,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -909,7 +1642,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -921,7 +1654,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -948,7 +1681,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P12" headerRowCount="1">
-  <autoFilter ref="A1:P12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
+  <autoFilter ref="A1:P11"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,17 +593,17 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Samuel Pastor, de Samuel Pastor</t>
+          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, distrito de Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de distrito de Puyca</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Samuel Pastor: Balneario Agustino, La Marina, La Punta Vieja, La Punta Nueva Zona A.</t>
+          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Urbanizaciones del distrito de distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión.</t>
+          <t>Subsanación de deficiencias en atención al procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Costanera desde CC - 400403.</t>
+          <t>Circuito : [70] COTAHUASI.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,92 +636,8 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>9120, 9303, 9107, 9074, 9281, 9137.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 20 DE JULIO DE 2026:
-Circuito : Costanera desde CC - 400403.
-Hora : 09:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Samuel Pastor: Balneario Agustino, La Marina, La Punta Vieja, La Punta Nueva Zona A.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9120, 9303, 9107, 9074, 9281, 9137.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:20 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:20</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5939&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>caed7f7a96bb0aa7b9ba53ee29b45d62d4c60cb77a2020643fd4d79148142bee</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, distrito de Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de distrito de Puyca</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Urbanizaciones del distrito de distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [70] COTAHUASI.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 21 DE JULIO DE 2026:
@@ -732,80 +648,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:21 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:21</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5941&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>171bf9e18a935a35b37acbd27c2b7b0ca08d1a132ff039e83557187ec97ababf</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5940</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Mariano Melgar, de Mariano Melgar</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>AAHH Berlín, Asoc. de Vivienda Pequeños talleres Sr. De los Milagros, P.J. El Mirador Zona I, P.J. El Mirador Zona II, AA.HH. Pueblo Libre, Los Ángeles, PP.JJ. Cerrito Belén (Distrito de Mariano Melgar).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento N° 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Galaxia desde EMT 16413.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>4049, 4772, 3641, 3642, 3375, 3376, 3643, 3354.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 21 DE JULIO DE 2026.
@@ -816,80 +732,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4049, 4772, 3641, 3642, 3375, 3376, 3643, 3354.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:20</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5940&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>7f521b7b6bc216443402b78589f8dc0584b7b7398729e30bc6b3b711b96147a9</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5945</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Majes, de Majes</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Majes: El Pedregal - Los Molles.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de retenida y podado de ramas de árboles cercanas a línea de media tensión).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Laive desde CC - 200497.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6007, 6032, 6031, 6030.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -900,80 +816,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6007, 6032, 6031, 6030.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:24</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5945&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>ab2a4dcb3320cd2828c53623653f4f08580b31965fd0b56634a413e2e7d1dfec</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5943</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Quilca, Samuel Pastor, de Quilca, de Samuel Pastor</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Quilca: Ampliación La Caleta, El Mirador, La Caleta de Quilca, Las Higueritas, Playa San Marino, Pueblo de Quilca. Urbanizaciones del distrito de Samuel Pastor: Las Cuevas, Los Cerrillos Zona III.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento N°228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Costanera desde SF6 - 200527.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -984,76 +900,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:22</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5943&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>07c7447fc49fb30b7c52bd38145adb1948a3043fd65a5f3f78ab4dd5fad59c83</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5946</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación de distribución.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1835</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026.
@@ -1063,76 +979,76 @@
 Zonas afectadas: Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:29</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5946&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>9145cf8c249f86ef6270e01e56a12f1b3a2188eb8cf38b372c1998c2fd2f1962</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5947</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación de distribución.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4486.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026.
@@ -1142,76 +1058,76 @@
 Zonas afectadas: Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:30 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:30</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5947&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>1d74dec2587e738ad1efe57ee4a5c0196ee6c5dde91c0c3892fe0e662d89a53f</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5942</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa, Jacobo Hunter</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Arequipa: Casa Lago San José, Parque Industrial. Urbanizaciones del Distrito Jacobo Hunter: Cooperativa Riego Chili, Parque Industrial.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Subsanación de punto caliente a salida del alimentador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : [410] LARA.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -1222,80 +1138,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 2343, 2969, 2533, 3701, 1880, 1622, 1369, 1497, 3446, 4044, 4173, 4468, 2375, 4665, 4682, 5180, 5272, 5037, 5397, 5396, 5395, 5398, 5399, 5629, 5299, 10323, 1553.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:22</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5942&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>66c9cd56cbce74366860a7a36ea0d8086cc1e8e1406f5344535eaeff414239b6</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5944</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cocachacra</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Desamparados, El Toro, La Pascana, Portal del Valle.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de transformador, conductor, crucetas, aisladores y podado de ramas de árboles cercanas a línea de media tensión).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : El Fiscal desde BC - 380303.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -1306,80 +1222,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:23 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:23</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5944&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>be92ab824efff26e78993d4203683b0b8c1b44d818b0ed8294fc1671f59d5668</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>5938</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>24/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Mariscal Cáceres, de Mariscal Cáceres</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : Jahuay desde REC - 200452.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 24 DE JULIO DE 2026:
@@ -1390,76 +1306,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:19</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5938&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>ab483a4e674f2dc992e3ea5bba15c7cf9005b1ad3e7d927bfe32def3546c3ba3</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>5948</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>24/07/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Colegio de Ingenieros, Docentes de La Católica, El Solar de Challapampa, La Libertad, Micaela Bastidas, Quinta Azores, Semi-Rural Pachacutec Grupo 14, 15, 16, 19, 23, 24, 25, 6, Tupac Amaru Zona B.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : [701] PORTALES.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 24 DE JULIO DE 2026:
@@ -1470,30 +1386,30 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3743, 3742, 2908, 1623, 3430, 1671, 1773, 2893, 2972, 3610, 3611, 3631, 3912, 1560, 1700, 3822, 1624, 1531, 3600, 3202, 3200, 2812, 2486, 3207, 3400, 2422, 3726, 3201, 4149, 4293, 4545, 4568, 4577, 4825, 5058, 5184, 5289, 5291, 5004, 5504, 5510, 5576, 5588, 5565, 5956, 10191, 10194, 2978.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:34 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:34</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5948&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>0c7ca2b50a22aec22efeaed040cae1c148e06ac8432ac1f06394d35c7774cb82</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1534,7 +1450,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21 12:02:05</t>
+          <t>2026-07-22 12:05:37</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1474,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1486,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1498,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1570,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1597,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
-  <autoFilter ref="A1:P11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
+  <autoFilter ref="A1:P9"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Alca, Cotahuasi, Huaynacotas, Pampamarca, Tomepampa, distrito de Puyca, de Alca, de Cotahuasi, de Huaynacotas, de Pampamarca, de Tomepampa, de distrito de Puyca</t>
+          <t>Majes, de Majes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Urbanizaciones del distrito de distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.</t>
+          <t>Urbanizaciones del distrito de Majes: El Pedregal - Los Molles.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Subsanación de deficiencias en atención al procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de retenida y podado de ramas de árboles cercanas a línea de media tensión).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [70] COTAHUASI.</t>
+          <t>Circuito : Laive desde CC - 200497.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,176 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>6007, 6032, 6031, 6030.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 21 DE JULIO DE 2026:
-Circuito : [70] COTAHUASI.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Subsanación de deficiencias en atención al procedimiento N° 014-2022-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas : Urbanizaciones del distrito de Alca: La Lucha, Yumasca, Alca, Ayahuasi, Cahuana, Huillac, Ticnay. Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Huaynacotas: Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa. Urbanizaciones del distrito de distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173, 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7308, 7309, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7733, 7728, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:21 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:21</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5941&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>171bf9e18a935a35b37acbd27c2b7b0ca08d1a132ff039e83557187ec97ababf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5940</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mariano Melgar, de Mariano Melgar</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>AAHH Berlín, Asoc. de Vivienda Pequeños talleres Sr. De los Milagros, P.J. El Mirador Zona I, P.J. El Mirador Zona II, AA.HH. Pueblo Libre, Los Ángeles, PP.JJ. Cerrito Belén (Distrito de Mariano Melgar).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al procedimiento N° 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Galaxia desde EMT 16413.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4049, 4772, 3641, 3642, 3375, 3376, 3643, 3354.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 21 DE JULIO DE 2026.
-Circuito : Galaxia desde EMT 16413.
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al procedimiento N° 228-2009-OS/CD Osinergmin y otros mantenimientos de redes de media tensión.
-Zonas afectadas: AAHH Berlín, Asoc. de Vivienda Pequeños talleres Sr. De los Milagros, P.J. El Mirador Zona I, P.J. El Mirador Zona II, AA.HH. Pueblo Libre, Los Ángeles, PP.JJ. Cerrito Belén (Distrito de Mariano Melgar).
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4049, 4772, 3641, 3642, 3375, 3376, 3643, 3354.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:20 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:20</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5940&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>7f521b7b6bc216443402b78589f8dc0584b7b7398729e30bc6b3b711b96147a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5945</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Majes, de Majes</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Majes: El Pedregal - Los Molles.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de retenida y podado de ramas de árboles cercanas a línea de media tensión).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Laive desde CC - 200497.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6007, 6032, 6031, 6030.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -816,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6007, 6032, 6031, 6030.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:24</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5945&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>ab2a4dcb3320cd2828c53623653f4f08580b31965fd0b56634a413e2e7d1dfec</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5943</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Quilca, Samuel Pastor, de Quilca, de Samuel Pastor</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Quilca: Ampliación La Caleta, El Mirador, La Caleta de Quilca, Las Higueritas, Playa San Marino, Pueblo de Quilca. Urbanizaciones del distrito de Samuel Pastor: Las Cuevas, Los Cerrillos Zona III.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento N°228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Costanera desde SF6 - 200527.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -900,76 +736,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:22</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5943&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>07c7447fc49fb30b7c52bd38145adb1948a3043fd65a5f3f78ab4dd5fad59c83</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5946</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación de distribución.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1835</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026.
@@ -979,76 +815,76 @@
 Zonas afectadas: Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:29</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5946&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>9145cf8c249f86ef6270e01e56a12f1b3a2188eb8cf38b372c1998c2fd2f1962</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5947</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de subestación de distribución.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4486.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026.
@@ -1058,76 +894,76 @@
 Zonas afectadas: Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:30 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:30</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5947&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>1d74dec2587e738ad1efe57ee4a5c0196ee6c5dde91c0c3892fe0e662d89a53f</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5942</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa, Jacobo Hunter</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Arequipa: Casa Lago San José, Parque Industrial. Urbanizaciones del Distrito Jacobo Hunter: Cooperativa Riego Chili, Parque Industrial.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Subsanación de punto caliente a salida del alimentador.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : [410] LARA.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -1138,80 +974,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 2343, 2969, 2533, 3701, 1880, 1622, 1369, 1497, 3446, 4044, 4173, 4468, 2375, 4665, 4682, 5180, 5272, 5037, 5397, 5396, 5395, 5398, 5399, 5629, 5299, 10323, 1553.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:22</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5942&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>66c9cd56cbce74366860a7a36ea0d8086cc1e8e1406f5344535eaeff414239b6</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5944</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cocachacra</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Desamparados, El Toro, La Pascana, Portal del Valle.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de transformador, conductor, crucetas, aisladores y podado de ramas de árboles cercanas a línea de media tensión).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : El Fiscal desde BC - 380303.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 22 DE JULIO DE 2026:
@@ -1222,80 +1058,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:23 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:23</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5944&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>be92ab824efff26e78993d4203683b0b8c1b44d818b0ed8294fc1671f59d5668</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5938</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>24/07/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Mariscal Cáceres, de Mariscal Cáceres</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : Jahuay desde REC - 200452.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 24 DE JULIO DE 2026:
@@ -1306,76 +1142,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:19</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5938&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ab483a4e674f2dc992e3ea5bba15c7cf9005b1ad3e7d927bfe32def3546c3ba3</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5948</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>24/07/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Colegio de Ingenieros, Docentes de La Católica, El Solar de Challapampa, La Libertad, Micaela Bastidas, Quinta Azores, Semi-Rural Pachacutec Grupo 14, 15, 16, 19, 23, 24, 25, 6, Tupac Amaru Zona B.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : [701] PORTALES.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 24 DE JULIO DE 2026:
@@ -1386,30 +1222,30 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3743, 3742, 2908, 1623, 3430, 1671, 1773, 2893, 2972, 3610, 3611, 3631, 3912, 1560, 1700, 3822, 1624, 1531, 3600, 3202, 3200, 2812, 2486, 3207, 3400, 2422, 3726, 3201, 4149, 4293, 4545, 4568, 4577, 4825, 5058, 5184, 5289, 5291, 5004, 5504, 5510, 5576, 5588, 5565, 5956, 10191, 10194, 2978.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:34 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:34</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5948&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>0c7ca2b50a22aec22efeaed040cae1c148e06ac8432ac1f06394d35c7774cb82</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1450,7 +1286,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 12:05:37</t>
+          <t>2026-07-23 12:04:14</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1310,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1322,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1334,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1406,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1433,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P9" headerRowCount="1">
-  <autoFilter ref="A1:P9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Majes, de Majes</t>
+          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Majes: El Pedregal - Los Molles.</t>
+          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (cambio de postes, cambio de retenida y podado de ramas de árboles cercanas a línea de media tensión).</t>
+          <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Laive desde CC - 200497.</t>
+          <t>Circuito : Jahuay desde REC - 200452.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,500 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>6007, 6032, 6031, 6030.</t>
+          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 22 DE JULIO DE 2026:
-Circuito : Laive desde CC - 200497.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de postes, cambio de retenida y podado de ramas de árboles cercanas a línea de media tensión).
-Zonas afectadas: Urbanizaciones del distrito de Majes: El Pedregal - Los Molles.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 6007, 6032, 6031, 6030.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:24 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:24</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5945&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>ab2a4dcb3320cd2828c53623653f4f08580b31965fd0b56634a413e2e7d1dfec</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5943</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Quilca, Samuel Pastor, de Quilca, de Samuel Pastor</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Quilca: Ampliación La Caleta, El Mirador, La Caleta de Quilca, Las Higueritas, Playa San Marino, Pueblo de Quilca. Urbanizaciones del distrito de Samuel Pastor: Las Cuevas, Los Cerrillos Zona III.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al procedimiento N°228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Costanera desde SF6 - 200527.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 22 DE JULIO DE 2026:
-Circuito : Costanera desde SF6 - 200527.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al procedimiento N°228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Quilca: Ampliación La Caleta, El Mirador, La Caleta de Quilca, Las Higueritas, Playa San Marino, Pueblo de Quilca. Urbanizaciones del distrito de Samuel Pastor: Las Cuevas, Los Cerrillos Zona III.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10112, 9145, 9256, 9201, 9338, 9300, 9294, 9351, 9239, 10026, 10027, 9241, 9242, 9243, 9244, 9245, 9240, 9091, 9136, 9309, 9254, 9132, 9093, 9367, 9133.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:22</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5943&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>07c7447fc49fb30b7c52bd38145adb1948a3043fd65a5f3f78ab4dd5fad59c83</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5946</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de subestación de distribución.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1835</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 22 DE JULIO DE 2026.
-Circuito : SED 1835.
-Hora : 07:30 a 12:00 Hrs.
-Motivo : Mantenimiento de subestación de distribución.
-Zonas afectadas: Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:29 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:29</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5946&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9145cf8c249f86ef6270e01e56a12f1b3a2188eb8cf38b372c1998c2fd2f1962</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5947</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de subestación de distribución.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4486.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 22 DE JULIO DE 2026.
-Circuito : SED 4486.
-Hora : 07:30 a 12:00 Hrs.
-Motivo : Mantenimiento de subestación de distribución.
-Zonas afectadas: Asoc. Eptasa, Av. Italia (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:30 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:30</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5947&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1d74dec2587e738ad1efe57ee4a5c0196ee6c5dde91c0c3892fe0e662d89a53f</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5942</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Arequipa, de Arequipa, Jacobo Hunter</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Arequipa: Casa Lago San José, Parque Industrial. Urbanizaciones del Distrito Jacobo Hunter: Cooperativa Riego Chili, Parque Industrial.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de punto caliente a salida del alimentador.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [410] LARA.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 22 DE JULIO DE 2026:
-Circuito : [410] LARA.
-Hora : 08:00 a 11:00 Hrs.
-Motivo : Subsanación de punto caliente a salida del alimentador.
-Zonas : Urbanizaciones del Distrito de Arequipa: Casa Lago San José, Parque Industrial. Urbanizaciones del Distrito Jacobo Hunter: Cooperativa Riego Chili, Parque Industrial.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 2343, 2969, 2533, 3701, 1880, 1622, 1369, 1497, 3446, 4044, 4173, 4468, 2375, 4665, 4682, 5180, 5272, 5037, 5397, 5396, 5395, 5398, 5399, 5629, 5299, 10323, 1553.</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:22 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:22</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5942&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>66c9cd56cbce74366860a7a36ea0d8086cc1e8e1406f5344535eaeff414239b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cocachacra</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Desamparados, El Toro, La Pascana, Portal del Valle.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de transformador, conductor, crucetas, aisladores y podado de ramas de árboles cercanas a línea de media tensión).</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : El Fiscal desde BC - 380303.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 22 DE JULIO DE 2026:
-Circuito : El Fiscal desde BC - 380303.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de transformador, conductor, crucetas, aisladores y podado de ramas de árboles cercanas a línea de media tensión).
-Zonas afectadas: Urbanizaciones del distrito Cocachacra: Anexo El Carrizal, Anexo El Dique, Anexo Quelgua Grande, Ayanquera, Caraquen, Desamparados, El Toro, La Pascana, Portal del Valle.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8283, 8263, 8436, 8276, 8264, 8303, 8304, 8305, 8542, 8324, 8306, 8318, 8319, 8320, 8737, 8598, 8618, 8340, 8508, 8312, 8313, 8314, 8315, 8316, 8317, 8339, 8372, 8378.</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:23 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:23</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5944&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>be92ab824efff26e78993d4203683b0b8c1b44d818b0ed8294fc1671f59d5668</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>24/07/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Jahuay desde REC - 200452.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 24 DE JULIO DE 2026:
@@ -1142,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:19 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:19</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5938&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>ab483a4e674f2dc992e3ea5bba15c7cf9005b1ad3e7d927bfe32def3546c3ba3</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5948</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>24/07/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Colegio de Ingenieros, Docentes de La Católica, El Solar de Challapampa, La Libertad, Micaela Bastidas, Quinta Azores, Semi-Rural Pachacutec Grupo 14, 15, 16, 19, 23, 24, 25, 6, Tupac Amaru Zona B.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [701] PORTALES.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 24 DE JULIO DE 2026:
@@ -1222,30 +732,30 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3743, 3742, 2908, 1623, 3430, 1671, 1773, 2893, 2972, 3610, 3611, 3631, 3912, 1560, 1700, 3822, 1624, 1531, 3600, 3202, 3200, 2812, 2486, 3207, 3400, 2422, 3726, 3201, 4149, 4293, 4545, 4568, 4577, 4825, 5058, 5184, 5289, 5291, 5004, 5504, 5510, 5576, 5588, 5565, 5956, 10191, 10194, 2978.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 20/07/2026 8:34 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>20/07/2026 8:34</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5948&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>0c7ca2b50a22aec22efeaed040cae1c148e06ac8432ac1f06394d35c7774cb82</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1286,7 +796,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23 12:04:14</t>
+          <t>2026-07-24 11:57:11</t>
         </is>
       </c>
     </row>
@@ -1310,7 +820,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -1322,7 +832,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -1334,7 +844,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1406,7 +916,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1433,7 +943,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
+  <autoFilter ref="A1:P5"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -754,8 +754,176 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Arqueta, Asociación Policial Campo Verde, La Libertad, Residencial Monte Bello, Urbanización Quinta Luisa, Veracruz, Vía Evitamiento.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (reubicación de línea de media tensión).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Cerro Colorado desde REC - 070206.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3965, 3924, 3964, 3966, 3967, 1672, 3909, 1515, 3908, 3741, 2957, 3109, 4012, 3776, 2956, 1929, 1248, 2085, 2984, 3323, 2106, 2048, 2789, 1467, 1251, 3710, 4624, 5066, 2155, 4868, 1973, 4663, 3971, 10223, 4017, 4546, 3132, 3126, 1799, 4008, 3753, 4305, 4326, 4395, 5966, 4394, 4578, 5296, 5074, 4915, 5505, 5425, 5196, 5631, 5416, 5675, 5713, 5884, 5891, 10050, 10262.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 26 DE JULIO DE 2026:
+Circuito : Cerro Colorado desde REC - 070206.
+Hora : 06:00 a 13:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (reubicación de línea de media tensión).
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Arqueta, Asociación Policial Campo Verde, La Libertad, Residencial Monte Bello, Urbanización Quinta Luisa, Veracruz, Vía Evitamiento.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3965, 3924, 3964, 3966, 3967, 1672, 3909, 1515, 3908, 3741, 2957, 3109, 4012, 3776, 2956, 1929, 1248, 2085, 2984, 3323, 2106, 2048, 2789, 1467, 1251, 3710, 4624, 5066, 2155, 4868, 1973, 4663, 3971, 10223, 4017, 4546, 3132, 3126, 1799, 4008, 3753, 4305, 4326, 4395, 5966, 4394, 4578, 5296, 5074, 4915, 5505, 5425, 5196, 5631, 5416, 5675, 5713, 5884, 5891, 10050, 10262.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 24/07/2026 8:08 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>24/07/2026 8:08</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5949&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2a83d374b002c0d22431a259cf9396b4bb5271d05f3bc96926cdbdf3707b7e7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5950</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, Viraco, Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas, Salamanca, Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>PROVINCIA DE CASTILLA: Distritos de Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, y Viraco. PROVINCIA DE CAYLLOMA: Distritos de Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas y Salamanca. PROVINCIA DE AREQUIPA: Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>CORTE PROGRAMADO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ELECTRICA DEL SUR OESTE S. A., comunica a sus usuarios y público en general que debido al CORTE PROGRAMADO POR MANTENIMIENTO DE REDES EN: SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV, se verá obligada a efectuar la suspensión temporal del suministro eléctrico el día domingo 02 de agosto de 2026, en el horario de 07:30 a 15:30 horas.
+MOTIVO: Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV
+Las zonas afectadas por el corte efectuado por SEAL serán:
+PROVINCIA DE CASTILLA:
+Distritos de Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, y Viraco.
+PROVINCIA DE CAYLLOMA:
+Distritos de Majes, Lluclla
+PROVINCIA DE CONDESUYOS
+Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas y Salamanca.
+PROVINCIA DE AREQUIPA:
+Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 24/07/2026 17:20 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>24/07/2026 17:20</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5950&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>59ef5263d48276a9271ed6f0b5d34f40412c0242e36ee9c074e200e0c85bf803</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -796,7 +964,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24 11:57:11</t>
+          <t>2026-07-25 11:38:20</t>
         </is>
       </c>
     </row>
@@ -820,7 +988,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -832,7 +1000,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -844,7 +1012,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -892,7 +1060,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -904,7 +1072,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -916,7 +1084,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -943,7 +1111,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
-  <autoFilter ref="A1:P5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mariscal Cáceres, de Mariscal Cáceres</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.</t>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Arqueta, Asociación Policial Campo Verde, La Libertad, Residencial Monte Bello, Urbanización Quinta Luisa, Veracruz, Vía Evitamiento.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
+          <t>Mantenimiento de redes de media tensión (reubicación de línea de media tensión).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Jahuay desde REC - 200452.</t>
+          <t>Circuito : Cerro Colorado desde REC - 070206.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,174 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
+          <t>3965, 3924, 3964, 3966, 3967, 1672, 3909, 1515, 3908, 3741, 2957, 3109, 4012, 3776, 2956, 1929, 1248, 2085, 2984, 3323, 2106, 2048, 2789, 1467, 1251, 3710, 4624, 5066, 2155, 4868, 1973, 4663, 3971, 10223, 4017, 4546, 3132, 3126, 1799, 4008, 3753, 4305, 4326, 4395, 5966, 4394, 4578, 5296, 5074, 4915, 5505, 5425, 5196, 5631, 5416, 5675, 5713, 5884, 5891, 10050, 10262.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 24 DE JULIO DE 2026:
-Circuito : Jahuay desde REC - 200452.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas : Urbanizaciones del distrito de Mariscal Cáceres: A.H. Jahuay, San Isidro, Santa Elizabeth, Villa Hermosa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9269, 9268, 5271, 9327, 9321, 9324, 9215, 9335, 9211, 9345, 9378, 9280, 9384, 9392, 9405, 9237, 9236, 9235, 9248, 9247, 9203, 9202, 10281, 10291.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:19 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:19</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5938&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>ab483a4e674f2dc992e3ea5bba15c7cf9005b1ad3e7d927bfe32def3546c3ba3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5948</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/07/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Colegio de Ingenieros, Docentes de La Católica, El Solar de Challapampa, La Libertad, Micaela Bastidas, Quinta Azores, Semi-Rural Pachacutec Grupo 14, 15, 16, 19, 23, 24, 25, 6, Tupac Amaru Zona B.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [701] PORTALES.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 24 DE JULIO DE 2026:
-Circuito : [701] PORTALES.
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Subsanación de deficiencias en atención al procedimiento 228-2009-OS/CD Osinergmin y otros mantenimientos de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Colegio de Ingenieros, Docentes de La Católica, El Solar de Challapampa, La Libertad, Micaela Bastidas, Quinta Azores, Semi-Rural Pachacutec Grupo 14, 15, 16, 19, 23, 24, 25, 6, Tupac Amaru Zona B.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 3743, 3742, 2908, 1623, 3430, 1671, 1773, 2893, 2972, 3610, 3611, 3631, 3912, 1560, 1700, 3822, 1624, 1531, 3600, 3202, 3200, 2812, 2486, 3207, 3400, 2422, 3726, 3201, 4149, 4293, 4545, 4568, 4577, 4825, 5058, 5184, 5289, 5291, 5004, 5504, 5510, 5576, 5588, 5565, 5956, 10191, 10194, 2978.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 20/07/2026 8:34 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026 8:34</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5948&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>0c7ca2b50a22aec22efeaed040cae1c148e06ac8432ac1f06394d35c7774cb82</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5949</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Arqueta, Asociación Policial Campo Verde, La Libertad, Residencial Monte Bello, Urbanización Quinta Luisa, Veracruz, Vía Evitamiento.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (reubicación de línea de media tensión).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Cerro Colorado desde REC - 070206.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3965, 3924, 3964, 3966, 3967, 1672, 3909, 1515, 3908, 3741, 2957, 3109, 4012, 3776, 2956, 1929, 1248, 2085, 2984, 3323, 2106, 2048, 2789, 1467, 1251, 3710, 4624, 5066, 2155, 4868, 1973, 4663, 3971, 10223, 4017, 4546, 3132, 3126, 1799, 4008, 3753, 4305, 4326, 4395, 5966, 4394, 4578, 5296, 5074, 4915, 5505, 5425, 5196, 5631, 5416, 5675, 5713, 5884, 5891, 10050, 10262.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 26 DE JULIO DE 2026:
@@ -816,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3965, 3924, 3964, 3966, 3967, 1672, 3909, 1515, 3908, 3741, 2957, 3109, 4012, 3776, 2956, 1929, 1248, 2085, 2984, 3323, 2106, 2048, 2789, 1467, 1251, 3710, 4624, 5066, 2155, 4868, 1973, 4663, 3971, 10223, 4017, 4546, 3132, 3126, 1799, 4008, 3753, 4305, 4326, 4395, 5966, 4394, 4578, 5296, 5074, 4915, 5505, 5425, 5196, 5631, 5416, 5675, 5713, 5884, 5891, 10050, 10262.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 24/07/2026 8:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>24/07/2026 8:08</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5949&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>2a83d374b002c0d22431a259cf9396b4bb5271d05f3bc96926cdbdf3707b7e7a</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5950</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, Viraco, Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas, Salamanca, Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>PROVINCIA DE CASTILLA: Distritos de Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, y Viraco. PROVINCIA DE CAYLLOMA: Distritos de Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas y Salamanca. PROVINCIA DE AREQUIPA: Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>CORTE PROGRAMADO</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>SOCIEDAD ELECTRICA DEL SUR OESTE S. A., comunica a sus usuarios y público en general que debido al CORTE PROGRAMADO POR MANTENIMIENTO DE REDES EN: SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV, se verá obligada a efectuar la suspensión temporal del suministro eléctrico el día domingo 02 de agosto de 2026, en el horario de 07:30 a 15:30 horas.
 MOTIVO: Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV
@@ -900,30 +736,30 @@
 Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 24/07/2026 17:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>24/07/2026 17:20</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5950&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>59ef5263d48276a9271ed6f0b5d34f40412c0242e36ee9c074e200e0c85bf803</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P5"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -964,7 +800,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25 11:38:20</t>
+          <t>2026-07-26 11:39:28</t>
         </is>
       </c>
     </row>
@@ -988,7 +824,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1000,7 +836,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -1012,7 +848,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -1084,7 +920,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1111,7 +947,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26 11:39:28</t>
+          <t>2026-07-27 13:22:48</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P2" headerRowCount="1">
+  <autoFilter ref="A1:P2"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,135 +593,51 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, Viraco, Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas, Salamanca, Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Arqueta, Asociación Policial Campo Verde, La Libertad, Residencial Monte Bello, Urbanización Quinta Luisa, Veracruz, Vía Evitamiento.</t>
+          <t>PROVINCIA DE CASTILLA: Distritos de Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, y Viraco. PROVINCIA DE CAYLLOMA: Distritos de Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas y Salamanca. PROVINCIA DE AREQUIPA: Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (reubicación de línea de media tensión).</t>
+          <t>Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Cerro Colorado desde REC - 070206.</t>
+          <t>SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>3965, 3924, 3964, 3966, 3967, 1672, 3909, 1515, 3908, 3741, 2957, 3109, 4012, 3776, 2956, 1929, 1248, 2085, 2984, 3323, 2106, 2048, 2789, 1467, 1251, 3710, 4624, 5066, 2155, 4868, 1973, 4663, 3971, 10223, 4017, 4546, 3132, 3126, 1799, 4008, 3753, 4305, 4326, 4395, 5966, 4394, 4578, 5296, 5074, 4915, 5505, 5425, 5196, 5631, 5416, 5675, 5713, 5884, 5891, 10050, 10262.</t>
-        </is>
-      </c>
+          <t>CORTE PROGRAMADO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 26 DE JULIO DE 2026:
-Circuito : Cerro Colorado desde REC - 070206.
-Hora : 06:00 a 13:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (reubicación de línea de media tensión).
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Arqueta, Asociación Policial Campo Verde, La Libertad, Residencial Monte Bello, Urbanización Quinta Luisa, Veracruz, Vía Evitamiento.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3965, 3924, 3964, 3966, 3967, 1672, 3909, 1515, 3908, 3741, 2957, 3109, 4012, 3776, 2956, 1929, 1248, 2085, 2984, 3323, 2106, 2048, 2789, 1467, 1251, 3710, 4624, 5066, 2155, 4868, 1973, 4663, 3971, 10223, 4017, 4546, 3132, 3126, 1799, 4008, 3753, 4305, 4326, 4395, 5966, 4394, 4578, 5296, 5074, 4915, 5505, 5425, 5196, 5631, 5416, 5675, 5713, 5884, 5891, 10050, 10262.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 24/07/2026 8:08 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>24/07/2026 8:08</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5949&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>2a83d374b002c0d22431a259cf9396b4bb5271d05f3bc96926cdbdf3707b7e7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5950</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, Viraco, Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas, Salamanca, Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>PROVINCIA DE CASTILLA: Distritos de Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, y Viraco. PROVINCIA DE CAYLLOMA: Distritos de Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas y Salamanca. PROVINCIA DE AREQUIPA: Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>CORTE PROGRAMADO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>SOCIEDAD ELECTRICA DEL SUR OESTE S. A., comunica a sus usuarios y público en general que debido al CORTE PROGRAMADO POR MANTENIMIENTO DE REDES EN: SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV, se verá obligada a efectuar la suspensión temporal del suministro eléctrico el día domingo 02 de agosto de 2026, en el horario de 07:30 a 15:30 horas.
 MOTIVO: Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV
@@ -736,30 +652,30 @@
 Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 24/07/2026 17:20 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>24/07/2026 17:20</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5950&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>59ef5263d48276a9271ed6f0b5d34f40412c0242e36ee9c074e200e0c85bf803</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -800,7 +716,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27 13:22:48</t>
+          <t>2026-07-28 12:15:53</t>
         </is>
       </c>
     </row>
@@ -824,7 +740,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -836,7 +752,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -848,7 +764,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -920,7 +836,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -947,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28 12:15:53</t>
+          <t>2026-07-29 12:22:58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 12:22:58</t>
+          <t>2026-07-30 12:06:13</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30 12:06:13</t>
+          <t>2026-07-31 12:19:33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 12:19:33</t>
+          <t>2026-08-01 11:36:28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 11:36:28</t>
+          <t>2026-08-02 11:36:06</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P2" headerRowCount="1">
-  <autoFilter ref="A1:P2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
+  <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -674,8 +674,410 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4489.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 04 DE AGOSTO DE 2026.
+Circuito : SED 4489.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Mz. A-B de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 03/08/2026 5:31 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 5:31</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5954&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>8f27dbfbe87b45f993fcab09e843d1d65a12ae4e8e25de5ca41bfbc1966421f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5955</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Mz. B-C-I-J de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4175.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 04 DE AGOSTO DE 2026.
+Circuito : SED 4175.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Mz. B-C-I-J de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 03/08/2026 5:31 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 5:31</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5955&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>75068fd0dd03b49f3415066b335c0a3eca1649e22c9a3b74232706bf5cbff7f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5953</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (instalación de pararrayos, cambio de aisladores, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>SET : [70] COTAHUASI.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 05 DE AGOSTO DE 2026:
+SET : [70] COTAHUASI.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (instalación de pararrayos, cambio de aisladores, podado de árboles).
+Zonas afectadas: Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 03/08/2026 5:30 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 5:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5953&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3b689bf202fbc04e9bf11cdf8550e15039bae5c3e4b21d1194c709783045de95</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones: Ampliación la Negrita, La Victoria, El Carmen, Cesar Vallejo.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Instalación de poste y nueva subestación de distribución.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : La Isla desde la celda salida de la SED N° 4797.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+MIÉRCOLES, 05 DE AGOSTO DE 2026:
+Circuito : La Isla desde la celda salida de la SED N° 4797.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Instalación de poste y nueva subestación de distribución.
+Zonas afectadas: Urbanizaciones: Ampliación la Negrita, La Victoria, El Carmen, Cesar Vallejo.
+Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 4751, 4797, 2374, 1139, 2373, 2371, 2357, 3387, 2369, 4309, 1141, 4297, 1140, 2368, 2367, 10154, 5932, 5683.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 03/08/2026 5:28 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 5:28</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5951&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>439f2350120a8fe20215ef031c8dfc0d1205298f5f5c44c7f43bae987f94a1f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de estructura de media tensión, subsanación de deficiencias.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Las Peñas desde BC - 041005.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 05 DE AGOSTO DE 2026:
+Circuito : Las Peñas desde BC - 041005.
+Hora : 08:00 a 12:00 Hrs.
+Motivo : Cambio de estructura de media tensión, subsanación de deficiencias.
+Zonas afectadas: Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 03/08/2026 5:29 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026 5:29</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5952&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>884db480bd9d2359d94072e5f0c4e63d314be040013da98436065393000cdf6c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -716,7 +1118,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02 11:36:06</t>
+          <t>2026-08-03 13:21:31</t>
         </is>
       </c>
     </row>
@@ -740,7 +1142,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -752,7 +1154,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -764,7 +1166,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -812,7 +1214,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -824,7 +1226,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -836,7 +1238,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -863,7 +1265,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
-  <autoFilter ref="A1:P7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,135 +593,51 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, Viraco, Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas, Salamanca, Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIA DE CASTILLA: Distritos de Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, y Viraco. PROVINCIA DE CAYLLOMA: Distritos de Majes, Lluclla PROVINCIA DE CONDESUYOS Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas y Salamanca. PROVINCIA DE AREQUIPA: Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
+          <t>Mz. A-B de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV</t>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV</t>
+          <t>Circuito : SED 4489.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>CORTE PROGRAMADO</t>
+          <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>SOCIEDAD ELECTRICA DEL SUR OESTE S. A., comunica a sus usuarios y público en general que debido al CORTE PROGRAMADO POR MANTENIMIENTO DE REDES EN: SET MAJES CON SUS SALIDAS EN 22KV, SET PIONERO CON SUS SALIDAS EN 22KV, CELDA DE SALIDAD DE LINEA L-6550, LÍNEA 60KV L-6550 MAJES-CORIRE-CHUQUIBAMBA, SET CORIRE (PUNTA COLORADA) CON SUS SALIDAS EN 13.2KV, SET CHUQUIBAMBA CON SUS SALIDAS EN 22.9KV, se verá obligada a efectuar la suspensión temporal del suministro eléctrico el día domingo 02 de agosto de 2026, en el horario de 07:30 a 15:30 horas.
-MOTIVO: Pruebas a transformador de potencia, mantenimiento de patio de llaves y mantenimiento en pórtico en 60KV
-Las zonas afectadas por el corte efectuado por SEAL serán:
-PROVINCIA DE CASTILLA:
-Distritos de Corire- Aplao (la capital), Huancarqui, Machaguay, Pampacolca, Tipán, Uñón, Uraca, y Viraco.
-PROVINCIA DE CAYLLOMA:
-Distritos de Majes, Lluclla
-PROVINCIA DE CONDESUYOS
-Distritos de Iray, Chuquibamba, Andaray, Yanaquihua, Chichas y Salamanca.
-PROVINCIA DE AREQUIPA:
-Distritos de Santa Rita de Siguas, San Juan de Siguas, Santa Isabel de Siguas.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 24/07/2026 17:20 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>24/07/2026 17:20</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5950&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>59ef5263d48276a9271ed6f0b5d34f40412c0242e36ee9c074e200e0c85bf803</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5954</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A-B de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4489.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 04 DE AGOSTO DE 2026.
@@ -731,76 +647,76 @@
 Zonas afectadas: Mz. A-B de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:31 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:31</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5954&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>8f27dbfbe87b45f993fcab09e843d1d65a12ae4e8e25de5ca41bfbc1966421f4</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5955</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Mz. B-C-I-J de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4175.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 04 DE AGOSTO DE 2026.
@@ -810,80 +726,80 @@
 Zonas afectadas: Mz. B-C-I-J de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:31 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:31</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5955&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>75068fd0dd03b49f3415066b335c0a3eca1649e22c9a3b74232706bf5cbff7f2</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5953</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (instalación de pararrayos, cambio de aisladores, podado de árboles).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 05 DE AGOSTO DE 2026:
@@ -894,72 +810,72 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:30 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:30</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5953&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>3b689bf202fbc04e9bf11cdf8550e15039bae5c3e4b21d1194c709783045de95</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5951</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones: Ampliación la Negrita, La Victoria, El Carmen, Cesar Vallejo.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Instalación de poste y nueva subestación de distribución.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Isla desde la celda salida de la SED N° 4797.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIÉRCOLES, 05 DE AGOSTO DE 2026:
@@ -970,80 +886,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 4751, 4797, 2374, 1139, 2373, 2371, 2357, 3387, 2369, 4309, 1141, 4297, 1140, 2368, 2367, 10154, 5932, 5683.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:28 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:28</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5951&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>439f2350120a8fe20215ef031c8dfc0d1205298f5f5c44c7f43bae987f94a1f1</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5952</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de estructura de media tensión, subsanación de deficiencias.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Peñas desde BC - 041005.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 05 DE AGOSTO DE 2026:
@@ -1054,30 +970,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:29</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5952&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>884db480bd9d2359d94072e5f0c4e63d314be040013da98436065393000cdf6c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P7"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1118,7 +1034,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03 13:21:31</t>
+          <t>2026-08-04 12:20:38</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1058,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1070,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1082,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1154,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1181,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
+  <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -992,8 +992,92 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5956</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Alto Selva Alegre, de Alto Selva Alegre</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Alto Selva Alegre: Chilina, San Lazaro.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (subsanación de deficiencias y desmontaje de red)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Independencia desde CC - 200188.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 07 DE AGOSTO DE 2026:
+Circuito : Independencia desde CC - 200188.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (subsanación de deficiencias y desmontaje de red)
+Zonas afectadas: Urbanizaciones del distrito de Alto Selva Alegre: Chilina, San Lazaro.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 04/08/2026 17:36 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 17:36</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5956&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6260ea7f29c9184ca598727d5f011c2569948c3377a0758a714df078063b6b3c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1034,7 +1118,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 12:20:38</t>
+          <t>2026-08-05 12:18:55</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1142,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1154,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1166,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1214,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1226,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1238,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1265,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P7" headerRowCount="1">
-  <autoFilter ref="A1:P7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Mz. A-B de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
+          <t>Mantenimiento de redes de media tensión (instalación de pararrayos, cambio de aisladores, podado de árboles).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 4489.</t>
+          <t>SET : [70] COTAHUASI.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,170 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 04 DE AGOSTO DE 2026.
-Circuito : SED 4489.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Mz. A-B de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 03/08/2026 5:31 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>03/08/2026 5:31</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5954&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>8f27dbfbe87b45f993fcab09e843d1d65a12ae4e8e25de5ca41bfbc1966421f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5955</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. B-C-I-J de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 4175.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 04 DE AGOSTO DE 2026.
-Circuito : SED 4175.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Mz. B-C-I-J de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 03/08/2026 5:31 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>03/08/2026 5:31</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5955&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>75068fd0dd03b49f3415066b335c0a3eca1649e22c9a3b74232706bf5cbff7f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5953</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (instalación de pararrayos, cambio de aisladores, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SET : [70] COTAHUASI.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 05 DE AGOSTO DE 2026:
@@ -810,72 +652,72 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:30 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:30</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5953&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>3b689bf202fbc04e9bf11cdf8550e15039bae5c3e4b21d1194c709783045de95</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5951</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones: Ampliación la Negrita, La Victoria, El Carmen, Cesar Vallejo.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Instalación de poste y nueva subestación de distribución.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Isla desde la celda salida de la SED N° 4797.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MIÉRCOLES, 05 DE AGOSTO DE 2026:
@@ -886,80 +728,80 @@
 Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 4751, 4797, 2374, 1139, 2373, 2371, 2357, 3387, 2369, 4309, 1141, 4297, 1140, 2368, 2367, 10154, 5932, 5683.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:28 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:28</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5951&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>439f2350120a8fe20215ef031c8dfc0d1205298f5f5c44c7f43bae987f94a1f1</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5952</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de estructura de media tensión, subsanación de deficiencias.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Las Peñas desde BC - 041005.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 05 DE AGOSTO DE 2026:
@@ -970,80 +812,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 03/08/2026 5:29 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>03/08/2026 5:29</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5952&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>884db480bd9d2359d94072e5f0c4e63d314be040013da98436065393000cdf6c</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5956</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Alto Selva Alegre, de Alto Selva Alegre</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Alto Selva Alegre: Chilina, San Lazaro.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (subsanación de deficiencias y desmontaje de red)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Independencia desde CC - 200188.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 07 DE AGOSTO DE 2026:
@@ -1054,30 +896,114 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 04/08/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>04/08/2026 17:36</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5956&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>6260ea7f29c9184ca598727d5f011c2569948c3377a0758a714df078063b6b3c</t>
         </is>
       </c>
     </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5957</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Peru desde SF6 - 020603.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 09 DE AGOSTO DE 2026:
+Circuito : Peru desde SF6 - 020603.
+Hora : 06:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 05/08/2026 18:16 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 18:16</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5957&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>7c535700357e06709a76dcb086c25cc048b8c27147c2e543711ef616b65416f7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P7"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1118,7 +1044,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 12:18:55</t>
+          <t>2026-08-06 12:20:53</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1068,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1080,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1092,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1140,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1152,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1164,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1191,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Alca, Huaynacotas, Puyca, Cotahuasi, Pampamarca, Tomepampa, de Alca, de Huaynacotas, de Puyca, de Cotahuasi, de Pampamarca, de Tomepampa</t>
+          <t>Alto Selva Alegre, de Alto Selva Alegre</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.</t>
+          <t>Urbanizaciones del distrito de Alto Selva Alegre: Chilina, San Lazaro.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (instalación de pararrayos, cambio de aisladores, podado de árboles).</t>
+          <t>Mantenimiento de redes en media tensión (subsanación de deficiencias y desmontaje de red)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SET : [70] COTAHUASI.</t>
+          <t>Circuito : Independencia desde CC - 200188.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,254 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
+          <t>2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 05 DE AGOSTO DE 2026:
-SET : [70] COTAHUASI.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (instalación de pararrayos, cambio de aisladores, podado de árboles).
-Zonas afectadas: Urbanizaciones del Distrito de Alca: Alca, Ayahuasi, Cahuana, Huillac, Ticnay, La Lucha, Yumasca, Urbanizaciones Distrito de Huaynacotas: Anatabamba, Chincayllapa, Huacay, Piramarca, Sarasara, Tarhuara, Yurac, Anexo Chaclla, Huaynacotas, Luicho Chico, Luicho Grande, Taurisma, Visve, Urbanizaciones Distrito de Puyca: Ccalla, Churca, Cuspa, Huactapa, Lauripampa, Maghuanca, Meclla, Petcce, Puica, Sayparara, Sayroso, Soncco, Suni, Urbanizaciones del distrito de Cotahuasi: Acobamba, Ccanchapata 2, Cuno Cuno, Villa Chacaylla. Urbanizaciones del distrito de Pampamarca: Cochapampa, Mungui, Pampamarca, Rumihuasi, Santa Rosa, Sencsincaylla, Tecca. Urbanizaciones del distrito de Tomepampa: Achambi, Huayhuanca, Locrahuanca, Tomepampa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7282, 7280, 7303, 7304, 7307, 7311, 7281, 7316, 7315, 7313, 7314, 7312, 7305, 7306, 7310, 7731, 7732, 7730, 7729, 7734, 7735, 7746, 7747, 7727, 7725, 7726, 7724, 8644, 9423, 10286, 7308, 7309, 7733, 7728, 7292, 7291, 7290, 7289, 7288, 7285, 7284, 7283, 7297, 7320, 7317, 7318, 7319, 7296, 7295, 7294, 7293, 7287, 7286, 7336, 7332, 7321, 7302, 7322, 7338, 7343, 7752, 7749, 7750, 7751, 7719, 7972, 9795, 9358, 9360, 9359, 9365, 9395, 10173.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 03/08/2026 5:30 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>03/08/2026 5:30</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5953&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>3b689bf202fbc04e9bf11cdf8550e15039bae5c3e4b21d1194c709783045de95</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5951</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones: Ampliación la Negrita, La Victoria, El Carmen, Cesar Vallejo.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Instalación de poste y nueva subestación de distribución.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : La Isla desde la celda salida de la SED N° 4797.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-MIÉRCOLES, 05 DE AGOSTO DE 2026:
-Circuito : La Isla desde la celda salida de la SED N° 4797.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Instalación de poste y nueva subestación de distribución.
-Zonas afectadas: Urbanizaciones: Ampliación la Negrita, La Victoria, El Carmen, Cesar Vallejo.
-Subestaciones de Distribución S.E. involucradas según zonas afectadas líneas arriba: 4751, 4797, 2374, 1139, 2373, 2371, 2357, 3387, 2369, 4309, 1141, 4297, 1140, 2368, 2367, 10154, 5932, 5683.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 03/08/2026 5:28 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>03/08/2026 5:28</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5951&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>439f2350120a8fe20215ef031c8dfc0d1205298f5f5c44c7f43bae987f94a1f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5952</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jacobo Hunter, Socabaya, de Jacobo Hunter, de Socabaya</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de estructura de media tensión, subsanación de deficiencias.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Las Peñas desde BC - 041005.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 05 DE AGOSTO DE 2026:
-Circuito : Las Peñas desde BC - 041005.
-Hora : 08:00 a 12:00 Hrs.
-Motivo : Cambio de estructura de media tensión, subsanación de deficiencias.
-Zonas afectadas: Urbanizaciones del distrito de Jacobo Hunter: La Estancia, Villa Florida, Villa Salaverry, Villa Sevilla. Urbanizaciones del distrito de Socabaya: Cerro Salaverry.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2326, 3098, 5624, 1322, 3097, 1708, 1710, 4878, 3286, 3282, 5704, 2460.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 03/08/2026 5:29 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>03/08/2026 5:29</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5952&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>884db480bd9d2359d94072e5f0c4e63d314be040013da98436065393000cdf6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5956</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Alto Selva Alegre, de Alto Selva Alegre</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Alto Selva Alegre: Chilina, San Lazaro.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (subsanación de deficiencias y desmontaje de red)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Independencia desde CC - 200188.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 07 DE AGOSTO DE 2026:
@@ -896,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 04/08/2026 17:36 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>04/08/2026 17:36</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5956&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>6260ea7f29c9184ca598727d5f011c2569948c3377a0758a714df078063b6b3c</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5957</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Peru desde SF6 - 020603.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 09 DE AGOSTO DE 2026:
@@ -980,30 +736,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 05/08/2026 18:16 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>05/08/2026 18:16</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5957&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>7c535700357e06709a76dcb086c25cc048b8c27147c2e543711ef616b65416f7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1044,7 +800,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:20:53</t>
+          <t>2026-08-07 11:09:19</t>
         </is>
       </c>
     </row>
@@ -1068,7 +824,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1080,7 +836,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1092,7 +848,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1164,7 +920,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1191,7 +947,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,13 +80,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -171,31 +168,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Fecha"/>
-    <tableColumn id="3" name="Hora inicio"/>
-    <tableColumn id="4" name="Hora fin"/>
-    <tableColumn id="5" name="Distrito"/>
-    <tableColumn id="6" name="Zona afectada"/>
-    <tableColumn id="7" name="Motivo"/>
-    <tableColumn id="8" name="Ubicación"/>
-    <tableColumn id="9" name="Título"/>
-    <tableColumn id="10" name="Subestaciones / SED"/>
-    <tableColumn id="11" name="Descripción completa"/>
-    <tableColumn id="12" name="Categoría"/>
-    <tableColumn id="13" name="Creado"/>
-    <tableColumn id="14" name="Modificado"/>
-    <tableColumn id="15" name="URL"/>
-    <tableColumn id="16" name="Hash"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -590,180 +562,9 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>5956</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Alto Selva Alegre, de Alto Selva Alegre</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Alto Selva Alegre: Chilina, San Lazaro.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (subsanación de deficiencias y desmontaje de red)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Independencia desde CC - 200188.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 07 DE AGOSTO DE 2026:
-Circuito : Independencia desde CC - 200188.
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Mantenimiento de redes en media tensión (subsanación de deficiencias y desmontaje de red)
-Zonas afectadas: Urbanizaciones del distrito de Alto Selva Alegre: Chilina, San Lazaro.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 2017, 4491, 5905, 4048, 1999, 1279, 5693, 2020</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 04/08/2026 17:36 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>04/08/2026 17:36</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5956&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>6260ea7f29c9184ca598727d5f011c2569948c3377a0758a714df078063b6b3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5957</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Arequipa, de Arequipa</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Peru desde SF6 - 020603.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-DOMINGO, 09 DE AGOSTO DE 2026:
-Circuito : Peru desde SF6 - 020603.
-Hora : 06:00 a 14:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 05/08/2026 18:16 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>05/08/2026 18:16</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5957&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>7c535700357e06709a76dcb086c25cc048b8c27147c2e543711ef616b65416f7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -781,173 +582,169 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-07 11:09:19</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08 10:53:17</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>REQUESTS_STATIC</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>2</v>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08 10:53:17</t>
+          <t>2026-08-09 10:54:25</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,10 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,6 +171,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P2" headerRowCount="1">
+  <autoFilter ref="A1:P2"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Hora inicio"/>
+    <tableColumn id="4" name="Hora fin"/>
+    <tableColumn id="5" name="Distrito"/>
+    <tableColumn id="6" name="Zona afectada"/>
+    <tableColumn id="7" name="Motivo"/>
+    <tableColumn id="8" name="Ubicación"/>
+    <tableColumn id="9" name="Título"/>
+    <tableColumn id="10" name="Subestaciones / SED"/>
+    <tableColumn id="11" name="Descripción completa"/>
+    <tableColumn id="12" name="Categoría"/>
+    <tableColumn id="13" name="Creado"/>
+    <tableColumn id="14" name="Modificado"/>
+    <tableColumn id="15" name="URL"/>
+    <tableColumn id="16" name="Hash"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -562,9 +590,96 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5957</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Peru desde SF6 - 020603.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 09 DE AGOSTO DE 2026:
+Circuito : Peru desde SF6 - 020603.
+Hora : 06:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 05/08/2026 18:16 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2026 18:16</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5957&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>7c535700357e06709a76dcb086c25cc048b8c27147c2e543711ef616b65416f7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -582,169 +697,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-09 10:54:25</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:28:00</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>REQUESTS_STATIC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P2" headerRowCount="1">
-  <autoFilter ref="A1:P2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
+  <autoFilter ref="A1:P11"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Arequipa, de Arequipa</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.</t>
+          <t>Mz. J-K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).</t>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Peru desde SF6 - 020603.</t>
+          <t>Circuito : SED 4487.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,46 +636,772 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
-DOMINGO, 09 DE AGOSTO DE 2026:
-Circuito : Peru desde SF6 - 020603.
-Hora : 06:00 a 14:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (camio de transformador, subsanar deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de Arequipa: Centro Histórico Arequipa, Cercado.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4950, 1640, 1486, 1696, 10139, 1712, 1554, 1951, 1052, 2891, 2885, 1955, 1013, 4067, 4849, 4150, 2704, 4236, 1767, 4363, 10275, 4850, 5021, 5873, 4830, 10222.</t>
+LUNES, 10 DE AGOSTO DE 2026.
+Circuito : SED 4487.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Mz. J-K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>el 05/08/2026 18:16 por Cuenta del sistema</t>
+          <t>el 10/08/2026 7:58 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 18:16</t>
+          <t>10/08/2026 7:58</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5957&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5959&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>7c535700357e06709a76dcb086c25cc048b8c27147c2e543711ef616b65416f7</t>
+          <t>daac8c29011d5456cdcbdbbc0a4c8a28d60b7879a85ff157cf707ec0be240c87</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>5960</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Mz. K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1940.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 10 DE AGOSTO DE 2026.
+Circuito : SED 1940.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Mz. K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 7:58 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 7:58</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5960&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>a9242b0c3625dc786e8fa91dca5fd90c676b960ed3b7c3985a8ac91256adb3c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5958</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Inserción de nueva subestación y cambio de EMT.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Tecsup desde la EMT 12770</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4987, 3242.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+MARTES, 11 DE AGOSTO DE 2026:
+Circuito : Tecsup desde la EMT 12770
+Hora : 07:30 a 16:30 Hrs.
+Motivo : Inserción de nueva subestación y cambio de EMT.
+Zonas : Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4987, 3242.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 7:57 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 7:57</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5958&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>458679a6cf5988bea98a29435f05d55a3ebb7c1b1915d02b13d5403b8a0c2d3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5965</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Atiquipa, Yauca, de Atiquipa, de Yauca</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (Subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Agua Salada desde REC - 560244.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 11 DE AGOSTO DE 2026:
+Circuito : Agua Salada desde REC - 560244.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (Subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 8:01 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 8:01</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5965&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>8fc343099ff94c7003207145a5fabf30d482d3defcb707d6c3d5a687f4f277a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5967</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Inserción de nueva subestación y cambio de EMT.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Tecsup desde la EMT 12770</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4987, 3242.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+MARTES, 11 DE AGOSTO DE 2026:
+Circuito : Tecsup desde la EMT 12770
+Hora : 07:30 a 16:30 Hrs.
+Motivo : Inserción de nueva subestación y cambio de EMT.
+Zonas : Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4987, 3242.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 8:03 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 8:03</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5967&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0eb79cb372c17674c648a6820a0312da7871d58ebc38db39cff2811c19d0a1c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5961</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Centro Comercial Las Malvinas del Sur (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5035.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 11 DE AGOSTO DE 2026.
+Circuito : SED 5035.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Centro Comercial Las Malvinas del Sur (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 7:59 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 7:59</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5961&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>a2c854ffd81694bd87d7caa6417cd1c3b3cc5b7307494eb272bb559b1ef1fb27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5962</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5343.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 11 DE AGOSTO DE 2026.
+Circuito : SED 5343.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 8:00 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 8:00</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5962&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>eb6826437ac4f3a983a560f60a474d1bd9142ed9f6b0f0f83b232b3a5da13ffc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5963</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5342.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 12 DE AGOSTO DE 2026.
+Circuito : SED 5342.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 8:00 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 8:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5963&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>67282863ff46e0535266a090e83589125074d785300c7035df56ca11b971f1e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5964</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5344.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 12 DE AGOSTO DE 2026.
+Circuito : SED 5344.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la Subestación.
+Zonas afectadas: Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 8:01 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 8:01</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5964&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>db2ebc8bf0ff61ee7e50494f84e79b52ce2a64e034509974fec3217d71da47f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5966</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Inserción de nueva subestación de distribución y ampliación de red de media tensión.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ciudad Municipal desde CC - 200343.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>REFORZAMIENTO DE REDES.
+JUEVES, 13 DE AGOSTO DE 2026:
+Circuito : Ciudad Municipal desde CC - 200343.
+Hora : 07:30 a 13:30 Hrs.
+Motivo : Inserción de nueva subestación de distribución y ampliación de red de media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 8:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 8:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5966&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>56a9aa8a8aa0bca8a788961a283e40817274fbe6bc0a448c469480b276259bc8</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -716,7 +1442,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10 11:28:00</t>
+          <t>2026-08-11 11:06:54</t>
         </is>
       </c>
     </row>
@@ -740,7 +1466,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -752,7 +1478,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -764,7 +1490,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -812,7 +1538,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -824,7 +1550,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -836,7 +1562,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -863,7 +1589,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -593,213 +593,55 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Mz. J-K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
+          <t>Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
+          <t>Inserción de nueva subestación y cambio de EMT.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 4487.</t>
+          <t>Circuito : Tecsup desde la EMT 12770</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+          <t>REFORZAMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4987, 3242.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 10 DE AGOSTO DE 2026.
-Circuito : SED 4487.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Mz. J-K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 7:58 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 7:58</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5959&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>daac8c29011d5456cdcbdbbc0a4c8a28d60b7879a85ff157cf707ec0be240c87</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5960</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1940.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 10 DE AGOSTO DE 2026.
-Circuito : SED 1940.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Mz. K de Urb. Asociación APTASA (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 7:58 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 7:58</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5960&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>a9242b0c3625dc786e8fa91dca5fd90c676b960ed3b7c3985a8ac91256adb3c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5958</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Inserción de nueva subestación y cambio de EMT.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Tecsup desde la EMT 12770</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4987, 3242.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MARTES, 11 DE AGOSTO DE 2026:
@@ -810,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4987, 3242.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 7:57 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 7:57</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5958&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>458679a6cf5988bea98a29435f05d55a3ebb7c1b1915d02b13d5403b8a0c2d3d</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5965</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Atiquipa, Yauca, de Atiquipa, de Yauca</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (Subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Agua Salada desde REC - 560244.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 11 DE AGOSTO DE 2026:
@@ -894,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:01</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5965&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>8fc343099ff94c7003207145a5fabf30d482d3defcb707d6c3d5a687f4f277a1</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5967</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Inserción de nueva subestación y cambio de EMT.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Tecsup desde la EMT 12770</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4987, 3242.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 MARTES, 11 DE AGOSTO DE 2026:
@@ -978,76 +820,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4987, 3242.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:03 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:03</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5967&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>0eb79cb372c17674c648a6820a0312da7871d58ebc38db39cff2811c19d0a1c2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5961</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Centro Comercial Las Malvinas del Sur (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5035.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 11 DE AGOSTO DE 2026.
@@ -1057,76 +899,76 @@
 Zonas afectadas: Centro Comercial Las Malvinas del Sur (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 7:59 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 7:59</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5961&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>a2c854ffd81694bd87d7caa6417cd1c3b3cc5b7307494eb272bb559b1ef1fb27</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5962</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5343.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 11 DE AGOSTO DE 2026.
@@ -1136,76 +978,76 @@
 Zonas afectadas: Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:00</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5962&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>eb6826437ac4f3a983a560f60a474d1bd9142ed9f6b0f0f83b232b3a5da13ffc</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5963</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5342.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 12 DE AGOSTO DE 2026.
@@ -1215,76 +1057,76 @@
 Zonas afectadas: Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:00</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5963&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>67282863ff46e0535266a090e83589125074d785300c7035df56ca11b971f1e9</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5964</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5344.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 12 DE AGOSTO DE 2026.
@@ -1294,80 +1136,80 @@
 Zonas afectadas: Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:01</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5964&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>db2ebc8bf0ff61ee7e50494f84e79b52ce2a64e034509974fec3217d71da47f1</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>5966</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Inserción de nueva subestación de distribución y ampliación de red de media tensión.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde CC - 200343.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 JUEVES, 13 DE AGOSTO DE 2026:
@@ -1378,25 +1220,193 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 10/08/2026 8:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026 8:02</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5966&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>56a9aa8a8aa0bca8a788961a283e40817274fbe6bc0a448c469480b276259bc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5968</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Mejia desde BC - 360119.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 14 DE AGOSTO DE 2026:
+Circuito : Mejia desde BC - 360119.
+Hora : 07:30 a 16:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Costa Palmeras.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 11/08/2026 17:25 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11/08/2026 17:25</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5968&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>e981974c26e94c645638a189a045efd1797b07ce6642469cd5960f159ab19d38</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5969</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Pastor</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (cambio de conductor, manteamiento de</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Cristo Rey desde REC - 200533.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 14 DE AGOSTO DE 2026:
+Circuito : Cristo Rey desde REC - 200533.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (cambio de conductor, manteamiento de subestaciones).
+Zonas : Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>el 10/08/2026 8:02 por Cuenta del sistema</t>
+          <t>el 11/08/2026 17:27 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 8:02</t>
+          <t>11/08/2026 17:27</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5966&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5969&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56a9aa8a8aa0bca8a788961a283e40817274fbe6bc0a448c469480b276259bc8</t>
+          <t>513cc2d7828d7aa136fffcc79f20c25af279b439bd0bffc6c11305501d694b1c</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1452,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 11:06:54</t>
+          <t>2026-08-12 11:12:32</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1476,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1488,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1500,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1548,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1560,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P11" headerRowCount="1">
-  <autoFilter ref="A1:P11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,461 +593,51 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+          <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.</t>
+          <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Inserción de nueva subestación y cambio de EMT.</t>
+          <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Tecsup desde la EMT 12770</t>
+          <t>Circuito : SED 5342.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>4987, 3242.</t>
-        </is>
-      </c>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-MARTES, 11 DE AGOSTO DE 2026:
-Circuito : Tecsup desde la EMT 12770
-Hora : 07:30 a 16:30 Hrs.
-Motivo : Inserción de nueva subestación y cambio de EMT.
-Zonas : Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4987, 3242.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 7:57 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 7:57</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5958&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>458679a6cf5988bea98a29435f05d55a3ebb7c1b1915d02b13d5403b8a0c2d3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5965</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Atiquipa, Yauca, de Atiquipa, de Yauca</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (Subsanación de deficiencias).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Agua Salada desde REC - 560244.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 11 DE AGOSTO DE 2026:
-Circuito : Agua Salada desde REC - 560244.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (Subsanación de deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de Atiquipa: Agua Salada, Atiquipa, Santa Rosa. Urbanizaciones del distrito de Yauca: Tanaka.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9638, 9379, 9637, 9647, 9650, 9649, 9639, 9818, 9875, 9876, 9636, 9976, 10159.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 8:01 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 8:01</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5965&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>8fc343099ff94c7003207145a5fabf30d482d3defcb707d6c3d5a687f4f277a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5967</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Inserción de nueva subestación y cambio de EMT.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Tecsup desde la EMT 12770</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4987, 3242.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-MARTES, 11 DE AGOSTO DE 2026:
-Circuito : Tecsup desde la EMT 12770
-Hora : 07:30 a 16:30 Hrs.
-Motivo : Inserción de nueva subestación y cambio de EMT.
-Zonas : Urbanizaciones del Distrito de Jose Luis Bustamante y Rivero: Urb. Bancarios, Urb. Casapia.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4987, 3242.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 8:03 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 8:03</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5967&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0eb79cb372c17674c648a6820a0312da7871d58ebc38db39cff2811c19d0a1c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5961</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Centro Comercial Las Malvinas del Sur (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5035.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 11 DE AGOSTO DE 2026.
-Circuito : SED 5035.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Centro Comercial Las Malvinas del Sur (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 7:59 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 7:59</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5961&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>a2c854ffd81694bd87d7caa6417cd1c3b3cc5b7307494eb272bb559b1ef1fb27</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5962</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5343.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 11 DE AGOSTO DE 2026.
-Circuito : SED 5343.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 8:00 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 8:00</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5962&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>eb6826437ac4f3a983a560f60a474d1bd9142ed9f6b0f0f83b232b3a5da13ffc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5963</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5342.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 12 DE AGOSTO DE 2026.
@@ -1057,76 +647,76 @@
 Zonas afectadas: Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:00</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5963&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>67282863ff46e0535266a090e83589125074d785300c7035df56ca11b971f1e9</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5964</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de la Subestación.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 5344.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 12 DE AGOSTO DE 2026.
@@ -1136,80 +726,80 @@
 Zonas afectadas: Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:01</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5964&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>db2ebc8bf0ff61ee7e50494f84e79b52ce2a64e034509974fec3217d71da47f1</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5966</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Inserción de nueva subestación de distribución y ampliación de red de media tensión.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Ciudad Municipal desde CC - 200343.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 JUEVES, 13 DE AGOSTO DE 2026:
@@ -1220,80 +810,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:02</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5966&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>56a9aa8a8aa0bca8a788961a283e40817274fbe6bc0a448c469480b276259bc8</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5968</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : Mejia desde BC - 360119.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 14 DE AGOSTO DE 2026:
@@ -1304,80 +894,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 11/08/2026 17:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11/08/2026 17:25</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026 18:45</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5968&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>e981974c26e94c645638a189a045efd1797b07ce6642469cd5960f159ab19d38</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>9bf2aa2380aff8706b277fd00c45be23f1b27e8ed5269f6db4fbea3a38f84cfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5969</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de conductor, manteamiento de</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cristo Rey desde REC - 200533.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 14 DE AGOSTO DE 2026:
@@ -1388,30 +978,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 11/08/2026 17:27 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11/08/2026 17:27</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5969&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>513cc2d7828d7aa136fffcc79f20c25af279b439bd0bffc6c11305501d694b1c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1452,7 +1042,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12 11:12:32</t>
+          <t>2026-08-13 11:12:25</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1066,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1078,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1090,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1162,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1189,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
+  <autoFilter ref="A1:P4"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,22 +593,22 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -618,188 +618,30 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
+          <t>Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
+          <t>Inserción de nueva subestación de distribución y ampliación de red de media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 5342.</t>
+          <t>Circuito : Ciudad Municipal desde CC - 200343.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+          <t>REFORZAMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 12 DE AGOSTO DE 2026.
-Circuito : SED 5342.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Km 6.8 de la Vía de evitamiento (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 8:00 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 8:00</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5963&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>67282863ff46e0535266a090e83589125074d785300c7035df56ca11b971f1e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5964</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la Subestación.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5344.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 12 DE AGOSTO DE 2026.
-Circuito : SED 5344.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la Subestación.
-Zonas afectadas: Km 6.8 de la Vía de evitamiento, los desamparados (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 8:01 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 8:01</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5964&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>db2ebc8bf0ff61ee7e50494f84e79b52ce2a64e034509974fec3217d71da47f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5966</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>13/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Inserción de nueva subestación de distribución y ampliación de red de media tensión.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Ciudad Municipal desde CC - 200343.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>REFORZAMIENTO DE REDES.
 JUEVES, 13 DE AGOSTO DE 2026:
@@ -810,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 10/08/2026 8:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10/08/2026 8:02</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5966&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>56a9aa8a8aa0bca8a788961a283e40817274fbe6bc0a448c469480b276259bc8</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5968</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Mejia desde BC - 360119.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 14 DE AGOSTO DE 2026:
@@ -894,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 11/08/2026 17:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>12/08/2026 18:45</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5968&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>9bf2aa2380aff8706b277fd00c45be23f1b27e8ed5269f6db4fbea3a38f84cfb</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5969</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de conductor, manteamiento de</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cristo Rey desde REC - 200533.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 14 DE AGOSTO DE 2026:
@@ -978,30 +820,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 11/08/2026 17:27 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11/08/2026 17:27</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13/08/2026 18:02</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5969&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>513cc2d7828d7aa136fffcc79f20c25af279b439bd0bffc6c11305501d694b1c</t>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9bf95da0236394a816ae20382aa6ab457ae8bc6da38aa53e5bb9614cf699ec2e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1042,7 +884,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13 11:12:25</t>
+          <t>2026-08-14 11:10:27</t>
         </is>
       </c>
     </row>
@@ -1066,7 +908,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1078,7 +920,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1090,7 +932,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1004,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1031,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
-  <autoFilter ref="A1:P4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
+  <autoFilter ref="A1:P3"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -608,124 +608,40 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
+          <t>Mollendo, de Mollendo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.</t>
+          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Inserción de nueva subestación de distribución y ampliación de red de media tensión.</t>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Ciudad Municipal desde CC - 200343.</t>
+          <t>Circuito : Mejia desde BC - 360119.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>REFORZAMIENTO DE REDES</t>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
+          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>REFORZAMIENTO DE REDES.
-JUEVES, 13 DE AGOSTO DE 2026:
-Circuito : Ciudad Municipal desde CC - 200343.
-Hora : 07:30 a 13:30 Hrs.
-Motivo : Inserción de nueva subestación de distribución y ampliación de red de media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: APIPA sector III, Asoc. Jose Luis Bustamte y Rivero sector 1.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5432, 5431, 5144, 5433, 5449, 5642, 5143.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 10/08/2026 8:02 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026 8:02</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5966&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>56a9aa8a8aa0bca8a788961a283e40817274fbe6bc0a448c469480b276259bc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5968</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Mejia desde BC - 360119.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 14 DE AGOSTO DE 2026:
@@ -736,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 11/08/2026 17:25 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>12/08/2026 18:45</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5968&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>9bf2aa2380aff8706b277fd00c45be23f1b27e8ed5269f6db4fbea3a38f84cfb</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5969</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Samuel Pastor</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (cambio de conductor, manteamiento de</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Cristo Rey desde REC - 200533.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 14 DE AGOSTO DE 2026:
@@ -820,30 +736,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 11/08/2026 17:27 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>13/08/2026 18:02</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5969&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>9bf95da0236394a816ae20382aa6ab457ae8bc6da38aa53e5bb9614cf699ec2e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P4"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -884,7 +800,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14 11:10:27</t>
+          <t>2026-08-15 10:42:09</t>
         </is>
       </c>
     </row>
@@ -908,7 +824,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -920,7 +836,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -932,7 +848,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -992,7 +908,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1004,7 +920,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1031,7 +947,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,13 +80,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -171,31 +168,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P3" headerRowCount="1">
-  <autoFilter ref="A1:P3"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Fecha"/>
-    <tableColumn id="3" name="Hora inicio"/>
-    <tableColumn id="4" name="Hora fin"/>
-    <tableColumn id="5" name="Distrito"/>
-    <tableColumn id="6" name="Zona afectada"/>
-    <tableColumn id="7" name="Motivo"/>
-    <tableColumn id="8" name="Ubicación"/>
-    <tableColumn id="9" name="Título"/>
-    <tableColumn id="10" name="Subestaciones / SED"/>
-    <tableColumn id="11" name="Descripción completa"/>
-    <tableColumn id="12" name="Categoría"/>
-    <tableColumn id="13" name="Creado"/>
-    <tableColumn id="14" name="Modificado"/>
-    <tableColumn id="15" name="URL"/>
-    <tableColumn id="16" name="Hash"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -590,180 +562,9 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>5968</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Mejia desde BC - 360119.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 14 DE AGOSTO DE 2026:
-Circuito : Mejia desde BC - 360119.
-Hora : 07:30 a 16:30 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de postes, mantenimiento conductor y otras actividades de mantenimiento).
-Zonas afectadas: Urbanizaciones del distrito de Mollendo: Costa Palmeras.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 11/08/2026 17:25 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>12/08/2026 18:45</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5968&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>9bf2aa2380aff8706b277fd00c45be23f1b27e8ed5269f6db4fbea3a38f84cfb</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5969</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Samuel Pastor</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (cambio de conductor, manteamiento de</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Cristo Rey desde REC - 200533.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 14 DE AGOSTO DE 2026:
-Circuito : Cristo Rey desde REC - 200533.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (cambio de conductor, manteamiento de subestaciones).
-Zonas : Zona del Distrito Samuel Pastor: A.H. Alto Luren, AA.HH. Bella Union, Almirante Grau, Alto Buenos Aires, Señor de Luren, Virgen de La Candelaria
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9193, 9169, 9231, 9266, 9307, 9192, 9340, 9330, 9331, 9369.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 11/08/2026 17:27 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>13/08/2026 18:02</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5969&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>9bf95da0236394a816ae20382aa6ab457ae8bc6da38aa53e5bb9614cf699ec2e</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -781,173 +582,169 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15 10:42:09</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:42:44</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>REQUESTS_STATIC</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>2</v>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16 10:42:44</t>
+          <t>2026-08-17 10:49:49</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 10:49:49</t>
+          <t>2026-08-18 10:48:51</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,10 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,6 +171,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
+  <autoFilter ref="A1:P8"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Hora inicio"/>
+    <tableColumn id="4" name="Hora fin"/>
+    <tableColumn id="5" name="Distrito"/>
+    <tableColumn id="6" name="Zona afectada"/>
+    <tableColumn id="7" name="Motivo"/>
+    <tableColumn id="8" name="Ubicación"/>
+    <tableColumn id="9" name="Título"/>
+    <tableColumn id="10" name="Subestaciones / SED"/>
+    <tableColumn id="11" name="Descripción completa"/>
+    <tableColumn id="12" name="Categoría"/>
+    <tableColumn id="13" name="Creado"/>
+    <tableColumn id="14" name="Modificado"/>
+    <tableColumn id="15" name="URL"/>
+    <tableColumn id="16" name="Hash"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -562,9 +590,590 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Arequipa: Campiña Dorada, Juventud Ferroviaria, Los Ángeles, San Jeronimo.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (subsanación de deficiencia)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Sacos Del Sur desde BC - 040502.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>3467, 5889, 5890, 1823, 1284, 5298, 10180.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 18 DE AGOSTO DE 2026:
+Circuito : Sacos Del Sur desde BC - 040502.
+Hora : 07:30 a 14:30 Hrs.
+Motivo : Mantenimiento de redes de media tensión (subsanación de deficiencia)
+Zonas afectadas: Urbanizaciones del distrito de Arequipa: Campiña Dorada, Juventud Ferroviaria, Los Ángeles, San Jeronimo.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3467, 5889, 5890, 1823, 1284, 5298, 10180.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 17/08/2026 7:55 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 7:55</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5970&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>04046107a8dc5ef95e3275d0e6675b6e9172e29a3a7620b76ab1750ded162eed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Chala, de Chala</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Chala: Chala, Imperial La Aguadita, Las Brisas, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (Cambio de poste, subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [5804] MANUEL PRADO.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9645, 10166, 10236, 10257, 9414.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 18 DE AGOSTO DE 2026:
+Circuito : [5804] MANUEL PRADO.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (Cambio de poste, subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Chala: Chala, Imperial La Aguadita, Las Brisas, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9645, 10166, 10236, 10257, 9414.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 17/08/2026 7:57 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 16:07</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5972&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>4ab9093fccbb96e261da95804a979b534b541fc7418c1974894bd86587a7f508</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5971</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XVI.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde BC - 200324.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5078, 5126, 5127, 5833.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 18 DE AGOSTO DE 2026:
+Circuito : P. Yura desde BC - 200324.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XVI.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5078, 5126, 5127, 5833.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 17/08/2026 7:56 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 7:56</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5971&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>11c2cfc3bd0500edeabcc6fbc7b866d93a5c4262846d701f5c44acb8b19af18c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5973</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Quinta La Floresta, Quebrada San Jacinto (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 100 KVA.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3958.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 19 DE AGOSTO DE 2026.
+Circuito : SED 3958.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Cambio de transformador a 100 KVA.
+Zonas afectadas: Urb. Quinta La Floresta, Quebrada San Jacinto (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 17/08/2026 7:58 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 15:42</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5973&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>b8ce50af51e2c922a048d02edd1eced79ef810cd0594cafd0b91de82838c8a62</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Uchumayo, de Uchumayo</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Lateral 4 – El Cural (Distrito de Uchumayo).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador a 50 KVA.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1091.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 19 DE AGOSTO DE 2026.
+Circuito : SED 1091.
+Hora : 08:00 a 13:00 Hrs.
+Motivo : Cambio de transformador a 50 KVA.
+Zonas afectadas: Lateral 4 – El Cural (Distrito de Uchumayo).</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 17/08/2026 7:58 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026 15:41</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5974&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>3c2aa033d733b4157741a86dfe3985d22d6349b431cdc9f1adb1501b533aa1cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5975</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector I, Apipa Sector VII, Apipa Sector VIII, Apipa Sector V-VI, Apipa Sector XIII.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde BC - 200356.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5128, 5129, 5130, 5131, 5132, 5429, 5438, 5439, 5859.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 20 DE AGOSTO DE 2026:
+Circuito : P. Yura desde BC - 200356.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apipa Sector I, Apipa Sector VII, Apipa Sector VIII, Apipa Sector V-VI, Apipa Sector XIII.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5128, 5129, 5130, 5131, 5132, 5429, 5438, 5439, 5859.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 17/08/2026 7:59 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 7:59</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5975&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>fca7411cd95fa005184f3656144c00cb6f1553d11f3ae544aa1f0f048aa39559</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5976</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XV.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde BC - 080320.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5133, 5134, 5135, 5446, 5447, 5448.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 21 DE AGOSTO DE 2026:
+Circuito : P. Yura desde BC - 080320.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).
+Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XV.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5133, 5134, 5135, 5446, 5447, 5448.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 17/08/2026 8:00 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026 8:00</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5976&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>dafabd863d2e0bd1ae9de5130e66473bd274e2ebdfc4f1b57b941df506c8eb74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -582,169 +1191,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-18 10:48:51</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19 11:09:59</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>REQUESTS_STATIC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
+      <c r="B16" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P8" headerRowCount="1">
-  <autoFilter ref="A1:P8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
+  <autoFilter ref="A1:P5"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,303 +593,51 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Arequipa, de Arequipa</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Arequipa: Campiña Dorada, Juventud Ferroviaria, Los Ángeles, San Jeronimo.</t>
+          <t>Urb. Quinta La Floresta, Quebrada San Jacinto (Distrito de Cayma).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (subsanación de deficiencia)</t>
+          <t>Cambio de transformador a 100 KVA.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Sacos Del Sur desde BC - 040502.</t>
+          <t>Circuito : SED 3958.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>3467, 5889, 5890, 1823, 1284, 5298, 10180.</t>
-        </is>
-      </c>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 18 DE AGOSTO DE 2026:
-Circuito : Sacos Del Sur desde BC - 040502.
-Hora : 07:30 a 14:30 Hrs.
-Motivo : Mantenimiento de redes de media tensión (subsanación de deficiencia)
-Zonas afectadas: Urbanizaciones del distrito de Arequipa: Campiña Dorada, Juventud Ferroviaria, Los Ángeles, San Jeronimo.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3467, 5889, 5890, 1823, 1284, 5298, 10180.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 17/08/2026 7:55 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>17/08/2026 7:55</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5970&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>04046107a8dc5ef95e3275d0e6675b6e9172e29a3a7620b76ab1750ded162eed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5972</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>18/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Chala, de Chala</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Chala: Chala, Imperial La Aguadita, Las Brisas, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (Cambio de poste, subsanación de deficiencias).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [5804] MANUEL PRADO.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9645, 10166, 10236, 10257, 9414.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 18 DE AGOSTO DE 2026:
-Circuito : [5804] MANUEL PRADO.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Mantenimiento de redes en media tensión (Cambio de poste, subsanación de deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de Chala: Chala, Imperial La Aguadita, Las Brisas, Los Jardines Chala Tradicional, Magisterial Chala, Manuel Prado, Nueva Juventud, Pueblo Tradicional de Chala, Sector Casuarinas, Virgen del Carmen.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 9658, 9643, 9640, 9652, 9686, 9685, 9641, 9680, 9679, 9665, 9644, 9830, 9869, 9896, 9983, 9980, 9984, 9322, 9798, 9575, 9576, 9574, 9573, 9348, 9599, 9346, 9382, 9402, 9404, 9645, 10166, 10236, 10257, 9414.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 17/08/2026 7:57 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>17/08/2026 16:07</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5972&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>4ab9093fccbb96e261da95804a979b534b541fc7418c1974894bd86587a7f508</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5971</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>18/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XVI.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : P. Yura desde BC - 200324.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5078, 5126, 5127, 5833.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 18 DE AGOSTO DE 2026:
-Circuito : P. Yura desde BC - 200324.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XVI.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5078, 5126, 5127, 5833.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 17/08/2026 7:56 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17/08/2026 7:56</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5971&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11c2cfc3bd0500edeabcc6fbc7b866d93a5c4262846d701f5c44acb8b19af18c</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5973</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>19/08/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urb. Quinta La Floresta, Quebrada San Jacinto (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 100 KVA.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3958.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 19 DE AGOSTO DE 2026.
@@ -899,76 +647,76 @@
 Zonas afectadas: Urb. Quinta La Floresta, Quebrada San Jacinto (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 17/08/2026 7:58 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>18/08/2026 15:42</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5973&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>b8ce50af51e2c922a048d02edd1eced79ef810cd0594cafd0b91de82838c8a62</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5974</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>19/08/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Uchumayo, de Uchumayo</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Lateral 4 – El Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador a 50 KVA.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1091.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 19 DE AGOSTO DE 2026.
@@ -978,80 +726,80 @@
 Zonas afectadas: Lateral 4 – El Cural (Distrito de Uchumayo).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 17/08/2026 7:58 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>18/08/2026 15:41</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5974&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>3c2aa033d733b4157741a86dfe3985d22d6349b431cdc9f1adb1501b533aa1cb</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5975</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector I, Apipa Sector VII, Apipa Sector VIII, Apipa Sector V-VI, Apipa Sector XIII.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde BC - 200356.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5128, 5129, 5130, 5131, 5132, 5429, 5438, 5439, 5859.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 20 DE AGOSTO DE 2026:
@@ -1062,80 +810,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5128, 5129, 5130, 5131, 5132, 5429, 5438, 5439, 5859.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 17/08/2026 7:59 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17/08/2026 7:59</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5975&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>fca7411cd95fa005184f3656144c00cb6f1553d11f3ae544aa1f0f048aa39559</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5976</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>21/08/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XV.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde BC - 080320.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>5133, 5134, 5135, 5446, 5447, 5448.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 21 DE AGOSTO DE 2026:
@@ -1146,30 +894,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5133, 5134, 5135, 5446, 5447, 5448.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 17/08/2026 8:00 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17/08/2026 8:00</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5976&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>dafabd863d2e0bd1ae9de5130e66473bd274e2ebdfc4f1b57b941df506c8eb74</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
+  <autoFilter ref="A1:P5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1210,7 +958,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19 11:09:59</t>
+          <t>2026-08-20 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1234,7 +982,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -1246,7 +994,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1006,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1078,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1105,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,13 +80,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -171,31 +168,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P5" headerRowCount="1">
-  <autoFilter ref="A1:P5"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Fecha"/>
-    <tableColumn id="3" name="Hora inicio"/>
-    <tableColumn id="4" name="Hora fin"/>
-    <tableColumn id="5" name="Distrito"/>
-    <tableColumn id="6" name="Zona afectada"/>
-    <tableColumn id="7" name="Motivo"/>
-    <tableColumn id="8" name="Ubicación"/>
-    <tableColumn id="9" name="Título"/>
-    <tableColumn id="10" name="Subestaciones / SED"/>
-    <tableColumn id="11" name="Descripción completa"/>
-    <tableColumn id="12" name="Categoría"/>
-    <tableColumn id="13" name="Creado"/>
-    <tableColumn id="14" name="Modificado"/>
-    <tableColumn id="15" name="URL"/>
-    <tableColumn id="16" name="Hash"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -590,338 +562,9 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>5973</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>19/08/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Urb. Quinta La Floresta, Quebrada San Jacinto (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 100 KVA.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3958.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 19 DE AGOSTO DE 2026.
-Circuito : SED 3958.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Cambio de transformador a 100 KVA.
-Zonas afectadas: Urb. Quinta La Floresta, Quebrada San Jacinto (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 17/08/2026 7:58 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>18/08/2026 15:42</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5973&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>b8ce50af51e2c922a048d02edd1eced79ef810cd0594cafd0b91de82838c8a62</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5974</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>19/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Uchumayo, de Uchumayo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Lateral 4 – El Cural (Distrito de Uchumayo).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador a 50 KVA.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1091.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 19 DE AGOSTO DE 2026.
-Circuito : SED 1091.
-Hora : 08:00 a 13:00 Hrs.
-Motivo : Cambio de transformador a 50 KVA.
-Zonas afectadas: Lateral 4 – El Cural (Distrito de Uchumayo).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 17/08/2026 7:58 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>18/08/2026 15:41</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5974&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>3c2aa033d733b4157741a86dfe3985d22d6349b431cdc9f1adb1501b533aa1cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector I, Apipa Sector VII, Apipa Sector VIII, Apipa Sector V-VI, Apipa Sector XIII.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : P. Yura desde BC - 200356.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5128, 5129, 5130, 5131, 5132, 5429, 5438, 5439, 5859.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 20 DE AGOSTO DE 2026:
-Circuito : P. Yura desde BC - 200356.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apipa Sector I, Apipa Sector VII, Apipa Sector VIII, Apipa Sector V-VI, Apipa Sector XIII.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5128, 5129, 5130, 5131, 5132, 5429, 5438, 5439, 5859.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 17/08/2026 7:59 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17/08/2026 7:59</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5975&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>fca7411cd95fa005184f3656144c00cb6f1553d11f3ae544aa1f0f048aa39559</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5976</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XV.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : P. Yura desde BC - 080320.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5133, 5134, 5135, 5446, 5447, 5448.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 21 DE AGOSTO DE 2026:
-Circuito : P. Yura desde BC - 080320.
-Hora : 08:00 a 14:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (limpieza de aisladores, ajustes de ferretería).
-Zonas afectadas: Urbanizaciones del distrito de Cerro Colorado: Apipa Sector XV.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5133, 5134, 5135, 5446, 5447, 5448.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 17/08/2026 8:00 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17/08/2026 8:00</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5976&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>dafabd863d2e0bd1ae9de5130e66473bd274e2ebdfc4f1b57b941df506c8eb74</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P5"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -939,173 +582,169 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20 10:49:32</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:50:23</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>REQUESTS_STATIC</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>4</v>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21 10:50:23</t>
+          <t>2026-08-22 10:42:53</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22 10:42:53</t>
+          <t>2026-08-23 10:43:52</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23 10:43:52</t>
+          <t>2026-08-24 10:56:11</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:56:11</t>
+          <t>2026-08-25 10:51:56</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:51:56</t>
+          <t>2026-08-26 10:53:31</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,10 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,6 +171,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
+  <autoFilter ref="A1:P10"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Hora inicio"/>
+    <tableColumn id="4" name="Hora fin"/>
+    <tableColumn id="5" name="Distrito"/>
+    <tableColumn id="6" name="Zona afectada"/>
+    <tableColumn id="7" name="Motivo"/>
+    <tableColumn id="8" name="Ubicación"/>
+    <tableColumn id="9" name="Título"/>
+    <tableColumn id="10" name="Subestaciones / SED"/>
+    <tableColumn id="11" name="Descripción completa"/>
+    <tableColumn id="12" name="Categoría"/>
+    <tableColumn id="13" name="Creado"/>
+    <tableColumn id="14" name="Modificado"/>
+    <tableColumn id="15" name="URL"/>
+    <tableColumn id="16" name="Hash"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -562,9 +590,748 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5987</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Nicolas de Pierola, Uraca, de Nicolas de Pierola, de Uraca</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani. Urbanizaciones del distrito de Uraca: A.A.H.H.Villa Electrica, Anexo La Punta Colorada, Cantas, El Pedregal, Escalerillas, La Mezana, Las Malvinas, Pitis, Punta Colorada, Sarcas, Satelite, Toran, Villa Hermosa.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (reubicación de estructura, cambio de crucetas, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [8102] TORAN.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>7111, 7151, 7156, 7166, 7171, 7135, 7134, 7136, 7113, 7124, 7120, 7125, 7127, 7128, 7126, 7130, 7142, 7117, 7121, 7122, 7132, 7129, 7131, 7155, 7153, 7154, 7176, 7178, 7188, 7198, 7499, 7486, 7638, 7471, 7472, 7697, 7946, 7949, 7993, 7994, 8835, 8859, 8538, 8611, 8671, 7141, 7119, 7161, 7115, 7116, 7118, 7183.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 26 DE AGOSTO DE 2026:
+Circuito : [8102] TORAN.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (reubicación de estructura, cambio de crucetas, podado de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani. Urbanizaciones del distrito de Uraca: A.A.H.H.Villa Electrica, Anexo La Punta Colorada, Cantas, El Pedregal, Escalerillas, La Mezana, Las Malvinas, Pitis, Punta Colorada, Sarcas, Satelite, Toran, Villa Hermosa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7111, 7151, 7156, 7166, 7171, 7135, 7134, 7136, 7113, 7124, 7120, 7125, 7127, 7128, 7126, 7130, 7142, 7117, 7121, 7122, 7132, 7129, 7131, 7155, 7153, 7154, 7176, 7178, 7188, 7198, 7499, 7486, 7638, 7471, 7472, 7697, 7946, 7949, 7993, 7994, 8835, 8859, 8538, 8611, 8671, 7141, 7119, 7161, 7115, 7116, 7118, 7183.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 24/08/2026 8:03 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 8:03</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5987&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>c176066abbee766c55c00f73f40abcd76b7455559e561b218a13cc1b1238c16b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>5986</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayma: Jorge Basadre, Mirasol de Cayma, Quinta Samay, Santa Elisa. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, El Rosario II, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de crucetas, otros trabajos de mantenimiento).</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Alto Cayma desde BC - 070110.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>10132, 3471, 3961, 4458, 3576, 1844, 2424, 3472, 5417, 3793, 3792, 4365, 4582, 5024, 5016, 4913, 5621.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 26 DE AGOSTO DE 2026:
+Circuito : Alto Cayma desde BC - 070110.
+Hora : 07:30 a 13:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de crucetas, otros trabajos de mantenimiento).
+Zonas afectadas: Urbanizaciones del distrito de Cayma: Jorge Basadre, Mirasol de Cayma, Quinta Samay, Santa Elisa. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, El Rosario II, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10132, 3471, 3961, 4458, 3576, 1844, 2424, 3472, 5417, 3793, 3792, 4365, 4582, 5024, 5016, 4913, 5621.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 24/08/2026 8:00 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 8:00</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5986&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>59588707a3f3aeab599ecb8d26eed47e91fd680a91e437f634f23edb5ed2781c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1838.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 26 DE AGOSTO DE 2026.
+Circuito : SED 1838.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Cambio de transformador.
+Zonas afectadas: Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 24/08/2026 7:55 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 7:55</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5981&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>029dd91a28e1581742d74a7b61601ca24abfac61a379ad4da149b74c9bc0e748</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Mz. D-E de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de la subestación.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1829.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 26 DE AGOSTO DE 2026.
+Circuito : SED 1829.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de la subestación.
+Zonas afectadas: Mz. D-E de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 24/08/2026 7:56 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 7:56</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5982&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>84d34f78db310a1b25837890292fedcbe049515b2e253cb367e35bad7a20c49d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Aplao, de Aplao</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Aplao: Anexo Central Zonas 1 y 2, La Central, Andamayo 1-2, Buenos Aires, Canal Luchea, Huatipilla Baja, La Nueva Central, Luchea 1-2, Ongoro, Ongoro Bajo, San Jose de Huatiapilla Alta.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (inserción de seccionador, cambio de crucetas, podado de árboles).</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Corire desde REC - 200280.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7001, 7004, 7014, 8855, 7003, 7002, 7481, 7482, 7483, 7005, 7008, 7007, 7013, 7144, 7157, 7012, 7011, 7193, 7010, 7009, 7497, 7492, 7491, 7490, 10256, 7489, 7488, 7487, 7493, 7498.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 27 DE AGOSTO DE 2026:
+Circuito : Corire desde REC - 200280.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (inserción de seccionador, cambio de crucetas, podado de árboles).
+Zonas afectadas: Urbanizaciones del distrito de Aplao: Anexo Central Zonas 1 y 2, La Central, Andamayo 1-2, Buenos Aires, Canal Luchea, Huatipilla Baja, La Nueva Central, Luchea 1-2, Ongoro, Ongoro Bajo, San Jose de Huatiapilla Alta.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7001, 7004, 7014, 8855, 7003, 7002, 7481, 7482, 7483, 7005, 7008, 7007, 7013, 7144, 7157, 7012, 7011, 7193, 7010, 7009, 7497, 7492, 7491, 7490, 10256, 7489, 7488, 7487, 7493, 7498.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 24/08/2026 8:05 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026 8:05</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5989&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>444059b630e5ba6099a5ea7e1076636112c82af7e00335d1b325317e98068b1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5988</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Yanahuara, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Yanahuara: Urb. Ibarguen, Yanahuara.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión (Subsanación de deficiencias).</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Saga desde EMT - 19939</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3271, 1217.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 27 DE AGOSTO DE 2026:
+Circuito : Saga desde EMT - 19939
+Hora : 07:30 a 15:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión (Subsanación de deficiencias).
+Zonas afectadas: Urbanizaciones del distrito de Yanahuara: Urb. Ibarguen, Yanahuara.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3271, 1217.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 24/08/2026 8:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 8:03</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5988&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>f1596169cee2d65c4e656c981468240a56f972429fe433a8a371548e21040d81</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de crucetas y otras actividades de mantenimiento).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Mejia desde BC - 360119.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 28 DE AGOSTO DE 2026:
+Circuito : Mejia desde BC - 360119.
+Hora : 07:30 a 16:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de postes, cambio de crucetas y otras actividades de mantenimiento).
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: Costa Palmeras.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 26/08/2026 8:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 8:06</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5990&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4862a0c5f803c3f5ec1e65e2d9b773bb474a0c51e5cb323aab622ea1feb930a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de subestación.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1839.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 28 DE AGOSTO DE 2026.
+Circuito : SED 1839.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de subestación.
+Zonas afectadas: Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 26/08/2026 8:08 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 8:08</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5991&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>ce92b856854feb8ebe671a992c698734370882c11aaf5bfdd277dd673a70761b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5992</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento y limpieza de subestación.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1836</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 28 DE AGOSTO DE 2026.
+Circuito : SED 1836.
+Hora : 08:00 a 12:30 Hrs.
+Motivo : Mantenimiento y limpieza de subestación.
+Zonas afectadas: Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 26/08/2026 8:09 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026 8:09</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5992&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>089d8f5fdac3010c6660713b332d6c8c95ebd758813ac503ec6674d58f77cb1f</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -582,169 +1349,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26 10:53:31</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27 20:33:43</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>REQUESTS_STATIC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
+      <c r="B16" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P10" headerRowCount="1">
-  <autoFilter ref="A1:P10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
+  <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nicolas de Pierola, Uraca, de Nicolas de Pierola, de Uraca</t>
+          <t>Aplao, de Aplao</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani. Urbanizaciones del distrito de Uraca: A.A.H.H.Villa Electrica, Anexo La Punta Colorada, Cantas, El Pedregal, Escalerillas, La Mezana, Las Malvinas, Pitis, Punta Colorada, Sarcas, Satelite, Toran, Villa Hermosa.</t>
+          <t>Urbanizaciones del distrito de Aplao: Anexo Central Zonas 1 y 2, La Central, Andamayo 1-2, Buenos Aires, Canal Luchea, Huatipilla Baja, La Nueva Central, Luchea 1-2, Ongoro, Ongoro Bajo, San Jose de Huatiapilla Alta.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (reubicación de estructura, cambio de crucetas, podado de árboles).</t>
+          <t>Mantenimiento de redes de media tensión (inserción de seccionador, cambio de crucetas, podado de árboles).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [8102] TORAN.</t>
+          <t>Circuito : Corire desde REC - 200280.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,336 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7111, 7151, 7156, 7166, 7171, 7135, 7134, 7136, 7113, 7124, 7120, 7125, 7127, 7128, 7126, 7130, 7142, 7117, 7121, 7122, 7132, 7129, 7131, 7155, 7153, 7154, 7176, 7178, 7188, 7198, 7499, 7486, 7638, 7471, 7472, 7697, 7946, 7949, 7993, 7994, 8835, 8859, 8538, 8611, 8671, 7141, 7119, 7161, 7115, 7116, 7118, 7183.</t>
+          <t>7001, 7004, 7014, 8855, 7003, 7002, 7481, 7482, 7483, 7005, 7008, 7007, 7013, 7144, 7157, 7012, 7011, 7193, 7010, 7009, 7497, 7492, 7491, 7490, 10256, 7489, 7488, 7487, 7493, 7498.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 26 DE AGOSTO DE 2026:
-Circuito : [8102] TORAN.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (reubicación de estructura, cambio de crucetas, podado de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani. Urbanizaciones del distrito de Uraca: A.A.H.H.Villa Electrica, Anexo La Punta Colorada, Cantas, El Pedregal, Escalerillas, La Mezana, Las Malvinas, Pitis, Punta Colorada, Sarcas, Satelite, Toran, Villa Hermosa.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7111, 7151, 7156, 7166, 7171, 7135, 7134, 7136, 7113, 7124, 7120, 7125, 7127, 7128, 7126, 7130, 7142, 7117, 7121, 7122, 7132, 7129, 7131, 7155, 7153, 7154, 7176, 7178, 7188, 7198, 7499, 7486, 7638, 7471, 7472, 7697, 7946, 7949, 7993, 7994, 8835, 8859, 8538, 8611, 8671, 7141, 7119, 7161, 7115, 7116, 7118, 7183.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 24/08/2026 8:03 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 8:03</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5987&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>c176066abbee766c55c00f73f40abcd76b7455559e561b218a13cc1b1238c16b</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5986</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, Cerro Colorado, de Cayma, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayma: Jorge Basadre, Mirasol de Cayma, Quinta Samay, Santa Elisa. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, El Rosario II, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de crucetas, otros trabajos de mantenimiento).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Alto Cayma desde BC - 070110.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>10132, 3471, 3961, 4458, 3576, 1844, 2424, 3472, 5417, 3793, 3792, 4365, 4582, 5024, 5016, 4913, 5621.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 26 DE AGOSTO DE 2026:
-Circuito : Alto Cayma desde BC - 070110.
-Hora : 07:30 a 13:30 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de crucetas, otros trabajos de mantenimiento).
-Zonas afectadas: Urbanizaciones del distrito de Cayma: Jorge Basadre, Mirasol de Cayma, Quinta Samay, Santa Elisa. Urbanizaciones del distrito de Cerro Colorado: Camargo, Casaparq, El Rosario II, Las Terrazas del Rosario, Quinta El Sol, Virgen del Rosario I.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 10132, 3471, 3961, 4458, 3576, 1844, 2424, 3472, 5417, 3793, 3792, 4365, 4582, 5024, 5016, 4913, 5621.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 24/08/2026 8:00 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 8:00</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5986&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>59588707a3f3aeab599ecb8d26eed47e91fd680a91e437f634f23edb5ed2781c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5981</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1838.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 26 DE AGOSTO DE 2026.
-Circuito : SED 1838.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Cambio de transformador.
-Zonas afectadas: Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 24/08/2026 7:55 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 7:55</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5981&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>029dd91a28e1581742d74a7b61601ca24abfac61a379ad4da149b74c9bc0e748</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5982</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Mz. D-E de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de la subestación.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1829.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 26 DE AGOSTO DE 2026.
-Circuito : SED 1829.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de la subestación.
-Zonas afectadas: Mz. D-E de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 24/08/2026 7:56 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 7:56</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5982&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>84d34f78db310a1b25837890292fedcbe049515b2e253cb367e35bad7a20c49d</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>27/08/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Aplao, de Aplao</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Aplao: Anexo Central Zonas 1 y 2, La Central, Andamayo 1-2, Buenos Aires, Canal Luchea, Huatipilla Baja, La Nueva Central, Luchea 1-2, Ongoro, Ongoro Bajo, San Jose de Huatiapilla Alta.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (inserción de seccionador, cambio de crucetas, podado de árboles).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Corire desde REC - 200280.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7001, 7004, 7014, 8855, 7003, 7002, 7481, 7482, 7483, 7005, 7008, 7007, 7013, 7144, 7157, 7012, 7011, 7193, 7010, 7009, 7497, 7492, 7491, 7490, 10256, 7489, 7488, 7487, 7493, 7498.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 27 DE AGOSTO DE 2026:
@@ -978,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7001, 7004, 7014, 8855, 7003, 7002, 7481, 7482, 7483, 7005, 7008, 7007, 7013, 7144, 7157, 7012, 7011, 7193, 7010, 7009, 7497, 7492, 7491, 7490, 10256, 7489, 7488, 7487, 7493, 7498.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 24/08/2026 8:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>24/08/2026 8:05</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5989&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>444059b630e5ba6099a5ea7e1076636112c82af7e00335d1b325317e98068b1a</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5988</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>27/08/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Yanahuara: Urb. Ibarguen, Yanahuara.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión (Subsanación de deficiencias).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Saga desde EMT - 19939</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>3271, 1217.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 27 DE AGOSTO DE 2026:
@@ -1062,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3271, 1217.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 24/08/2026 8:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>26/08/2026 8:03</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5988&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>f1596169cee2d65c4e656c981468240a56f972429fe433a8a371548e21040d81</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5990</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de crucetas y otras actividades de mantenimiento).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : Mejia desde BC - 360119.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 28 DE AGOSTO DE 2026:
@@ -1146,76 +820,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 26/08/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26/08/2026 8:06</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5990&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>4862a0c5f803c3f5ec1e65e2d9b773bb474a0c51e5cb323aab622ea1feb930a9</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5991</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de subestación.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1839.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 28 DE AGOSTO DE 2026.
@@ -1225,76 +899,76 @@
 Zonas afectadas: Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 26/08/2026 8:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>26/08/2026 8:08</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5991&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>ce92b856854feb8ebe671a992c698734370882c11aaf5bfdd277dd673a70761b</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5992</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de subestación.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1836</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 28 DE AGOSTO DE 2026.
@@ -1304,30 +978,30 @@
 Zonas afectadas: Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 26/08/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>26/08/2026 8:09</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5992&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>089d8f5fdac3010c6660713b332d6c8c95ebd758813ac503ec6674d58f77cb1f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1368,7 +1042,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 20:33:43</t>
+          <t>2026-08-28 21:11:30</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1066,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1078,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1090,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1162,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1189,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P6" headerRowCount="1">
-  <autoFilter ref="A1:P6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
+  <autoFilter ref="A1:P4"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aplao, de Aplao</t>
+          <t>Mollendo, de Mollendo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Aplao: Anexo Central Zonas 1 y 2, La Central, Andamayo 1-2, Buenos Aires, Canal Luchea, Huatipilla Baja, La Nueva Central, Luchea 1-2, Ongoro, Ongoro Bajo, San Jose de Huatiapilla Alta.</t>
+          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes de media tensión (inserción de seccionador, cambio de crucetas, podado de árboles).</t>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de crucetas y otras actividades de mantenimiento).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Corire desde REC - 200280.</t>
+          <t>Circuito : Mejia desde BC - 360119.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,178 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7001, 7004, 7014, 8855, 7003, 7002, 7481, 7482, 7483, 7005, 7008, 7007, 7013, 7144, 7157, 7012, 7011, 7193, 7010, 7009, 7497, 7492, 7491, 7490, 10256, 7489, 7488, 7487, 7493, 7498.</t>
+          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 27 DE AGOSTO DE 2026:
-Circuito : Corire desde REC - 200280.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (inserción de seccionador, cambio de crucetas, podado de árboles).
-Zonas afectadas: Urbanizaciones del distrito de Aplao: Anexo Central Zonas 1 y 2, La Central, Andamayo 1-2, Buenos Aires, Canal Luchea, Huatipilla Baja, La Nueva Central, Luchea 1-2, Ongoro, Ongoro Bajo, San Jose de Huatiapilla Alta.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7001, 7004, 7014, 8855, 7003, 7002, 7481, 7482, 7483, 7005, 7008, 7007, 7013, 7144, 7157, 7012, 7011, 7193, 7010, 7009, 7497, 7492, 7491, 7490, 10256, 7489, 7488, 7487, 7493, 7498.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 24/08/2026 8:05 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 8:05</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5989&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>444059b630e5ba6099a5ea7e1076636112c82af7e00335d1b325317e98068b1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5988</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>27/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Yanahuara, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Yanahuara: Urb. Ibarguen, Yanahuara.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes de media tensión (Subsanación de deficiencias).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Saga desde EMT - 19939</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES. SUSPENDIDO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>3271, 1217.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 27 DE AGOSTO DE 2026:
-Circuito : Saga desde EMT - 19939
-Hora : 07:30 a 15:00 Hrs.
-Motivo : Mantenimiento de redes de media tensión (Subsanación de deficiencias).
-Zonas afectadas: Urbanizaciones del distrito de Yanahuara: Urb. Ibarguen, Yanahuara.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 3271, 1217.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 24/08/2026 8:04 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>26/08/2026 8:03</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5988&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>f1596169cee2d65c4e656c981468240a56f972429fe433a8a371548e21040d81</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de crucetas y otras actividades de mantenimiento).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Mejia desde BC - 360119.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 28 DE AGOSTO DE 2026:
@@ -820,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 26/08/2026 8:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>26/08/2026 8:06</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5990&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>4862a0c5f803c3f5ec1e65e2d9b773bb474a0c51e5cb323aab622ea1feb930a9</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5991</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de subestación.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1839.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 28 DE AGOSTO DE 2026.
@@ -899,76 +731,76 @@
 Zonas afectadas: Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 26/08/2026 8:08 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>26/08/2026 8:08</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5991&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>ce92b856854feb8ebe671a992c698734370882c11aaf5bfdd277dd673a70761b</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5992</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento y limpieza de subestación.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1836</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 28 DE AGOSTO DE 2026.
@@ -978,30 +810,30 @@
 Zonas afectadas: Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 26/08/2026 8:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26/08/2026 8:09</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5992&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>089d8f5fdac3010c6660713b332d6c8c95ebd758813ac503ec6674d58f77cb1f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P6"/>
+  <autoFilter ref="A1:P4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1042,7 +874,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:11:30</t>
+          <t>2026-08-29 15:06:17</t>
         </is>
       </c>
     </row>
@@ -1066,7 +898,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1078,7 +910,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -1090,7 +922,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1162,7 +994,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1021,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,13 +80,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -171,31 +168,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P4" headerRowCount="1">
-  <autoFilter ref="A1:P4"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Fecha"/>
-    <tableColumn id="3" name="Hora inicio"/>
-    <tableColumn id="4" name="Hora fin"/>
-    <tableColumn id="5" name="Distrito"/>
-    <tableColumn id="6" name="Zona afectada"/>
-    <tableColumn id="7" name="Motivo"/>
-    <tableColumn id="8" name="Ubicación"/>
-    <tableColumn id="9" name="Título"/>
-    <tableColumn id="10" name="Subestaciones / SED"/>
-    <tableColumn id="11" name="Descripción completa"/>
-    <tableColumn id="12" name="Categoría"/>
-    <tableColumn id="13" name="Creado"/>
-    <tableColumn id="14" name="Modificado"/>
-    <tableColumn id="15" name="URL"/>
-    <tableColumn id="16" name="Hash"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -590,254 +562,9 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Mollendo, de Mollendo</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Mollendo: Costa Palmeras.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de crucetas y otras actividades de mantenimiento).</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Mejia desde BC - 360119.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 28 DE AGOSTO DE 2026:
-Circuito : Mejia desde BC - 360119.
-Hora : 07:30 a 16:30 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de postes, cambio de crucetas y otras actividades de mantenimiento).
-Zonas afectadas: Urbanizaciones del distrito de Mollendo: Costa Palmeras.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8103, 8100, 8637, 8106, 8105, 8429, 8098, 8491, 8654, 8474, 8099, 8101, 8293, 8108, 8302, 8497, 8466, 8467, 8104, 8102.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 26/08/2026 8:06 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>26/08/2026 8:06</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5990&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>4862a0c5f803c3f5ec1e65e2d9b773bb474a0c51e5cb323aab622ea1feb930a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de subestación.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1839.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 28 DE AGOSTO DE 2026.
-Circuito : SED 1839.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de subestación.
-Zonas afectadas: Mz. B de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 26/08/2026 8:08 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>26/08/2026 8:08</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5991&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>ce92b856854feb8ebe671a992c698734370882c11aaf5bfdd277dd673a70761b</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5992</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento y limpieza de subestación.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1836</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-VIERNES, 28 DE AGOSTO DE 2026.
-Circuito : SED 1836.
-Hora : 08:00 a 12:30 Hrs.
-Motivo : Mantenimiento y limpieza de subestación.
-Zonas afectadas: Mz. B-G de Urb. Parque Industrial Rio Seco (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 26/08/2026 8:09 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26/08/2026 8:09</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5992&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>089d8f5fdac3010c6660713b332d6c8c95ebd758813ac503ec6674d58f77cb1f</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P4"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -855,173 +582,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
+      <c r="B1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-29 15:06:17</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30 14:53:26</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>REQUESTS_STATIC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>3</v>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,10 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,6 +171,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P21" headerRowCount="1">
+  <autoFilter ref="A1:P21"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Hora inicio"/>
+    <tableColumn id="4" name="Hora fin"/>
+    <tableColumn id="5" name="Distrito"/>
+    <tableColumn id="6" name="Zona afectada"/>
+    <tableColumn id="7" name="Motivo"/>
+    <tableColumn id="8" name="Ubicación"/>
+    <tableColumn id="9" name="Título"/>
+    <tableColumn id="10" name="Subestaciones / SED"/>
+    <tableColumn id="11" name="Descripción completa"/>
+    <tableColumn id="12" name="Categoría"/>
+    <tableColumn id="13" name="Creado"/>
+    <tableColumn id="14" name="Modificado"/>
+    <tableColumn id="15" name="URL"/>
+    <tableColumn id="16" name="Hash"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -562,9 +590,1612 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>6006</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores, de Miraflores</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra N° 3 de Calle Elías Aguirre (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 10169.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 31 DE AGOSTO DE 2026.
+Circuito : SED 10169.
+Hora : 05:30 a 06:00 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra N° 3 de Calle Elías Aguirre (Distrito de Miraflores).</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:34 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:34</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6006&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>a49fd013b2f20297b4ee7e82ee157b59ca57bc14ce2a241e49b1e22dce7288b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Mariano Melgar, de Mariano Melgar</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 10-12 de Av. Lima, cuadra 12-13-14-15 de Av. Simón Bolívar, cuadra 5 de Calle Ameria, cuadra 3 Calle Amazonas, cuadra 5 de Calle Arias (Distrito de Mariano Melgar).</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1942.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 31 DE AGOSTO DE 2026.
+Circuito : SED 1942.
+Hora : 06:20 a 06:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 10-12 de Av. Lima, cuadra 12-13-14-15 de Av. Simón Bolívar, cuadra 5 de Calle Ameria, cuadra 3 Calle Amazonas, cuadra 5 de Calle Arias (Distrito de Mariano Melgar).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:35 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:35</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6007&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>dd68ed5e470e91dce562cf03b7cc8cd8bb86a92c6b0a36a5bc442be33d58c617</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6011</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 7-8-9 de Av. Arequipa, cuadra 8-9-10 de Av. Ramon Castilla (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de conductor y cambio de EBT.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5620</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 31 DE AGOSTO DE 2026.
+Circuito : SED 5620.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Cambio de conductor y cambio de EBT.
+Zonas afectadas: Cuadra 7-8-9 de Av. Arequipa, cuadra 8-9-10 de Av. Ramon Castilla (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:37 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:37</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6011&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>72bb0a57fd5afe335a1ef31ed882ff46fc2470739abdc2b21198a1c3bddf85cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6008</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Mz. T-U -V de Urb. Quinta Tristán (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1438.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 31 DE AGOSTO DE 2026.
+Circuito : SED 1438.
+Hora : 08:00 a 08:30 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. T-U -V de Urb. Quinta Tristán (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:35 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:35</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6008&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>04422bff66cd075e0f2d03db955933a73038d169b00dde07be968255998d3716</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Dean Valdivia, de Dean Valdivia</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Dean Valdivia: Irrigación Iberia.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de conductor, limpieza de aisladores, mantenimiento de subestación).</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Ensenada desde CC - 370226.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8358, 8359, 8361, 8360.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 31 DE AGOSTO DE 2026:
+Circuito : Ensenada desde CC - 370226.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de conductor, limpieza de aisladores, mantenimiento de subestación).
+Zonas afectadas: Urbanizaciones del distrito de Dean Valdivia: Irrigación Iberia.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8358, 8359, 8361, 8360.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:38 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:38</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6012&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>6807449ae5eb287536f67c348d814fa525a6da3da90ee29eceb864d95419967c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Residencial VIVE (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 5622</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 31 DE AGOSTO DE 2026.
+Circuito : SED 5622.
+Hora : 08:30 a 09:00 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Residencial VIVE (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:36 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:36</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6009&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>31c054527f4657e4f066d2b52c1897d0745255f9d50318d976200d4805777697</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6010</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Characato, de Characato</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Mz. 2-3-4 Sector E de AA.HH. Horacio Zeballos Gamez (Distrito de Characato).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3681.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+LUNES, 31 DE AGOSTO DE 2026.
+Circuito : SED 3681.
+Hora : 09:30 a 10:00 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. 2-3-4 Sector E de AA.HH. Horacio Zeballos Gamez (Distrito de Characato).</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:36 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:36</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6010&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>f6fab5a6b8b77f187fe37712b9355b4d757f6c8a685c9c4519a02fba2d2feb21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Aplao, de Aplao</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Aplao: Los Puros.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (Podado de árboles, cambio de postes, cambio de crucetas).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Corire desde CC - 810129.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7066.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MARTES, 01 DE SETIEMBRE DE 2026:
+Circuito : Corire desde CC - 810129.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (Podado de árboles, cambio de postes, cambio de crucetas).
+Zonas afectadas: Urbanizaciones del distrito de Aplao: Los Puros.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7066.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:12 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:12</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5993&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>782396809f3ab75eb1d0e626686cf63b8f49586265bf2730a311249194d91c80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5994</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayma: 1 de Junio Zona A, 30 de Marzo, Acequia Alta, Charcani Chapi Chico, Francisco Bolognesi, Jose Olaya, Juan Velasco Alvarado, La Tomilla Zona C, Rafael Belaunde Diez Canseco Zona A-C, San Martin de Porres, Villa El Mirador.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [1701] CHACHANI.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026:
+Circuito : [1701] CHACHANI.
+Hora : 08:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión.
+Zonas afectadas: Urbanizaciones del distrito de Cayma: 1 de Junio Zona A, 30 de Marzo, Acequia Alta, Charcani Chapi Chico, Francisco Bolognesi, Jose Olaya, Juan Velasco Alvarado, La Tomilla Zona C, Rafael Belaunde Diez Canseco Zona A-C, San Martin de Porres, Villa El Mirador.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:13 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:13</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5994&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>689092c9a8d94730ffb51eb4289cb92b5604087fe86d9f1f1b346e4af0f0170c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5995</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Yanahuara, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3257.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 3257.
+Hora : 08:00 a 08:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:14 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:14</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5995&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>b2cb1294637255df7e81e1e794cdb5e73a2eb3bcbaea11bc1a48f8c115193493</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5996</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Yanahuara, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1450.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 1450.
+Hora : 08:30 a 08:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:17 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:17</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5996&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>731c6f480b229404944fab3f07c10efdce5a22e104bb45b16d8ffc0f525c80b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>5997</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Yanahuara, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3264.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 3264.
+Hora : 09:00 a 09:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:21 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:21</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5997&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>b5edd2d9ef183847fee1539275c380fc5bcd212aa5b98cb8ad3fd33cca92ec54</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5998</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Yanahuara, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3263.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 3263.
+Hora : 09:30 a 09:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:22 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:22</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5998&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>b7d153ca18abc4cb6eb956bbddedac6ab20d1ea64ac5488e31d9adeac33ef1bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>5999</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Yanahuara, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1800.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 1800.
+Hora : 10:00 a 10:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:23</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5999&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>ae64e076a14a38c9b9f8f758922b93ed487635a9c4fe0d160c68015603056e4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, de Cayma</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urb. El Señorial (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1542.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 1542.
+Hora : 10:30 a 10:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Urb. El Señorial (Distrito de Cayma).</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:23</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6000&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>ec3d14f94585eda9e2aa9fb040ee74c971c21fe804c09395d21e3cdaa2ea8076</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Cayma, de Cerro Cayma</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3166.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 3166.
+Hora : 11:00 a 11:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:24 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:24</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6001&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>31f5824a8b64f3291c0e7896881f2752f7d7b0480214982b9c35729a24372e77</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 2596.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 2596.
+Hora : 14:00 a 14:20 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:31 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:31</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6002&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>9cbfa3dff2d6b0debe64d6379bd6b90e2fb033ff2447d9deef201c258dea30b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Yura, de Yura</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 10292.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 10292.
+Hora : 14:40 a 15:00 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:32</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6003&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>8b291e4a5cc7f5eeb932f91fc95c6c5b5c90cc379abc3942a24224a462610f4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3697</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
+Circuito : SED 3697.
+Hora : 15:40 a 16:00 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:32</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6004&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6f2269335f482bf152f818302bfba2e79d7347a26921e5b67e40027df0e92d1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Nicolas de Pierola, de Nicolas de Pierola</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de transformador, cambio de crucetas, aisladores y podado)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Toran desde CC - 810132.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>8611, 7153, 7154, 7155.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+JUEVES, 03 DE SETIEMBRE DE 2026:
+Circuito : Toran desde CC - 810132.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Cambio de transformador, cambio de crucetas, aisladores y podado)
+Zonas afectadas: Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8611, 7153, 7154, 7155.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:33 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:33</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6005&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>899326f4376898673d82bd0aef6af9f54f80ef232fa975b6a83272ec55fe727e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -582,173 +2213,173 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>APP Seal - Resumen de extracción</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
+      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>fecha_ejecucion</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-30 14:53:26</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:38:35</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/SitePages/Cortes.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>fecha_base</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>fecha_inicio</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>fecha_inicio</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>fecha_fin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>dias_atras</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>dias_adelante</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>metodo_ids</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>REQUESTS_STATIC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ids_detectados</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>eventos_totales_extraidos</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>eventos_guardados_en_rango</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>docs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Total cortes</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
+      <c r="B16" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31 17:38:35</t>
+          <t>2026-09-01 14:56:44</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P21" headerRowCount="1">
-  <autoFilter ref="A1:P21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P14" headerRowCount="1">
+  <autoFilter ref="A1:P14"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,42 +593,42 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Miraflores, de Miraflores</t>
+          <t>Aplao, de Aplao</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Cuadra N° 3 de Calle Elías Aguirre (Distrito de Miraflores).</t>
+          <t>Urbanizaciones del distrito de Aplao: Los Puros.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de posición del conmutador.</t>
+          <t>Mantenimiento de redes en media tensión (Podado de árboles, cambio de postes, cambio de crucetas).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : SED 10169.</t>
+          <t>Circuito : Corire desde CC - 810129.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,570 +636,12 @@
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>7066.</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 31 DE AGOSTO DE 2026.
-Circuito : SED 10169.
-Hora : 05:30 a 06:00 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra N° 3 de Calle Elías Aguirre (Distrito de Miraflores).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:34 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:34</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6006&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>a49fd013b2f20297b4ee7e82ee157b59ca57bc14ce2a241e49b1e22dce7288b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mariano Melgar, de Mariano Melgar</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 10-12 de Av. Lima, cuadra 12-13-14-15 de Av. Simón Bolívar, cuadra 5 de Calle Ameria, cuadra 3 Calle Amazonas, cuadra 5 de Calle Arias (Distrito de Mariano Melgar).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1942.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 31 DE AGOSTO DE 2026.
-Circuito : SED 1942.
-Hora : 06:20 a 06:50 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra 10-12 de Av. Lima, cuadra 12-13-14-15 de Av. Simón Bolívar, cuadra 5 de Calle Ameria, cuadra 3 Calle Amazonas, cuadra 5 de Calle Arias (Distrito de Mariano Melgar).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:35 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:35</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6007&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>dd68ed5e470e91dce562cf03b7cc8cd8bb86a92c6b0a36a5bc442be33d58c617</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>6011</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 7-8-9 de Av. Arequipa, cuadra 8-9-10 de Av. Ramon Castilla (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de conductor y cambio de EBT.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5620</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 31 DE AGOSTO DE 2026.
-Circuito : SED 5620.
-Hora : 07:30 a 15:30 Hrs.
-Motivo : Cambio de conductor y cambio de EBT.
-Zonas afectadas: Cuadra 7-8-9 de Av. Arequipa, cuadra 8-9-10 de Av. Ramon Castilla (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:37 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:37</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6011&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>72bb0a57fd5afe335a1ef31ed882ff46fc2470739abdc2b21198a1c3bddf85cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>6008</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Mz. T-U -V de Urb. Quinta Tristán (Distrito de Jose Luis Bustamante y Rivero).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1438.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 31 DE AGOSTO DE 2026.
-Circuito : SED 1438.
-Hora : 08:00 a 08:30 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. T-U -V de Urb. Quinta Tristán (Distrito de Jose Luis Bustamante y Rivero).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:35 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:35</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6008&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>04422bff66cd075e0f2d03db955933a73038d169b00dde07be968255998d3716</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6012</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Dean Valdivia, de Dean Valdivia</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Dean Valdivia: Irrigación Iberia.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de conductor, limpieza de aisladores, mantenimiento de subestación).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Ensenada desde CC - 370226.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8358, 8359, 8361, 8360.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 31 DE AGOSTO DE 2026:
-Circuito : Ensenada desde CC - 370226.
-Hora : 08:00 a 16:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (cambio de conductor, limpieza de aisladores, mantenimiento de subestación).
-Zonas afectadas: Urbanizaciones del distrito de Dean Valdivia: Irrigación Iberia.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8358, 8359, 8361, 8360.</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:38 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:38</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6012&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>6807449ae5eb287536f67c348d814fa525a6da3da90ee29eceb864d95419967c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6009</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Residencial VIVE (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 5622</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 31 DE AGOSTO DE 2026.
-Circuito : SED 5622.
-Hora : 08:30 a 09:00 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Residencial VIVE (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:36 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:36</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6009&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>31c054527f4657e4f066d2b52c1897d0745255f9d50318d976200d4805777697</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>6010</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Characato, de Characato</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Mz. 2-3-4 Sector E de AA.HH. Horacio Zeballos Gamez (Distrito de Characato).</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3681.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-LUNES, 31 DE AGOSTO DE 2026.
-Circuito : SED 3681.
-Hora : 09:30 a 10:00 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. 2-3-4 Sector E de AA.HH. Horacio Zeballos Gamez (Distrito de Characato).</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:36 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:36</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6010&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>f6fab5a6b8b77f187fe37712b9355b4d757f6c8a685c9c4519a02fba2d2feb21</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>5993</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Aplao, de Aplao</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Aplao: Los Puros.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (Podado de árboles, cambio de postes, cambio de crucetas).</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Corire desde CC - 810129.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7066.</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MARTES, 01 DE SETIEMBRE DE 2026:
@@ -1210,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7066.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:12 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:12</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5993&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>782396809f3ab75eb1d0e626686cf63b8f49586265bf2730a311249194d91c80</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5994</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: 1 de Junio Zona A, 30 de Marzo, Acequia Alta, Charcani Chapi Chico, Francisco Bolognesi, Jose Olaya, Juan Velasco Alvarado, La Tomilla Zona C, Rafael Belaunde Diez Canseco Zona A-C, San Martin de Porres, Villa El Mirador.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : [1701] CHACHANI.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026:
@@ -1294,76 +736,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:13</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5994&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>689092c9a8d94730ffb51eb4289cb92b5604087fe86d9f1f1b346e4af0f0170c</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5995</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3257.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1373,76 +815,76 @@
 Zonas afectadas: Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:14</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5995&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>b2cb1294637255df7e81e1e794cdb5e73a2eb3bcbaea11bc1a48f8c115193493</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5996</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>08:50</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1450.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1452,76 +894,76 @@
 Zonas afectadas: Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:17</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5996&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>731c6f480b229404944fab3f07c10efdce5a22e104bb45b16d8ffc0f525c80b9</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5997</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>09:20</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3264.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1531,76 +973,76 @@
 Zonas afectadas: Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:21 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:21</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5997&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>b5edd2d9ef183847fee1539275c380fc5bcd212aa5b98cb8ad3fd33cca92ec54</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5998</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>09:50</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3263.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1610,76 +1052,76 @@
 Zonas afectadas: Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:22</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5998&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>b7d153ca18abc4cb6eb956bbddedac6ab20d1ea64ac5488e31d9adeac33ef1bd</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5999</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1800.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1689,76 +1131,76 @@
 Zonas afectadas: Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:23</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5999&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ae64e076a14a38c9b9f8f758922b93ed487635a9c4fe0d160c68015603056e4e</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urb. El Señorial (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1542.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1768,76 +1210,76 @@
 Zonas afectadas: Urb. El Señorial (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:23</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6000&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>ec3d14f94585eda9e2aa9fb040ee74c971c21fe804c09395d21e3cdaa2ea8076</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6001</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Cerro Cayma, de Cerro Cayma</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3166.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1847,76 +1289,76 @@
 Zonas afectadas: Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:24</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6001&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>31f5824a8b64f3291c0e7896881f2752f7d7b0480214982b9c35729a24372e77</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6002</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2596.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1926,76 +1368,76 @@
 Zonas afectadas: Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:31 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:31</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6002&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>9cbfa3dff2d6b0debe64d6379bd6b90e2fb033ff2447d9deef201c258dea30b3</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6003</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>14:40</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10292.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -2005,76 +1447,76 @@
 Zonas afectadas: Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:32</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6003&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>8b291e4a5cc7f5eeb932f91fc95c6c5b5c90cc379abc3942a24224a462610f4c</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6004</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3697</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -2084,80 +1526,80 @@
 Zonas afectadas: Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:32</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6004&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>6f2269335f482bf152f818302bfba2e79d7347a26921e5b67e40027df0e92d1d</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="70" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6005</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Nicolas de Pierola, de Nicolas de Pierola</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador, cambio de crucetas, aisladores y podado)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : Toran desde CC - 810132.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>8611, 7153, 7154, 7155.</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 03 DE SETIEMBRE DE 2026:
@@ -2168,30 +1610,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8611, 7153, 7154, 7155.</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:33 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:33</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6005&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>899326f4376898673d82bd0aef6af9f54f80ef232fa975b6a83272ec55fe727e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P21"/>
+  <autoFilter ref="A1:P14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2232,7 +1674,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01 14:56:44</t>
+          <t>2026-09-02 14:32:09</t>
         </is>
       </c>
     </row>
@@ -2256,7 +1698,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -2268,7 +1710,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -2280,7 +1722,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -2328,7 +1770,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2340,7 +1782,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2352,7 +1794,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -2379,7 +1821,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P14" headerRowCount="1">
-  <autoFilter ref="A1:P14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P30" headerRowCount="1">
+  <autoFilter ref="A1:P30"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,17 +593,17 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -613,119 +613,35 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aplao, de Aplao</t>
+          <t>Cayma, de Cayma</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Aplao: Los Puros.</t>
+          <t>Urbanizaciones del distrito de Cayma: 1 de Junio Zona A, 30 de Marzo, Acequia Alta, Charcani Chapi Chico, Francisco Bolognesi, Jose Olaya, Juan Velasco Alvarado, La Tomilla Zona C, Rafael Belaunde Diez Canseco Zona A-C, San Martin de Porres, Villa El Mirador.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión (Podado de árboles, cambio de postes, cambio de crucetas).</t>
+          <t>Mantenimiento de redes en media tensión.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Corire desde CC - 810129.</t>
+          <t>Circuito : [1701] CHACHANI.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES.</t>
+          <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>7066.</t>
+          <t>4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MARTES, 01 DE SETIEMBRE DE 2026:
-Circuito : Corire desde CC - 810129.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión (Podado de árboles, cambio de postes, cambio de crucetas).
-Zonas afectadas: Urbanizaciones del distrito de Aplao: Los Puros.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7066.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:12 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:12</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5993&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>782396809f3ab75eb1d0e626686cf63b8f49586265bf2730a311249194d91c80</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5994</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Cayma: 1 de Junio Zona A, 30 de Marzo, Acequia Alta, Charcani Chapi Chico, Francisco Bolognesi, Jose Olaya, Juan Velasco Alvarado, La Tomilla Zona C, Rafael Belaunde Diez Canseco Zona A-C, San Martin de Porres, Villa El Mirador.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : [1701] CHACHANI.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026:
@@ -736,76 +652,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:13</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5994&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>689092c9a8d94730ffb51eb4289cb92b5604087fe86d9f1f1b346e4af0f0170c</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>5995</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3257.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -815,76 +731,76 @@
 Zonas afectadas: Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:14</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5995&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>b2cb1294637255df7e81e1e794cdb5e73a2eb3bcbaea11bc1a48f8c115193493</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>5996</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>08:50</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1450.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -894,76 +810,76 @@
 Zonas afectadas: Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:17 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:17</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5996&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>731c6f480b229404944fab3f07c10efdce5a22e104bb45b16d8ffc0f525c80b9</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>5997</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>09:20</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3264.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -973,76 +889,76 @@
 Zonas afectadas: Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:21 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:21</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5997&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>b5edd2d9ef183847fee1539275c380fc5bcd212aa5b98cb8ad3fd33cca92ec54</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5998</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>09:50</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3263.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1052,76 +968,76 @@
 Zonas afectadas: Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:22 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:22</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5998&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>b7d153ca18abc4cb6eb956bbddedac6ab20d1ea64ac5488e31d9adeac33ef1bd</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>5999</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Yanahuara, de Yanahuara</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1800.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1131,76 +1047,76 @@
 Zonas afectadas: Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:23</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5999&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>ae64e076a14a38c9b9f8f758922b93ed487635a9c4fe0d160c68015603056e4e</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Cayma, de Cayma</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urb. El Señorial (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1542.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1210,76 +1126,76 @@
 Zonas afectadas: Urb. El Señorial (Distrito de Cayma).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:23</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6000&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ec3d14f94585eda9e2aa9fb040ee74c971c21fe804c09395d21e3cdaa2ea8076</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6001</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Cerro Cayma, de Cerro Cayma</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3166.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1289,76 +1205,76 @@
 Zonas afectadas: Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:24 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:24</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6001&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>31f5824a8b64f3291c0e7896881f2752f7d7b0480214982b9c35729a24372e77</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6002</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 2596.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1368,76 +1284,76 @@
 Zonas afectadas: Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:31 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:31</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6002&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>9cbfa3dff2d6b0debe64d6379bd6b90e2fb033ff2447d9deef201c258dea30b3</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6003</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>14:40</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Yura, de Yura</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 10292.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1447,76 +1363,76 @@
 Zonas afectadas: Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:32</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6003&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>8b291e4a5cc7f5eeb932f91fc95c6c5b5c90cc379abc3942a24224a462610f4c</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6004</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3697</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
@@ -1526,80 +1442,80 @@
 Zonas afectadas: Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:32</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6004&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>6f2269335f482bf152f818302bfba2e79d7347a26921e5b67e40027df0e92d1d</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6005</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Nicolas de Pierola, de Nicolas de Pierola</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Cambio de transformador, cambio de crucetas, aisladores y podado)</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : Toran desde CC - 810132.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8611, 7153, 7154, 7155.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 03 DE SETIEMBRE DE 2026:
@@ -1610,30 +1526,1398 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8611, 7153, 7154, 7155.</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>el 31/08/2026 8:33 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026 8:33</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6005&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>899326f4376898673d82bd0aef6af9f54f80ef232fa975b6a83272ec55fe727e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6014</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Uraca, de Uraca</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Uraca: Bellavista, La Candelaria, Toro Grande.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, podad de árboles, cambio de crucetas).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : Corire desde CC - 810131.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7484, 7104, 7148, 7103, 7102, 7105, 7174.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026:
+Circuito : Corire desde CC - 810131.
+Hora : 07:00 a 15:00 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de postes, podad de árboles, cambio de crucetas).
+Zonas afectadas: Urbanizaciones del distrito de Uraca: Bellavista, La Candelaria, Toro Grande.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7484, 7104, 7148, 7103, 7102, 7105, 7174.</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>el 31/08/2026 8:33 por Cuenta del sistema</t>
+          <t>el 02/09/2026 17:59 por Cuenta del sistema</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026 8:33</t>
+          <t>02/09/2026 17:59</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6005&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6014&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>899326f4376898673d82bd0aef6af9f54f80ef232fa975b6a83272ec55fe727e</t>
+          <t>47172288e10064d0027470fa61df82dc98c36097a35feb79f6983f71752ff85f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>6016</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Mollendo, de Mollendo</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Mollendo: El Mirador Al Pacifico, La Victoria, Villa Lourdes 1-2 Etapa.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de transformador, otros mantenimientos).</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : La Florida desde BC - 200566.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8256, 8072, 8069, 8071, 8579, 8073.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026:
+Circuito : La Florida desde BC - 200566.
+Hora : 07:30 a 15:30 Hrs.
+Motivo : Mantenimiento de redes en media tensión (cambio de postes, cambio de transformador, otros mantenimientos).
+Zonas afectadas: Urbanizaciones del distrito de Mollendo: El Mirador Al Pacifico, La Victoria, Villa Lourdes 1-2 Etapa.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8256, 8072, 8069, 8071, 8579, 8073.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:02 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:02</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6016&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>03131189727b6099f258787edbaa3c05152a4130e0f164c65f11a3d18d08ee59</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Colorado, de Cerro Colorado</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones de distrito de Cerro Colorado: Apipa Sector IX-X-VIII-XII, Jose Luis Bustamante y Rivero</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de redes de media tensión.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : P. Yura desde BC - 080313.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5136, 5138, 5137, 5440, 5441, 5442, 5443, 5444, 5445, 5852.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026:
+Circuito : P. Yura desde BC - 080313.
+Hora : 08:00 a 14:00 Hrs.
+Motivo : Mantenimiento de redes de media tensión.
+Zonas afectadas: Urbanizaciones de distrito de Cerro Colorado: Apipa Sector IX-X-VIII-XII, Jose Luis Bustamante y Rivero
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5136, 5138, 5137, 5440, 5441, 5442, 5443, 5444, 5445, 5852.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:01 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6015&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>b6bc3059c534ec14beaff64f9802c9b904dd1632d98146dc0b54235f2ff38869</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6017</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Urb. San Jeronimo, Mz.B de Urb. Los Pilcos (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1283.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 1283.
+Hora : 08:00 a 08:25 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Urb. San Jeronimo, Mz.B de Urb. Los Pilcos (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:04</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6017&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>51ee02cf1b89f80117c359a7e45962bee4cd30ff7ef36f971b3b17b0182dfa3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6018</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Cooperativa Ferroviaria (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1282.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 1282.
+Hora : 08:45 a 09:10 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Urb. Cooperativa Ferroviaria (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:04 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:04</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6018&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>a6c76d6fb5ac0f8e42e8210edd35ab708eb0e3ed03abefce94dac22d20d1bd3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>6019</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 1 de Calle Prolongación Vitor Lira (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3898.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 3898.
+Hora : 09:30 a 09:55 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 1 de Calle Prolongación Vitor Lira (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:05 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:05</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6019&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>78747bc2ace2e3e68d747edc95fd809315add28df59793e1e19278041a26d3c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6020</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Arequipa, de Arequipa</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Francisco Mostajo (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1747.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 1747.
+Hora : 10:10 a 10:35 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Urb. Francisco Mostajo (Distrito de Arequipa).</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:06</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6020&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>33a0d1176ab1e83295183e5f2101d6aa80877c1249672e3d9b5f389659d272ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra 1 de Av. Dolores (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3417.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 3417.
+Hora : 10:30 a 11:55 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Cuadra 1 de Av. Dolores (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:09 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:09</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6022&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>d808b96cd47f10923eb6e33ed94b59b01e4467a6ec77cc6ac55d0813cc0dd7e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="70" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Mz. B-C-D de Urb. Los Rosales (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3859.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 3859.
+Hora : 10:50 a 11:15 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. B-C-D de Urb. Los Rosales (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:06 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:06</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6021&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>e33844d951c1e00dbc0a2726bb00b877de12101b1d7bba34fa50a2016a5fcf24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Mz. G de Urb. Cooperativa Daniel Alcides Carrión (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3855.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 3855.
+Hora : 12:10 a 12:35 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. G de Urb. Cooperativa Daniel Alcides Carrión (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:10</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6023&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>a5c5861c03766cc65a49278896ed7c6cdde20072f3fb9b68e721d3f9842439b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Paucarpata, de Paucarpata</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>II Etapa de Urb. Guardia Civil (Distrito de Paucarpata).</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1299.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 1299.
+Hora : 14:00 a 14:25 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: II Etapa de Urb. Guardia Civil (Distrito de Paucarpata).</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:10 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:10</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6024&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>8ac102f43023f77e323fb0077f77ebdaab1e91373df7ee1983203ffa421c53e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="70" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Urb. La Encalada (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 1738</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 1738.
+Hora : 14:40 a 15:05 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Urb. La Encalada (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:11 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:11</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6025&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>ad5f909b4fb973508e48baa3afa0bf3570867b6594a80b040975afbbd7e9c2eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="70" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Mz. C-D-E-L de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3612.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 3612.
+Hora : 15:15 a 15:40 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. C-D-E-L de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:12 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:12</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6026&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2dbe2978b023cbe86aaf594864d76981c0e89201154c1633ff36b2f686c1a81a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="70" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>6027</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Mz. F-G-H-I-J de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 3613.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 3613.
+Hora : 15:50 a 16:15 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. F-G-H-I-J de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:13 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6027&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>5132a83c0e658459b576364f7c44a4520c099e73217c7e525d63bc3800f90527</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="70" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mz. A-B-D-E-J de Urb. Alameda del Sol, MZ. A-B-D-E-F de Urb. Santa Úrsula (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Cambio de posición del conmutador.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : SED 4404.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+VIERNES, 04 DE SETIEMBRE DE 2026.
+Circuito : SED 4404.
+Hora : 16:25 a 16:50 Hrs.
+Motivo : Cambio de posición del conmutador.
+Zonas afectadas: Mz. A-B-D-E-J de Urb. Alameda del Sol, MZ. A-B-D-E-F de Urb. Santa Úrsula (Distrito de Jose Luis Bustamante y Rivero).</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:13 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6028&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>e49d0bd12f6b0c5d09ab03365ea56a1e5734ccee810823e79ab3bc4f4309cdb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>6013</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento del transformador de la subestación de Caylloma.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Circuito : [9301] SAN ANTONIO.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+SÁBADO, 05 DE SETIEMBRE DE 2026:
+Circuito : [9301] SAN ANTONIO.
+Hora : 06:00 a 18:00 Hrs.
+Motivo : Mantenimiento del transformador de la subestación de Caylloma.
+Zonas afectadas: Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 17:58 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 17:58</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6013&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>87cae465b632a656491c44ae0cc47040622c28e945e4feb4714ea9c02b51d013</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="70" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Mantenimiento de transformador de potencia.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>SET : [7] CHALLAPAMPA.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO DE REDES.
+DOMINGO, 06 DE SETIEMBRE DE 2026:
+SET : [7] CHALLAPAMPA.
+Hora : 08:00 a 16:00 Hrs.
+Motivo : Mantenimiento de transformador de potencia.
+Zonas afectadas: Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.
+Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>el 02/09/2026 18:14 por Cuenta del sistema</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>02/09/2026 18:14</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6029&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>d97067c0261932b1d64c143bed897ec74373434e8a879bfb1928de309a3cfa3b</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
+  <autoFilter ref="A1:P30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1674,7 +2958,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:32:09</t>
+          <t>2026-09-03 14:36:51</t>
         </is>
       </c>
     </row>
@@ -1698,7 +2982,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -1710,7 +2994,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -1722,7 +3006,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1770,7 +3054,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1782,7 +3066,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1794,7 +3078,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1821,7 +3105,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P30" headerRowCount="1">
-  <autoFilter ref="A1:P30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P19" headerRowCount="1">
+  <autoFilter ref="A1:P19"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,17 +593,17 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -613,909 +613,35 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cayma, de Cayma</t>
+          <t>Nicolas de Pierola, de Nicolas de Pierola</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Cayma: 1 de Junio Zona A, 30 de Marzo, Acequia Alta, Charcani Chapi Chico, Francisco Bolognesi, Jose Olaya, Juan Velasco Alvarado, La Tomilla Zona C, Rafael Belaunde Diez Canseco Zona A-C, San Martin de Porres, Villa El Mirador.</t>
+          <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento de redes en media tensión.</t>
+          <t>Cambio de transformador, cambio de crucetas, aisladores y podado)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : [1701] CHACHANI.</t>
+          <t>Circuito : Toran desde CC - 810132.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO DE REDES</t>
+          <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
+          <t>8611, 7153, 7154, 7155.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026:
-Circuito : [1701] CHACHANI.
-Hora : 08:00 a 15:00 Hrs.
-Motivo : Mantenimiento de redes en media tensión.
-Zonas afectadas: Urbanizaciones del distrito de Cayma: 1 de Junio Zona A, 30 de Marzo, Acequia Alta, Charcani Chapi Chico, Francisco Bolognesi, Jose Olaya, Juan Velasco Alvarado, La Tomilla Zona C, Rafael Belaunde Diez Canseco Zona A-C, San Martin de Porres, Villa El Mirador.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 4003, 3935, 3444, 1998, 2892, 2026, 2027, 1709, 1577, 2022, 1275, 1834, 2640, 2028, 1132, 1660, 1001, 2270, 2992, 1714, 1889, 1886, 3094, 2417, 2409, 2415, 1888, 1887, 2408, 2416, 3108, 1635, 2032, 1404, 4013, 4100, 4560, 5002, 5118, 5153, 5346, 5369, 5620, 5752, 5757, 5756, 10234.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:13 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:13</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5994&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>689092c9a8d94730ffb51eb4289cb92b5604087fe86d9f1f1b346e4af0f0170c</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>5995</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Yanahuara, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3257.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 3257.
-Hora : 08:00 a 08:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra N° 3 de Av. Francisco Bolognesi (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:14 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:14</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5995&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>b2cb1294637255df7e81e1e794cdb5e73a2eb3bcbaea11bc1a48f8c115193493</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>5996</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Yanahuara, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1450.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 1450.
-Hora : 08:30 a 08:50 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. B de Urb. La Rinconada (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:17 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:17</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5996&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>731c6f480b229404944fab3f07c10efdce5a22e104bb45b16d8ffc0f525c80b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>5997</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Yanahuara, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3264.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 3264.
-Hora : 09:00 a 09:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra 7-8 de Calle Jerusalén (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:21 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:21</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5997&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>b5edd2d9ef183847fee1539275c380fc5bcd212aa5b98cb8ad3fd33cca92ec54</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5998</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Yanahuara, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3263.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 3263.
-Hora : 09:30 a 09:50 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra 5-6-7 de Calle Zela, cuadra 5-6 de calle Oscar, cuadra 2 de calle Manco Capac (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:22 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:22</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5998&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>b7d153ca18abc4cb6eb956bbddedac6ab20d1ea64ac5488e31d9adeac33ef1bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5999</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Yanahuara, de Yanahuara</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1800.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 1800.
-Hora : 10:00 a 10:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra 7 de Av. Ejército, cuadra 2-3-4 de calle Tronchadero, cuadra 6-7 de calle Beatriz (Distrito de Yanahuara).</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:23</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=5999&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>ae64e076a14a38c9b9f8f758922b93ed487635a9c4fe0d160c68015603056e4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Cayma, de Cayma</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Urb. El Señorial (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 1542.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 1542.
-Hora : 10:30 a 10:50 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Urb. El Señorial (Distrito de Cayma).</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:23 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:23</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6000&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>ec3d14f94585eda9e2aa9fb040ee74c971c21fe804c09395d21e3cdaa2ea8076</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>6001</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Cayma, de Cerro Cayma</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3166.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 3166.
-Hora : 11:00 a 11:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Cuadra 5 de Av. Cayma, Pasaje Santa Cruz, Calle Manzanos, Calle Los Ciruelos (Distrito de Cerro Cayma).</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:24 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:24</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6001&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>31f5824a8b64f3291c0e7896881f2752f7d7b0480214982b9c35729a24372e77</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>6002</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 2596.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 2596.
-Hora : 14:00 a 14:20 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. A-B-C de Asociación Javier de la Luna Pizarro (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:31 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:31</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6002&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9cbfa3dff2d6b0debe64d6379bd6b90e2fb033ff2447d9deef201c258dea30b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>6003</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Yura, de Yura</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 10292.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 10292.
-Hora : 14:40 a 15:00 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. A-B-D-S-T-U de Zona 3 de Urb. Asociación Ciudad de Dios (Distrito de Yura).</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:32</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6003&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>8b291e4a5cc7f5eeb932f91fc95c6c5b5c90cc379abc3942a24224a462610f4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>6004</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Cerro Colorado, de Cerro Colorado</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de posición del conmutador.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : SED 3697</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-MIÉRCOLES, 02 DE SETIEMBRE DE 2026.
-Circuito : SED 3697.
-Hora : 15:40 a 16:00 Hrs.
-Motivo : Cambio de posición del conmutador.
-Zonas afectadas: Mz. 4-11-18-19 Zona F de Urb. Semi Rural Pachacutec (Distrito de Cerro Colorado).</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:32 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:32</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6004&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6f2269335f482bf152f818302bfba2e79d7347a26921e5b67e40027df0e92d1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Nicolas de Pierola, de Nicolas de Pierola</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Cambio de transformador, cambio de crucetas, aisladores y podado)</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Toran desde CC - 810132.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8611, 7153, 7154, 7155.</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 JUEVES, 03 DE SETIEMBRE DE 2026:
@@ -1526,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8611, 7153, 7154, 7155.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 31/08/2026 8:33 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>31/08/2026 8:33</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6005&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>899326f4376898673d82bd0aef6af9f54f80ef232fa975b6a83272ec55fe727e</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6014</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Uraca, de Uraca</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Uraca: Bellavista, La Candelaria, Toro Grande.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, podad de árboles, cambio de crucetas).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : Corire desde CC - 810131.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>7484, 7104, 7148, 7103, 7102, 7105, 7174.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026:
@@ -1610,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7484, 7104, 7148, 7103, 7102, 7105, 7174.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 17:59 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 17:59</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6014&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>47172288e10064d0027470fa61df82dc98c36097a35feb79f6983f71752ff85f</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6016</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: El Mirador Al Pacifico, La Victoria, Villa Lourdes 1-2 Etapa.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de transformador, otros mantenimientos).</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Florida desde BC - 200566.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8256, 8072, 8069, 8071, 8579, 8073.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026:
@@ -1694,80 +820,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8256, 8072, 8069, 8071, 8579, 8073.</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:02</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6016&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>03131189727b6099f258787edbaa3c05152a4130e0f164c65f11a3d18d08ee59</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de distrito de Cerro Colorado: Apipa Sector IX-X-VIII-XII, Jose Luis Bustamante y Rivero</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde BC - 080313.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>5136, 5138, 5137, 5440, 5441, 5442, 5443, 5444, 5445, 5852.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026:
@@ -1778,76 +904,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5136, 5138, 5137, 5440, 5441, 5442, 5443, 5444, 5445, 5852.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:01</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6015&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>b6bc3059c534ec14beaff64f9802c9b904dd1632d98146dc0b54235f2ff38869</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6017</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>08:25</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urb. San Jeronimo, Mz.B de Urb. Los Pilcos (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1283.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1857,76 +983,76 @@
 Zonas afectadas: Urb. San Jeronimo, Mz.B de Urb. Los Pilcos (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:04</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6017&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>51ee02cf1b89f80117c359a7e45962bee4cd30ff7ef36f971b3b17b0182dfa3c</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6018</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Urb. Cooperativa Ferroviaria (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1282.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1936,76 +1062,76 @@
 Zonas afectadas: Urb. Cooperativa Ferroviaria (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:04</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6018&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>a6c76d6fb5ac0f8e42e8210edd35ab708eb0e3ed03abefce94dac22d20d1bd3d</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6019</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>09:55</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Cuadra 1 de Calle Prolongación Vitor Lira (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3898.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2015,76 +1141,76 @@
 Zonas afectadas: Cuadra 1 de Calle Prolongación Vitor Lira (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:05</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6019&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>78747bc2ace2e3e68d747edc95fd809315add28df59793e1e19278041a26d3c3</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6020</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>10:10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>10:35</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Urb. Francisco Mostajo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1747.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2094,76 +1220,76 @@
 Zonas afectadas: Urb. Francisco Mostajo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:06</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6020&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>33a0d1176ab1e83295183e5f2101d6aa80877c1249672e3d9b5f389659d272ce</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="70" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6022</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>11:55</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Cuadra 1 de Av. Dolores (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3417.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2173,76 +1299,76 @@
 Zonas afectadas: Cuadra 1 de Av. Dolores (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:09</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6022&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>d808b96cd47f10923eb6e33ed94b59b01e4467a6ec77cc6ac55d0813cc0dd7e5</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Mz. B-C-D de Urb. Los Rosales (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3859.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2252,76 +1378,76 @@
 Zonas afectadas: Mz. B-C-D de Urb. Los Rosales (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:06</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6021&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>e33844d951c1e00dbc0a2726bb00b877de12101b1d7bba34fa50a2016a5fcf24</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="70" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6023</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>12:35</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Mz. G de Urb. Cooperativa Daniel Alcides Carrión (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3855.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2331,76 +1457,76 @@
 Zonas afectadas: Mz. G de Urb. Cooperativa Daniel Alcides Carrión (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:10</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6023&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>a5c5861c03766cc65a49278896ed7c6cdde20072f3fb9b68e721d3f9842439b3</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="70" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6024</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Paucarpata, de Paucarpata</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>II Etapa de Urb. Guardia Civil (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1299.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2410,76 +1536,76 @@
 Zonas afectadas: II Etapa de Urb. Guardia Civil (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:10</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6024&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>8ac102f43023f77e323fb0077f77ebdaab1e91373df7ee1983203ffa421c53e7</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="70" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6025</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>14:40</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Urb. La Encalada (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1738</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2489,76 +1615,76 @@
 Zonas afectadas: Urb. La Encalada (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:11 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:11</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6025&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>ad5f909b4fb973508e48baa3afa0bf3570867b6594a80b040975afbbd7e9c2eb</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="70" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>6026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Mz. C-D-E-L de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3612.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2568,76 +1694,76 @@
 Zonas afectadas: Mz. C-D-E-L de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:12 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:12</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6026&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>2dbe2978b023cbe86aaf594864d76981c0e89201154c1633ff36b2f686c1a81a</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="70" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>6027</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>15:50</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Mz. F-G-H-I-J de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3613.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2647,76 +1773,76 @@
 Zonas afectadas: Mz. F-G-H-I-J de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:13</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6027&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>5132a83c0e658459b576364f7c44a4520c099e73217c7e525d63bc3800f90527</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="70" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>6028</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>16:25</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-D-E-J de Urb. Alameda del Sol, MZ. A-B-D-E-F de Urb. Santa Úrsula (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4404.</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -2726,80 +1852,80 @@
 Zonas afectadas: Mz. A-B-D-E-J de Urb. Alameda del Sol, MZ. A-B-D-E-F de Urb. Santa Úrsula (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:13</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6028&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>e49d0bd12f6b0c5d09ab03365ea56a1e5734ccee810823e79ab3bc4f4309cdb3</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="70" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>6013</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento del transformador de la subestación de Caylloma.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Circuito : [9301] SAN ANTONIO.</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SÁBADO, 05 DE SETIEMBRE DE 2026:
@@ -2810,80 +1936,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 17:58 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 17:58</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6013&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>87cae465b632a656491c44ae0cc47040622c28e945e4feb4714ea9c02b51d013</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="70" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>6029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>06/09/2026</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de transformador de potencia.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SET : [7] CHALLAPAMPA.</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 06 DE SETIEMBRE DE 2026:
@@ -2894,30 +2020,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:14</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6029&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>d97067c0261932b1d64c143bed897ec74373434e8a879bfb1928de309a3cfa3b</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P30"/>
+  <autoFilter ref="A1:P19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2958,7 +2084,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:36:51</t>
+          <t>2026-09-04 14:24:00</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2108,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2120,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -3006,7 +2132,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3078,7 +2204,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -3105,7 +2231,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/cortes_seal_latest.xlsx
+++ b/docs/cortes_seal_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cortes'!$A$1:$P$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P19" headerRowCount="1">
-  <autoFilter ref="A1:P19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaCortesSEAL" displayName="TablaCortesSEAL" ref="A1:P18" headerRowCount="1">
+  <autoFilter ref="A1:P18"/>
   <tableColumns count="16">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fecha"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -613,22 +613,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nicolas de Pierola, de Nicolas de Pierola</t>
+          <t>Uraca, de Uraca</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.</t>
+          <t>Urbanizaciones del distrito de Uraca: Bellavista, La Candelaria, Toro Grande.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cambio de transformador, cambio de crucetas, aisladores y podado)</t>
+          <t>Mantenimiento de redes en media tensión (cambio de postes, podad de árboles, cambio de crucetas).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Circuito : Toran desde CC - 810132.</t>
+          <t>Circuito : Corire desde CC - 810131.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -638,94 +638,10 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>8611, 7153, 7154, 7155.</t>
+          <t>7484, 7104, 7148, 7103, 7102, 7105, 7174.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.
-JUEVES, 03 DE SETIEMBRE DE 2026:
-Circuito : Toran desde CC - 810132.
-Hora : 07:00 a 15:00 Hrs.
-Motivo : Cambio de transformador, cambio de crucetas, aisladores y podado)
-Zonas afectadas: Urbanizaciones del distrito de Nicolas de Pierola: Charahuayo, Sahuani, San Martin.
-Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8611, 7153, 7154, 7155.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>el 31/08/2026 8:33 por Cuenta del sistema</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>31/08/2026 8:33</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6005&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>899326f4376898673d82bd0aef6af9f54f80ef232fa975b6a83272ec55fe727e</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6014</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Uraca, de Uraca</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Urbanizaciones del distrito de Uraca: Bellavista, La Candelaria, Toro Grande.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mantenimiento de redes en media tensión (cambio de postes, podad de árboles, cambio de crucetas).</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Circuito : Corire desde CC - 810131.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO DE REDES.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>7484, 7104, 7148, 7103, 7102, 7105, 7174.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026:
@@ -736,80 +652,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7484, 7104, 7148, 7103, 7102, 7105, 7174.</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 17:59 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 17:59</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6014&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>47172288e10064d0027470fa61df82dc98c36097a35feb79f6983f71752ff85f</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>6016</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Mollendo, de Mollendo</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Mollendo: El Mirador Al Pacifico, La Victoria, Villa Lourdes 1-2 Etapa.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes en media tensión (cambio de postes, cambio de transformador, otros mantenimientos).</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Circuito : La Florida desde BC - 200566.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8256, 8072, 8069, 8071, 8579, 8073.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026:
@@ -820,80 +736,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 8256, 8072, 8069, 8071, 8579, 8073.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:02 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:02</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6016&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>03131189727b6099f258787edbaa3c05152a4130e0f164c65f11a3d18d08ee59</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>6015</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Cerro Colorado, de Cerro Colorado</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones de distrito de Cerro Colorado: Apipa Sector IX-X-VIII-XII, Jose Luis Bustamante y Rivero</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de redes de media tensión.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Circuito : P. Yura desde BC - 080313.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5136, 5138, 5137, 5440, 5441, 5442, 5443, 5444, 5445, 5852.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026:
@@ -904,76 +820,76 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 5136, 5138, 5137, 5440, 5441, 5442, 5443, 5444, 5445, 5852.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:01 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:01</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6015&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>b6bc3059c534ec14beaff64f9802c9b904dd1632d98146dc0b54235f2ff38869</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>6017</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>08:25</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Urb. San Jeronimo, Mz.B de Urb. Los Pilcos (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1283.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -983,76 +899,76 @@
 Zonas afectadas: Urb. San Jeronimo, Mz.B de Urb. Los Pilcos (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:04</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6017&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>51ee02cf1b89f80117c359a7e45962bee4cd30ff7ef36f971b3b17b0182dfa3c</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>6018</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urb. Cooperativa Ferroviaria (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1282.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1062,76 +978,76 @@
 Zonas afectadas: Urb. Cooperativa Ferroviaria (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:04 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:04</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6018&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>a6c76d6fb5ac0f8e42e8210edd35ab708eb0e3ed03abefce94dac22d20d1bd3d</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6019</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>09:55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Cuadra 1 de Calle Prolongación Vitor Lira (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3898.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1141,76 +1057,76 @@
 Zonas afectadas: Cuadra 1 de Calle Prolongación Vitor Lira (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:05 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:05</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6019&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>78747bc2ace2e3e68d747edc95fd809315add28df59793e1e19278041a26d3c3</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6020</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>10:10</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>10:35</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Arequipa, de Arequipa</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Urb. Francisco Mostajo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1747.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1220,76 +1136,76 @@
 Zonas afectadas: Urb. Francisco Mostajo (Distrito de Arequipa).</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:06</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6020&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>33a0d1176ab1e83295183e5f2101d6aa80877c1249672e3d9b5f389659d272ce</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>6022</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>11:55</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Cuadra 1 de Av. Dolores (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3417.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1299,76 +1215,76 @@
 Zonas afectadas: Cuadra 1 de Av. Dolores (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:09 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:09</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6022&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>d808b96cd47f10923eb6e33ed94b59b01e4467a6ec77cc6ac55d0813cc0dd7e5</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>6021</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Mz. B-C-D de Urb. Los Rosales (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3859.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1378,76 +1294,76 @@
 Zonas afectadas: Mz. B-C-D de Urb. Los Rosales (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:06 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:06</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6021&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>e33844d951c1e00dbc0a2726bb00b877de12101b1d7bba34fa50a2016a5fcf24</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>6023</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>12:35</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Mz. G de Urb. Cooperativa Daniel Alcides Carrión (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3855.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1457,76 +1373,76 @@
 Zonas afectadas: Mz. G de Urb. Cooperativa Daniel Alcides Carrión (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:10</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6023&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>a5c5861c03766cc65a49278896ed7c6cdde20072f3fb9b68e721d3f9842439b3</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>6024</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Paucarpata, de Paucarpata</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>II Etapa de Urb. Guardia Civil (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1299.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1536,76 +1452,76 @@
 Zonas afectadas: II Etapa de Urb. Guardia Civil (Distrito de Paucarpata).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:10 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:10</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6024&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>8ac102f43023f77e323fb0077f77ebdaab1e91373df7ee1983203ffa421c53e7</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>6025</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>14:40</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>15:05</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Urb. La Encalada (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 1738</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1615,76 +1531,76 @@
 Zonas afectadas: Urb. La Encalada (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:11 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:11</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6025&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>ad5f909b4fb973508e48baa3afa0bf3570867b6594a80b040975afbbd7e9c2eb</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>6026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Mz. C-D-E-L de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3612.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1694,76 +1610,76 @@
 Zonas afectadas: Mz. C-D-E-L de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:12 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:12</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6026&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>2dbe2978b023cbe86aaf594864d76981c0e89201154c1633ff36b2f686c1a81a</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>6027</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>15:50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Mz. F-G-H-I-J de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 3613.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1773,76 +1689,76 @@
 Zonas afectadas: Mz. F-G-H-I-J de Urb. Casabella (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:13</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6027&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>5132a83c0e658459b576364f7c44a4520c099e73217c7e525d63bc3800f90527</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>6028</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>04/09/2026</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>16:25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Jose Luis Bustamante, Rivero, de Jose Luis Bustamante</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Mz. A-B-D-E-J de Urb. Alameda del Sol, MZ. A-B-D-E-F de Urb. Santa Úrsula (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Cambio de posición del conmutador.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Circuito : SED 4404.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 VIERNES, 04 DE SETIEMBRE DE 2026.
@@ -1852,80 +1768,80 @@
 Zonas afectadas: Mz. A-B-D-E-J de Urb. Alameda del Sol, MZ. A-B-D-E-F de Urb. Santa Úrsula (Distrito de Jose Luis Bustamante y Rivero).</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:13 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:13</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6028&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>e49d0bd12f6b0c5d09ab03365ea56a1e5734ccee810823e79ab3bc4f4309cdb3</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>6013</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Caylloma, Sibayo, Tisco, de Caylloma, de Sibayo, de Tisco</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Caylloma: Coraza, Cuchocapilla, Jachaña, Pusa Pusa, Santa Rosa, Sotocaya. Urbanizaciones del distrito de Sibayo: Condorcuyo. Urbanizaciones del distrito de Tisco: Ccascas, Tarucamarca.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento del transformador de la subestación de Caylloma.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Circuito : [9301] SAN ANTONIO.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 SÁBADO, 05 DE SETIEMBRE DE 2026:
@@ -1936,80 +1852,80 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 7603, 7611, 7608, 7609, 7604, 7610, 7607, 7606, 7605, 7602.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 17:58 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 17:58</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6013&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>87cae465b632a656491c44ae0cc47040622c28e945e4feb4714ea9c02b51d013</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>6029</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>06/09/2026</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Cayma, Cerro Colorado, Yanahuara, de Cayma, de Cerro Colorado, de Yanahuara</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Urbanizaciones del distrito de Cayma: Andres Avelino Caceres, Buenos Aires de Cayma Zona 1-2, Casimiro Cuadros, Casimiro Cuadros I Alto Cayma, Dean Valdivia, Dean Valdivia Sector 2, Jose Abelardo Quiñones, Jose Carlos Mariategui, Jose Olaya, Las Malvinas, Villa Continental, Villa Continental Zona 1-2-4, Virgen de La Candelaria. Urbanizaciones del distrito de Cerro Colorado: Alto Libertad, Arqueta, Asociacion Policial Campo Verde, Buenos Aires de Cayma Zona 2, Cerro Colorado (Pueblo Viejo), Challapampa, Colegio de Ingenieros, Docentes de La Catolica, El Azufral, El Solar de Challapampa, Fundo Challapampa, Habilitacion Urbana La Alqueria, Ibarcena, Juan Manuel Guillen, La Castellana, La Hacienda, La Libertad, La Merced, La Merced II, La Molina, La Planicie de Challapampa, La Tejada, Las Flores, Los Alamos, Los Sauces, Micaela Bastidas, Quinta Azores, Residencial Casabella, Residencial Monte Bello, Rio Seco, San Pedro, Semi-Rural Pachacutec Grupo 14-15-16-19-23-24-25, Semi-Rural Pachacutec Grupo 6, Teresa de Jesus, Tupac Amaru Zona B, Urbanizacion La Pradera, Urbanizacion Quinta Luisa, Veracruz, Via Evitamiento, Victor Andres Belaunde, Villa Arequipa, Villa Florida, Zamacola. Urbanizaciones del distrito de Yanahuara: San Pedro.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Mantenimiento de transformador de potencia.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>SET : [7] CHALLAPAMPA.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>MANTENIMIENTO DE REDES.
 DOMINGO, 06 DE SETIEMBRE DE 2026:
@@ -2020,30 +1936,30 @@
 Subestaciones eléctricas de distribución (SED), involucradas según zonas afectadas líneas arriba: 1799, 2106, 2957, 1985, 1903, 1672, 3109, 2956, 3368, 3743, 3742, 1256, 2908, 1239, 3741, 3776, 3753, 3938, 2169, 1661, 3971, 3956, 3939, 3965, 3964, 3966, 3972, 1496, 3924, 3967, 3927, 4012, 2789, 2048, 1516, 3135, 3132, 3119, 3127, 3126, 1467, 1251, 3710, 2155, 3323, 4008, 1623, 2806, 3430, 1671, 1773, 2893, 2972, 3610, 3631, 1259, 3121, 3909, 3908, 2690, 3912, 1560, 1700, 3393, 3398, 2294, 1662, 1713, 1831, 1537, 1772, 1250, 1664, 3380, 3510, 1972, 3801, 3822, 1624, 1248, 1531, 1734, 3600, 3093, 1258, 2317, 2984, 1973, 2085, 1041, 1764, 1070, 1051, 1902, 1054, 2653, 1693, 2221, 1792, 2845, 1722, 1733, 1736, 1904, 1988, 1735, 2692, 1241, 3343, 1247, 3287, 3718, 2107, 3645, 1240, 3553, 3226, 2812, 2655, 3099, 2486, 3207, 3400, 1459, 2246, 3528, 1493, 2689, 2691, 3326, 2635, 1464, 3217, 2422, 3868, 3726, 1522, 3381, 4017, 3201, 4009, 3747, 1665, 1588, 4149, 4152, 4171, 4198, 4204, 4232, 4293, 4298, 3957, 4305, 4317, 4326, 4337, 4344, 4394, 4395, 4545, 4511, 4546, 4568, 4569, 4578, 4592, 4577, 4597, 4624, 4663, 4673, 4674, 4807, 4825, 4868, 4897, 4898, 4889, 4694, 4799, 4953, 4945, 4993, 4995, 5034, 5066, 5083, 5084, 5058, 5029, 5194, 5264, 5161, 5184, 5125, 5289, 5296, 5291, 5316, 5318, 5074, 5004, 5045, 5009, 5010, 4723, 5333, 4951, 5117, 5320, 4915, 5390, 5505, 5504, 5425, 5511, 5510, 5576, 5588, 5565, 5196, 5631, 5049, 5633, 5416, 3120, 5640, 5655, 5694, 5695, 5622, 5675, 5727, 5713, 5512, 5794, 5795, 5808, 5851, 5858, 5883, 5884, 5891, 5949, 5956, 3873, 5966, 10037, 10036, 10050, 10151, 5962, 10191, 5974, 10271, 10194, 1120, 10262, 2978, 3611, 3202, 3200, 5928, 1929, 1515, 10223, 2330, 2846, 2842, 1765, 1875, 2713, 4412, 10264, 4056, 4035.</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>el 02/09/2026 18:14 por Cuenta del sistema</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>02/09/2026 18:14</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>https://www.seal.com.pe/clientes/Lists/Calendario/DispForm.aspx?ID=6029&amp;Source=https%3A%2F%2Fwww.seal.com.pe%2Fclientes%2FSitePages%2FCortes.aspx</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>d97067c0261932b1d64c143bed897ec74373434e8a879bfb1928de309a3cfa3b</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P19"/>
+  <autoFilter ref="A1:P18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2084,7 +2000,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04 14:24:00</t>
+          <t>2026-09-05 13:28:21</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2024,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2036,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2048,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2120,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2147,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
